--- a/smartbiz_bulk_upload_template_v10.xlsx
+++ b/smartbiz_bulk_upload_template_v10.xlsx
@@ -7974,30 +7974,21 @@
       </c>
     </row>
     <row r="2" ht="51" customHeight="1">
-      <c r="A2" t="inlineStr"/>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>whl239_73380_big_round_rangoli_stencil_b</t>
+          <t>whl239_73330_rng_stn_om_12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Big Round Rangoli Stencil Board for Home Entrance, Diwali and Festival Decor</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
+          <t>Om Mandala Rangoli Design – Mess-Free Pooja Decoration</t>
+        </is>
+      </c>
+      <c r="H2" t="n">
+        <v>539</v>
+      </c>
+      <c r="I2" t="n">
+        <v>259</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -8006,108 +7997,66 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Create beautiful traditional designs with this round MDF rangoli stencil board. Perfect for home entrance, living areas, or mandir decorations during Diwali, Navratri, weddings, and other festive occasions, this large stencil helps you achieve neat and elegant rangoli patterns with ease. Its circular design ensures a balanced and eye-catching centerpiece, making it ideal for both beginners and experienced rangoli artists. Key features Big round MDF rangoli stencil board Guided layout for clean, even color filling Suitable for large floor decoration spaces Beginner-friendly format for easy use Creates a festive centerpiece effect Materials &amp;amp; care This rangoli stencil board is made from durable MDF. To clean, gently wipe with a dry or slightly damp cloth. Avoid prolonged exposure to water to&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+          <t>&lt;p&gt;Enhance your pooja room or home entrance with this Om Mandala Rangoli design stencil. Perfect for creating a sacred and serene atmosphere during festivals and rituals, this stencil helps you achieve a clean, precise, and mess-free rangoli every time. Key features Sacred Om Design – Ideal for mandir, pooja rooms, and festive celebrations. Mess-Free Application – Keeps colors neatly within the stencil for crisp lines. Heavy MDF Base – Ensures stability and prevents movement even under a fan. Reusable and Durable – Made to last with sturdy materials for repeated use. Easy Maintenance – Simply brush off colors after use and store for next time. Materials &amp;amp; care Crafted from durable MDF, this rangoli stencil is designed for steady use. To maintain its quality, gently brush off any residual powd&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U2" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr"/>
       <c r="W2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/nn0gyk.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/nG8pP6034D.jpg</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/mybcf6.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/qjVOzEOdV6.jpg</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4vacd3.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/7MiafrLHU9.jpg</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/46xsyf.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/eC4r57kdI4.jpg</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/xe3x17.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Wjirk4ymqK.jpg</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/fqnxts.jpg</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
-      <c r="AF2" t="inlineStr"/>
-      <c r="AG2" t="inlineStr"/>
-      <c r="AH2" t="inlineStr"/>
-      <c r="AI2" t="inlineStr"/>
-      <c r="AJ2" t="inlineStr"/>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="inlineStr"/>
-      <c r="AN2" t="inlineStr"/>
-      <c r="AO2" t="inlineStr"/>
-      <c r="AP2" t="inlineStr"/>
-      <c r="AQ2" t="inlineStr"/>
-      <c r="AR2" t="inlineStr"/>
-      <c r="AS2" t="inlineStr"/>
-      <c r="AT2" t="inlineStr"/>
-      <c r="AU2" t="inlineStr"/>
-      <c r="AV2" t="inlineStr"/>
-      <c r="AW2" t="inlineStr"/>
-      <c r="AX2" t="inlineStr"/>
-      <c r="AY2" t="inlineStr"/>
-      <c r="AZ2" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/9c038ad8-5546-4b2d-9475-6d6ce7435c04.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="51" customHeight="1">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>13749_adiyogi_shiva_smoke_fountain_1pc</t>
+          <t>whl313_90633_pm105_murti</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Adiyogi Shiva Backflow Incense Holder – Serene Smoke Fountain | Fixorix</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
+          <t>Panchmukhi Hanuman Idol for Home, Office &amp; Car Dashboard Spiritual Decor</t>
+        </is>
+      </c>
+      <c r="H3" t="n">
+        <v>499</v>
+      </c>
+      <c r="I3" t="n">
+        <v>349</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -8116,108 +8065,66 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Experience spiritual tranquility with our exquisite Adiyogi Shiva Backflow Incense Holder , designed to bring peace and a mesmerizing visual display to your home. This stunning smoke fountain creates a cascade of fragrant smoke, flowing downwards like a serene waterfall, perfectly embodying the calm and meditative spirit of Lord Shiva. Crafted with devotion and precision, this unique piece not only serves as a beautiful decorative item but also as a focal point for meditation and spiritual practices. The gentle descent of the smoke fosters a calming atmosphere, making it an ideal addition to your puja room, living area, or office. Embrace the divine aura and elevate your space with this captivating Adiyogi Shiva Backflow Incense Holder. It’s more than just an incense burner; it’s an invita&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+          <t>&lt;p&gt;Discover the divine presence of a Panchmukhi Hanuman idol , perfect for enhancing your spiritual space. This beautifully crafted idol embodies protection, courage, and devotion, bringing positive energy to your home, office, or car dashboard. Its intricate design and antique bronze finish make it a truly special addition to any decor. Key features Premium antique bronze finish with detailed craftsmanship Depicts the powerful Panchmukhi (Five-Faced) Hanuman form Symbol of protection, courage, devotion, and success Intricate traditional design with sacred weapons and ornaments Ideal for home temples, offices, and spiritual spaces Durable and elegant decorative idol Perfect gift for Hanuman Jayanti, Diwali, housewarming ceremonies, and religious occasions Materials &amp;amp; care Crafted with a durab&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr"/>
       <c r="W3" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_09315466-9d0c-49c3-ad47-bc7ca1f803f5.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/0fKCWS2Oce.jpg</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_b3af6617-7bc3-4fb3-856b-5d30a0374fea.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/P7wd9B2NAL.jpg</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_ed6ff1f8-ebe7-425b-b8c1-7149520d89d7.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/n8Y1s6GVMm.jpg</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_c37763ff-ea14-4478-8a23-a77914484708.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4eGHmZINcF.jpg</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_750e495d-6d97-4ac0-a6ac-f3d00970fc90.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/lVdyq9JuSj.jpg</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_86da234f-d53e-4aca-8ead-44691e2c5b01.jpg</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
-      <c r="AH3" t="inlineStr"/>
-      <c r="AI3" t="inlineStr"/>
-      <c r="AJ3" t="inlineStr"/>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
-      <c r="AM3" t="inlineStr"/>
-      <c r="AN3" t="inlineStr"/>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
-      <c r="AS3" t="inlineStr"/>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr"/>
-      <c r="AX3" t="inlineStr"/>
-      <c r="AY3" t="inlineStr"/>
-      <c r="AZ3" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/HH9yyt2nK9.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="51" customHeight="1">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22461_2in1_cleaning_brush</t>
+          <t>whl239_73363_decor_laxmi_charan_paduka_s</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2 in 1 Floor Cleaning Brush with Water Scraper and Metal Handle for Bathroom Use</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
+          <t>Laxmi Charan Paduka Stickers – Festive Spiritual Home Décor (Pack of 2)</t>
+        </is>
+      </c>
+      <c r="H4" t="n">
+        <v>559</v>
+      </c>
+      <c r="I4" t="n">
+        <v>229</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -8226,108 +8133,66 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Efficiently tackle floor cleaning with this versatile 2 in 1 floor cleaning brush with water scraper. This innovative tool combines dense scrubbing bristles and an integrated scraper edge, making it perfect for both loosening dirt and moving water across various hard floor surfaces. Its sectional metal handle provides sturdy support and can be disassembled for compact storage, while the top grip includes a convenient hanging hole for easy storage. Key features Two-in-one head combines a scrubbing brush with a water scraper for dual functionality. Dense bristles effectively loosen dirt and grime during manual scrubbing tasks. Integrated scraper edge efficiently moves water across suitable hard floors, speeding up drying. Sectional metal handle ensures durability and allows for easy assembly&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
+          <t>&lt;p&gt;Enhance your home&amp;#x27;s spiritual aura with our Laxmi Charan Paduka Sticker Set, designed to bring blessings and prosperity during festivals and daily pooja rituals. These sacred Laxmi Charan Paduka stickers feature traditional footprints embellished with vibrant beads and sparkling stones for a divine touch, making them perfect for festive spiritual home decor. Key features Traditional Goddess Lakshmi footprints featuring the auspicious Swastik symbol Decorated with multicolored beads, sequins, and glittering stones for vibrant appeal Easy peel-and-stick backing suitable for doors, walls, floors, and pooja thalis Reusable and simple to clean with a dry wipe, ideal for multiple festive occasions Perfect for Diwali, Lakshmi Pujan, Navratri, Griha Pravesh, and spiritual home decoration Comes pac&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U4" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22461-1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_9da764a6-0ee2-4da6-aac6-e8bc7849da42.jpg</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22461-2.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_d891c284-8708-4c38-b0e4-aeca264c3244.jpg</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22461-3.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_edf02a26-c1a5-4ee0-a634-cb9843a6d666.jpg</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22461-4.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_155b0a2f-27c8-4248-af67-d5b57806a5a7.jpg</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22461-5.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_1e5c06fe-75d5-4c51-afe2-d262f4fccc14.jpg</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22461-6.jpg</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
-      <c r="AH4" t="inlineStr"/>
-      <c r="AI4" t="inlineStr"/>
-      <c r="AJ4" t="inlineStr"/>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr"/>
-      <c r="AM4" t="inlineStr"/>
-      <c r="AN4" t="inlineStr"/>
-      <c r="AO4" t="inlineStr"/>
-      <c r="AP4" t="inlineStr"/>
-      <c r="AQ4" t="inlineStr"/>
-      <c r="AR4" t="inlineStr"/>
-      <c r="AS4" t="inlineStr"/>
-      <c r="AT4" t="inlineStr"/>
-      <c r="AU4" t="inlineStr"/>
-      <c r="AV4" t="inlineStr"/>
-      <c r="AW4" t="inlineStr"/>
-      <c r="AX4" t="inlineStr"/>
-      <c r="AY4" t="inlineStr"/>
-      <c r="AZ4" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_7f2a7e37-7e1e-4011-af4f-c64f39073aa9.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="51" customHeight="1">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>whl167_48504_lavendor_agarbatti</t>
+          <t>9041_small_hand_tally_counter</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Agarbatti – Premium Organic Incense Sticks for Puja &amp; Home</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
+          <t>Hand Tally Counter for Jaap and Mantra Chanting Pooja Use</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>509</v>
+      </c>
+      <c r="I5" t="n">
+        <v>219</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -8336,104 +8201,66 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Experience peace and purity with our premium Agarbatti, perfect for Puja, prayers, and enhancing your home ambiance. These organic incense sticks create a calming atmosphere, infused with the delicate Nightqueen fragrance. Key features Premium quality organic agarbatti ideal for religious rituals and daily worship Refreshing Nightqueen aroma suitable for meditation and spiritual spaces Natural, non-toxic ingredients inspired by Ayurvedic traditions Enhances home fragrance, bringing relaxation and balance 90gm pack providing long-lasting incense use Safe for family use with no harmful chemicals Supports tranquil and devotional environment FAQ Q1: What makes this agarbatti ideal for puja? A: Our agarbatti is made from natural, organic materials and infused with a sacred fragrance, perfect fo&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
+          <t>&lt;p&gt;A digital finger tally counter with strap simplifies your spiritual practices by accurately tracking repetitions. This essential tool ensures your focus remains on your jaap or mantra chanting, removing the distraction of manual counting. Its compact design and comfortable strap make it ideal for extended use during daily prayers, meditation, or temple visits. Key features Keeps precise count for uninterrupted chanting and meditation One-thumb press operation allows for easy, discreet counting Reading holds even when paused, perfect for intermittent use Quick reset dial returns count to zero for new sessions Compact size with a strap for comfortable, secure wear on finger Manual click mechanism means no batteries are required Portable design fits easily in pooja thali, pocket, or bag Versa&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U5" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/0ba17838-d6ae-4d84-91bb-aae90a6f2c12.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/9041_656ca080-9177-4b35-93ae-60b7732d45e4.png</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_f0552278-a4ab-4854-aab1-5274d36b0cad.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/eedc839b-60ab-46ad-99d2-45ecaa0c38f3.jpg</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_81673033-3bf0-4e1c-b915-beb13ce18ff8.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/7_7da8be7e-c7e8-48ac-90bb-dd94e795c570.jpg</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_a09959c3-2d4c-42b1-988a-07005c4dc9a3.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/8_4ba63586-6093-450c-8983-0bb4ad8820ff.jpg</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_252c9a00-49de-41ef-86e6-d5bb11ea897a.jpg</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
-      <c r="AH5" t="inlineStr"/>
-      <c r="AI5" t="inlineStr"/>
-      <c r="AJ5" t="inlineStr"/>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
-      <c r="AN5" t="inlineStr"/>
-      <c r="AO5" t="inlineStr"/>
-      <c r="AP5" t="inlineStr"/>
-      <c r="AQ5" t="inlineStr"/>
-      <c r="AR5" t="inlineStr"/>
-      <c r="AS5" t="inlineStr"/>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AU5" t="inlineStr"/>
-      <c r="AV5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr"/>
-      <c r="AX5" t="inlineStr"/>
-      <c r="AY5" t="inlineStr"/>
-      <c r="AZ5" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/4_11d433d1-4d76-44b8-b5fa-30b7cf078440.jpg</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/5_62ec6240-78d3-49c8-902a-1c574b5f8eac.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="51" customHeight="1">
-      <c r="A6" t="inlineStr"/>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>13687_mix_flav_incense_sticks_10pc</t>
+          <t>22198_hand_shape_kankavati_kumkum_holder</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Agarbatti Sticks – Premium Mixed Flavours for Pooja &amp; Home | Styleva</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>535</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+          <t>Hand Shaped Kankavati – Elegant Puja Storage with Enamel Work</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>535</v>
+      </c>
+      <c r="I6" t="n">
+        <v>229</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -8442,108 +8269,66 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Elevate your daily rituals and infuse your space with peace using our exquisite Brown Incense Sticks from Styleva. Crafted for a truly immersive experience, these premium incense sticks are perfect for daily pooja, deep meditation, or simply creating a serene home fragrance. Each pack delivers 10 long-lasting sticks, featuring a delightful mix of natural aromas like soothing sandalwood and rich woody notes, designed to transform any environment into a calming sanctuary. Experience moments of calm and joy with every burn, making these brown incense sticks an essential for your spiritual and relaxation practices. Key features Handcrafted from premium natural ingredients for a clean, consistent, and long-lasting burn. Features a versatile mix of 10 captivating natural aromas, including tradit&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
+          <t>&lt;p&gt;Discover the beauty and utility of the Hamsa hand decorative puja thali, an exquisite accessory designed for your sacred rituals. Crafted in a traditional hand (hamsa) shape, this kumkum holder features twin compartments for storing kumkum (roli) and chawal (rice), along with two additional lidded boxes for extra storage. Enhanced with intricate blue and teal enamel floral work on a rich golden finish, it adds a divine touch to your home temple, pooja thali, or festival celebrations. This elegant piece not only serves as a practical puja item but also accentuates the spiritual ambiance of your worship space. Key features Hamsa hand shaped decorative kumkum holder Dual compartments for kumkum and chawal Two extra lidded boxes for additional storage Rich golden finish with detailed enamel wo&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/013bcf98-70fc-434f-873f-cf69a13907ce.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-01-no-sku_238ab33d-25cc-4182-82c4-47ef051b6e42.jpg</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/b307a2b6-6078-47d6-a2fa-7fddba796e62.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-02-sku_b70a011f-7333-4e61-b427-3a05d88bfd4b.jpg</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_0ace28fa-cf5b-4964-ac41-a04fd215c57d.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-03-product_db2e4ff7-43b1-4168-ace1-6b2631e96070.jpg</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_e0de1ddf-a72e-4882-9252-e0d7addbfc20_1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-04-product_c0d57e72-f3c9-4144-b5cb-d010ce441491.jpg</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/15_1e81c386-4c17-4026-aa78-8184dc461e5f.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-05-white-bg_27048fdf-a731-4c2b-a9a4-734b7cda6d2c.jpg</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_399ba7b8-21a1-4940-87e0-f7b0183e5130.jpg</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
-      <c r="AH6" t="inlineStr"/>
-      <c r="AI6" t="inlineStr"/>
-      <c r="AJ6" t="inlineStr"/>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr"/>
-      <c r="AM6" t="inlineStr"/>
-      <c r="AN6" t="inlineStr"/>
-      <c r="AO6" t="inlineStr"/>
-      <c r="AP6" t="inlineStr"/>
-      <c r="AQ6" t="inlineStr"/>
-      <c r="AR6" t="inlineStr"/>
-      <c r="AS6" t="inlineStr"/>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AU6" t="inlineStr"/>
-      <c r="AV6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr"/>
-      <c r="AX6" t="inlineStr"/>
-      <c r="AY6" t="inlineStr"/>
-      <c r="AZ6" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-06-size_d81be685-bb60-4de5-b054-f198156a3229.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="51" customHeight="1">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>13678_mix_flav_incense_sticks_90gm</t>
+          <t>whl175_94317_7104</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Agarbatti Sticks – Mixed Floral Fragrance, 90 GM | DeoDap</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+          <t>Decorative Palm Shape Ganesh Idols for Pooja Mandir, Table &amp; Home Decor (Set of 4)</t>
+        </is>
+      </c>
+      <c r="H7" t="n">
+        <v>479</v>
+      </c>
+      <c r="I7" t="n">
+        <v>349</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -8552,108 +8337,66 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Elevate your daily rituals and create a serene ambiance with DeoDap Mixed Floral Fragrance Incense Sticks . Crafted with a delightful mixed floral fragrance, these premium incense sticks are perfect for puja, meditation, and transforming any space into a haven of peace. Experience the traditional essence of India with every light, bringing purity and positive energy to your home or office. Our high-quality Mixed Floral Fragrance Incense Sticks are designed to provide a long-lasting, soothing aroma, making them an essential addition to your spiritual practices and daily life. Whether you&amp;#x27;re seeking to enhance your meditation sessions, perform daily prayers, or simply imbue your living space with a calming and pleasant scent, these Mixed Floral Fragrance Incense Sticks offer an authentic and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+          <t>&lt;p&gt;Add a distinctive devotional touch to your space with these Palm Shape Ganesh Idols. Each piece features Lord Ganesh seated within a hand-shaped frame, enhanced with metallic detailing that gives the idols a refined and traditional appearance. The compact design makes them suitable for home mandirs, pooja shelves, office desks, side tables and festive arrangements. The different metallic accents add variety while maintaining a coordinated overall look. Key Features Unique palm-shaped Ganesh idol design Decorative metallic detailing Elegant white finish Suitable for mandir and pooja setup Compact design for table and shelf placement Ideal for festive and devotional decoration Can be displayed together or separately Quantity: Set of 4&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/13678.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/FxXtgzeQJm.png</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_24bf1e99-6269-4d14-9146-11f188a066c1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ioyZy5nIog.png</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_a9902133-8ea0-48cb-8c2a-7ba6daa65170.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/s9wUTME51k.png</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_22326326-f5ff-440c-85d9-c467647226e7.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/r91BKyN07e.png</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_c66bc375-cb95-4ccd-b52b-bfcc62fb74af.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/zDQ0S1HOvP.png</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_3f05a6a8-c49f-4fa7-9ded-cb9f7296d832_1.jpg</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
-      <c r="AI7" t="inlineStr"/>
-      <c r="AJ7" t="inlineStr"/>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr"/>
-      <c r="AN7" t="inlineStr"/>
-      <c r="AO7" t="inlineStr"/>
-      <c r="AP7" t="inlineStr"/>
-      <c r="AQ7" t="inlineStr"/>
-      <c r="AR7" t="inlineStr"/>
-      <c r="AS7" t="inlineStr"/>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AU7" t="inlineStr"/>
-      <c r="AV7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr"/>
-      <c r="AX7" t="inlineStr"/>
-      <c r="AY7" t="inlineStr"/>
-      <c r="AZ7" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Kc9dgHYt5a.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="51" customHeight="1">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>whl167_48535_7rose_dhoop_stick</t>
+          <t>2234_silver_bajot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7 Rose Dhoop Sticks – Premium Natural Aroma Jar 100g</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+          <t>Aluminium Foil Bajot – Handcrafted Pooja Chowki for Home | Styleva</t>
+        </is>
+      </c>
+      <c r="H8" t="n">
+        <v>500</v>
+      </c>
+      <c r="I8" t="n">
+        <v>219</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -8662,104 +8405,61 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Experience the divine fragrance of 7 Rose Premium Dhoop Sticks, designed to fill your home with a soothing and natural aroma. These dhoop sticks are carefully crafted to provide a long-lasting, calming effect, perfect for meditation, daily prayers, or simply creating a serene and inviting atmosphere in any space. Discover a blend that enhances your well-being and brings a touch of tranquility. Key features Premium Rose Blend: Enjoy a rich, exquisite blend of seven distinct rose fragrances for a delightful sensory experience. Natural Ingredients: Made from pure, plant-based materials, ensuring a gentle and chemical-free aroma for your environment. Long-lasting Fragrance: Our concentrated formula guarantees a prolonged and consistent aroma, enriching your space for hours. Versatile Use: Idea&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+          <t>&lt;p&gt;Elevate your spiritual space and home aesthetics with our exquisite Aluminium Foil Bajot . This beautifully handcrafted pooja chowki is designed to add a touch of traditional elegance to your rituals and interior decor. Perfect for royal weddings, daily pujas, or as a charming accent piece, this versatile patla combines durability with a luxurious finish, making it an essential addition to any Indian home. Key features Luxurious Minakari Design: Adorned with intricate white metal minakari work over aluminium foil, creating a royal and eye-catching appearance. Sturdy Wooden Construction: Built on a solid wooden base for lasting durability and stability. Multipurpose Utility: Ideal for placing deity idols during pooja, sitting comfortably for rituals, or as a decorative stand for plants and&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U8" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr"/>
       <c r="W8" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Sa8igJj280.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/2_bdb9a21a-cd11-4af6-a6c7-f54b76dc16b9.jpg</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/oGJ8yemBtS.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/2234SKUCODE.jpg</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/UMHOY47pQY.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/944879d7-32b1-4582-9b5a-83f6ced20d26.jpg</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ISpdU5ttWo.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/22341.jpg</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/cUllWiugL8.jpg</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
-      <c r="AE8" t="inlineStr"/>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="inlineStr"/>
-      <c r="AH8" t="inlineStr"/>
-      <c r="AI8" t="inlineStr"/>
-      <c r="AJ8" t="inlineStr"/>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr"/>
-      <c r="AN8" t="inlineStr"/>
-      <c r="AO8" t="inlineStr"/>
-      <c r="AP8" t="inlineStr"/>
-      <c r="AQ8" t="inlineStr"/>
-      <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/4_2803ea4c-8890-4014-a2e1-9326a35f17ec.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="51" customHeight="1">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>whl344_41237_danglar_6in1_20gm</t>
+          <t>19675_shubh_labh_wall_hangings_2pc_no7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>6 in 1 Premium Incense Sticks Pouch for Puja, Meditation 6 Fragrance Combo (120 gm)</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>629</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
+          <t>Shubh Labh Wall Hangings – Set of 2 Festive Decorative Pieces</t>
+        </is>
+      </c>
+      <c r="H9" t="n">
+        <v>575</v>
+      </c>
+      <c r="I9" t="n">
+        <v>229</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -8768,108 +8468,66 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Discover our assorted fragrance incense stick pouches, perfect for puja, meditation, and enhancing your home atmosphere. These premium incense sticks offer a delightful combination of six unique fragrances, designed to create a soothing and calming environment. Made from high-quality natural ingredients, they are 100% charcoal-free, ensuring a safe and non-toxic experience for daily use. Key features Set of six assorted fragrances for varied moods Made from natural, high-quality ingredients 100% charcoal-free for safe daily use Low smoke formulation for a cleaner burn Ideal for puja, meditation, yoga, and home fragrance Each pouch contains 90 grams of incense sticks Materials &amp;amp; care Crafted from natural ingredients. Store in a cool, dry place away from direct sunlight and moisture to prese&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
+          <t>&lt;p&gt;Invite prosperity and good fortune into your home with this exquisite Shubh Labh wall hangings set. This vibrant set of two decorative pieces features traditional &amp;quot;Shubh&amp;quot; (auspicious) and &amp;quot;Labh&amp;quot; (profit) inscriptions, beautifully enhanced with shimmering glitter and intricate stonework. Perfect for elevating festive vibes or adding spiritual charm to your living spaces, these lightweight wall hangings instantly bring positivity and traditional Indian elegance. Key features Auspicious inscriptions: Displays &amp;quot;Shubh&amp;quot; and &amp;quot;Labh&amp;quot; symbols, promoting good luck and success. Festive design: Glitter-embellished and stone-studded for an eye-catching decorative appeal. Versatile placement: Ideal for home entrances, pooja rooms, temples, shops, or offices. Lightweight and easy to hang: Quick to install&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U9" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr"/>
       <c r="W9" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/5rKcdMgMe4.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_8e3fcd8e-cfe6-4b3b-ad8e-780f5014fd5d.jpg</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/TULXdJ2Qu3.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/85c9a601-5322-428e-8145-60f1125d9a86.jpg</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/pxQQkWuO10.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_a36c43ec-b2ae-43ae-b6f3-4d0b7379be99.jpg</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4nUvrQmo56.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_65960b96-d73c-4105-a152-bbdaa8429caf.jpg</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/6Rj9FwdJOH.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_a4e5998b-cba0-46cd-99ea-494709aeea51.jpg</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/YNBSkBMZnq.jpg</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr"/>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AU9" t="inlineStr"/>
-      <c r="AV9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr"/>
-      <c r="AX9" t="inlineStr"/>
-      <c r="AY9" t="inlineStr"/>
-      <c r="AZ9" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_a27e5163-97d3-490d-a3e2-80709a0433ce.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="51" customHeight="1">
-      <c r="A10" t="inlineStr"/>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2234_silver_bajot</t>
+          <t>8444_led_iceberg_light_1pc</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Aluminium Foil Bajot – Handcrafted Pooja Chowki for Home | Styleva</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+          <t>Iceberg Night Light – Flameless LED Decor for Home | Indo Glow</t>
+        </is>
+      </c>
+      <c r="H10" t="n">
+        <v>460</v>
+      </c>
+      <c r="I10" t="n">
+        <v>259</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -8878,104 +8536,66 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Elevate your spiritual space and home aesthetics with our exquisite Aluminium Foil Bajot . This beautifully handcrafted pooja chowki is designed to add a touch of traditional elegance to your rituals and interior decor. Perfect for royal weddings, daily pujas, or as a charming accent piece, this versatile patla combines durability with a luxurious finish, making it an essential addition to any Indian home. Key features Luxurious Minakari Design: Adorned with intricate white metal minakari work over aluminium foil, creating a royal and eye-catching appearance. Sturdy Wooden Construction: Built on a solid wooden base for lasting durability and stability. Multipurpose Utility: Ideal for placing deity idols during pooja, sitting comfortably for rituals, or as a decorative stand for plants and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr"/>
-      <c r="R10" t="inlineStr"/>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
+          <t>&lt;p&gt;Transform your living space with the enchanting LED light-up clear iceberg decor from Indo Glow. This modern and unique flameless LED lamp creates a serene ambiance, perfect for any room. Ideal for bedroom decor, festive celebrations like Diwali, or as a thoughtful gift, its captivating iceberg design adds a touch of contemporary elegance without the hazards of traditional candles. Experience the perfect blend of style and safety with our innovative LED light-up clear iceberg decor. Powered by energy-efficient LEDs, it offers a gentle, calming glow that enhances your home&amp;#x27;s atmosphere. Whether you&amp;#x27;re looking to create a cozy reading nook, a tranquil bedroom sanctuary, or a festive display for special occasions, this versatile night light is an excellent choice. Its compact size makes it a&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U10" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr"/>
       <c r="W10" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/2_bdb9a21a-cd11-4af6-a6c7-f54b76dc16b9.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/8444_led_iceberg_light_1pc.jpg</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/2234SKUCODE.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/0ee593c4-95b9-4def-87cf-594eb2310c96.jpg</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/944879d7-32b1-4582-9b5a-83f6ced20d26.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/19417.png</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/22341.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/19418.png</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/4_2803ea4c-8890-4014-a2e1-9326a35f17ec.jpg</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
-      <c r="AE10" t="inlineStr"/>
-      <c r="AF10" t="inlineStr"/>
-      <c r="AG10" t="inlineStr"/>
-      <c r="AH10" t="inlineStr"/>
-      <c r="AI10" t="inlineStr"/>
-      <c r="AJ10" t="inlineStr"/>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr"/>
-      <c r="AM10" t="inlineStr"/>
-      <c r="AN10" t="inlineStr"/>
-      <c r="AO10" t="inlineStr"/>
-      <c r="AP10" t="inlineStr"/>
-      <c r="AQ10" t="inlineStr"/>
-      <c r="AR10" t="inlineStr"/>
-      <c r="AS10" t="inlineStr"/>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AU10" t="inlineStr"/>
-      <c r="AV10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr"/>
-      <c r="AX10" t="inlineStr"/>
-      <c r="AY10" t="inlineStr"/>
-      <c r="AZ10" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/011_8d4ae56c-5560-44b2-8f46-e4f7fefbdcb2.jpg</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/2092621834.png</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="51" customHeight="1">
-      <c r="A11" t="inlineStr"/>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>whl167_48553_gugalam_agarbatti_250g</t>
+          <t>whl167_48605_handcrafted_tulsi_diya_4pc</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Agarbatti Incense Sticks – Premium Natural Fragrance 250g Jar</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+          <t>Handcrafted Tulsi Kiyaro Diya Set – Festive Clay Oil Lamps with Swastik &amp; Shree</t>
+        </is>
+      </c>
+      <c r="H11" t="n">
+        <v>459</v>
+      </c>
+      <c r="I11" t="n">
+        <v>299</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -8984,104 +8604,61 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Experience the calming aroma of Gugalam Premium Guggal Agarbatti incense sticks , designed to create a soothing ambiance for your home, meditation, or pooja rituals. Crafted with natural ingredients, these premium Guggal agarbatti sticks ensure a pure and long-lasting fragrance, turning any space into a tranquil sanctuary. Perfect for daily use, these incense sticks enhance your spiritual practices and uplift your mood. Key features Made from natural wood powders, aromatic herbs, resins, and essential oils Emits a soft, calming, and long-lasting Guggal fragrance Convenient 250 gram jar packaging for easy storage and use Ideal for yoga, meditation, pooja, and enhancing home or office atmosphere Ready-to-use bamboo sticks that burn evenly and cleanly Materials &amp; care The Gugalam Premium Gugg</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr"/>
-      <c r="R11" t="inlineStr"/>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
+          <t>&lt;p&gt;Celebrate your festivals with the Handcrafted Tulsi Kiyaro Diya Set, a perfect blend of tradition and vibrant decor. These clay oil lamps, adorned with sacred Swastik and Shree symbols, bring divine positivity and an auspicious atmosphere to your home. Ideal for Diwali, Navratri, Ganesh Chaturthi, weddings, and daily pooja rituals, these square-shaped diyas are a beautiful spiritual addition to your festive decor. Key features Hand-painted square diyas featuring sacred Hindu symbols like Swastik and Shree for spiritual significance. Made from high-quality clay that enhances traditional authenticity and durability. Multi-color palette including red, green, purple, and orange to brighten your festive ambiance. Compatible with oil, ghee, or tealight candles for versatile use. Eco-friendly and&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U11" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr"/>
       <c r="W11" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Q9edm4uwBM.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/cisTqUbngf.jpg</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/O1tOwoVvBg.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ae6zk3JnnF.jpg</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/G6UsAS6SC8.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/10ax8Rhryi.jpg</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PdvIil1z5L.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/pDAthNJ4UE.jpg</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/YV3joKomOc.jpg</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
-      <c r="AE11" t="inlineStr"/>
-      <c r="AF11" t="inlineStr"/>
-      <c r="AG11" t="inlineStr"/>
-      <c r="AH11" t="inlineStr"/>
-      <c r="AI11" t="inlineStr"/>
-      <c r="AJ11" t="inlineStr"/>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr"/>
-      <c r="AM11" t="inlineStr"/>
-      <c r="AN11" t="inlineStr"/>
-      <c r="AO11" t="inlineStr"/>
-      <c r="AP11" t="inlineStr"/>
-      <c r="AQ11" t="inlineStr"/>
-      <c r="AR11" t="inlineStr"/>
-      <c r="AS11" t="inlineStr"/>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AU11" t="inlineStr"/>
-      <c r="AV11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr"/>
-      <c r="AX11" t="inlineStr"/>
-      <c r="AY11" t="inlineStr"/>
-      <c r="AZ11" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/pZtERD6xxD.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="51" customHeight="1">
-      <c r="A12" t="inlineStr"/>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>whl190_64539_chesse_tomato_soya_mini_120</t>
+          <t>whl202_67906_diya_flower_5l_red</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cheese Tomato Soya Mini Premium High Protein Roasted Crunchy Tasty Soya Bites (120g)</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
+          <t>Flower 5-Step Decorative Diya – Multi-Purpose Eco-Friendly Holder</t>
+        </is>
+      </c>
+      <c r="H12" t="n">
+        <v>480</v>
+      </c>
+      <c r="I12" t="n">
+        <v>249</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -9090,108 +8667,66 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Festive &amp; Lights</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>Experience the delicious crunch and high protein content of Oracle Soya Mini Cheese Tomato snacks. These savory bites are tossed in a tangy cheese and tomato seasoning, making them a perfect healthy snack option for any time of the day. Made from wholesome soya, these non-fried snacks are ideal for those looking for a nutritious snack without compromising on flavor. Key features Crunchy, high-protein soya bites in cheese &amp; tomato seasoning Tangy, cheesy, and irresistibly flavorful Rich in plant-based protein and non-fried for healthier snacking Ingredients include: soya, edible vegetable oil, cheese &amp; tomato seasoning, salt, spices Net Weight: 120 g, Best Before: 6 months from production date Perfect for kids' lunchboxes, parties, tea-time, and festive snacking Materials &amp; care Store in a</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+          <t>&lt;p&gt;Enhance your home ambiance with the Flower 5-Step Decorative Diya, a versatile eco-friendly gypsum holder perfect for pooja rituals, festive lighting, or stylish decor. This multi-purpose diya blends traditional charm with modern functionality to illuminate your space with warmth and serenity. Key features Crafted from premium-quality, non-toxic, and durable gypsum, ensuring an eco-friendly product Intricately handcrafted lotus flower design symbolizing purity and peace Multi-use as a diya, tealight candle holder, dhoop cone stand, mini planter, or creative craft base Elegant and smooth finish complements pooja rooms, offices, living areas, and festive decorations Perfect for Diwali, Navratri, weddings, housewarmings, and gifting Customizable surface — easily painted or decorated to suit y&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U12" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V12" t="inlineStr"/>
       <c r="W12" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_3787a688-ce49-4def-8685-98c34abb86b8.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/mOff8nPgzy.png</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_c60e561b-38db-4acf-babb-3e264718513f.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/b456Ff1Wkc.png</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_a558b319-b415-4d6a-b9fe-3491d9142853.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/uLHCbmbvTd.png</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_d7400fee-bbd2-4a37-8795-c9609de6799a.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ZgWdJBsnmE.png</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_3b06ee0c-c2fe-4190-b426-1b0183dae827.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/vju4NtPzlL.png</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_9fe557c9-cbb4-4907-8059-798bf675d3cb.jpg</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
-      <c r="AE12" t="inlineStr"/>
-      <c r="AF12" t="inlineStr"/>
-      <c r="AG12" t="inlineStr"/>
-      <c r="AH12" t="inlineStr"/>
-      <c r="AI12" t="inlineStr"/>
-      <c r="AJ12" t="inlineStr"/>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr"/>
-      <c r="AM12" t="inlineStr"/>
-      <c r="AN12" t="inlineStr"/>
-      <c r="AO12" t="inlineStr"/>
-      <c r="AP12" t="inlineStr"/>
-      <c r="AQ12" t="inlineStr"/>
-      <c r="AR12" t="inlineStr"/>
-      <c r="AS12" t="inlineStr"/>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AU12" t="inlineStr"/>
-      <c r="AV12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr"/>
-      <c r="AX12" t="inlineStr"/>
-      <c r="AY12" t="inlineStr"/>
-      <c r="AZ12" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/x1aApIbqsH.png</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="51" customHeight="1">
-      <c r="A13" t="inlineStr"/>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>7928_2in1_cleaning_brush</t>
+          <t>10314_ss_kitchen_veg_n_friut_grater</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2 in 1 Floor Cleaning Brush with Wiper and Long Handle (1 Pc)</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
+          <t>Stainless Steel Cheese Grater – Multi-Purpose Kitchen Tool | CookAura</t>
+        </is>
+      </c>
+      <c r="H13" t="n">
+        <v>550</v>
+      </c>
+      <c r="I13" t="n">
+        <v>229</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -9200,108 +8735,66 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Clean your home effortlessly with this versatile 2 in 1 floor cleaning brush with squeegee and long handle. This innovative tool combines scrubbing and wiping functions, making bathroom and home cleaning quicker and more efficient. Say goodbye to bending and squatting, as this brush allows you to clean standing up, protecting your knees and back from strain. Key features Scrub and wipe with one tool, no changing over mid-job. Done standing up, no bending or squatting on wet tiles. Stiff bristles effectively clean tile grout and corners. Rubber squeegee pulls water out in one smooth pass. Durable stainless steel handle withstands pressure without flexing. Long reach for under sinks and behind commodes. Rinses clean easily under a tap and stands to air dry. Also suitable for balconies, terra&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+          <t>&lt;p&gt;Elevate your culinary experience with the CookAura Stainless Steel Cheese Grater , an essential multi-purpose tool for every Indian kitchen. This versatile grater is designed to make food preparation quicker, easier, and more efficient, whether you&amp;#x27;re grating hard cheeses, shredding fresh vegetables, or zesting citrus fruits. Its durable construction and ergonomic design ensure a comfortable grip and superior performance for all your grating needs. Crafted from high-quality stainless steel, this kitchen essential promises long-lasting sharpness and resistance to rust, making it a reliable companion for years to come. From ginger and garlic to chocolate and potatoes, this efficient kitchen tool handles a wide array of ingredients with ease. Its compact design also ensures it won&amp;#x27;t take up m&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U13" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V13" t="inlineStr"/>
       <c r="W13" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Cleaning_Brush_2.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_b3320453-ee8d-4bf5-b0ea-623fe797673d.jpg</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/7928.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_cd98e4a7-fd75-4603-8071-6ab9c25a5b02.jpg</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Cleaning_Brush_3.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_dcc8733f-c840-45a9-8f09-c98c74856e3d.jpg</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Cleaning_Brush_5.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_07060837-ddc5-4743-b877-f8f3a50a3c73.jpg</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Cleaning_Brush_4.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_c8bec7f9-6ccb-41a1-b3df-59122766b82b.jpg</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Cleaning_Brush_6.jpg</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
-      <c r="AE13" t="inlineStr"/>
-      <c r="AF13" t="inlineStr"/>
-      <c r="AG13" t="inlineStr"/>
-      <c r="AH13" t="inlineStr"/>
-      <c r="AI13" t="inlineStr"/>
-      <c r="AJ13" t="inlineStr"/>
-      <c r="AK13" t="inlineStr"/>
-      <c r="AL13" t="inlineStr"/>
-      <c r="AM13" t="inlineStr"/>
-      <c r="AN13" t="inlineStr"/>
-      <c r="AO13" t="inlineStr"/>
-      <c r="AP13" t="inlineStr"/>
-      <c r="AQ13" t="inlineStr"/>
-      <c r="AR13" t="inlineStr"/>
-      <c r="AS13" t="inlineStr"/>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AU13" t="inlineStr"/>
-      <c r="AV13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr"/>
-      <c r="AX13" t="inlineStr"/>
-      <c r="AY13" t="inlineStr"/>
-      <c r="AZ13" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_e6461edb-bfed-45f3-87cb-42e6adc0fb96.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="51" customHeight="1">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2856_pla_manual_lemon_squeezer</t>
+          <t>2996_round_sili_strainer_1pc_no1</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2-in-1 Lemon Squeezer – Plastic &amp; Bottle Opener | Quickslice</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+          <t>Silicone Collapsible Strainer – Space-Saving Kitchen Tool for Easy Draining</t>
+        </is>
+      </c>
+      <c r="H14" t="n">
+        <v>519</v>
+      </c>
+      <c r="I14" t="n">
+        <v>319</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -9310,108 +8803,66 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Say goodbye to sticky hands and wasted juice with the versatile 2-in-1 Lemon Squeezer from Quickslice. This ingenious kitchen tool is designed to make juicing lemons and limes effortless, while also serving as a convenient bottle opener. Crafted from high-quality, durable plastic, it ensures you get every last drop of fresh citrus juice without pulp or seeds, enhancing your cooking and beverages in a jiffy. Whether you&amp;#x27;re making refreshing lemonade or adding a zesty touch to your dishes, this manual plastic juicer is a must-have for every Indian kitchen. Key features Dual Functionality: Enjoy the convenience of this 2-in-1 lemon squeezer , offering a powerful citrus juicer and a reliable bottle opener in one compact kitchen tool. Efficient Juicing: Designed to extract maximum juice from le&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+          <t>&lt;p&gt;The silicone collapsible strainer is an essential kitchen accessory that simplifies draining and rinsing tasks. Its flexible, food-grade silicone body folds flat, allowing for compact storage while providing a sturdy, reliable strainer when needed. Designed for versatile use, this collapsible colander is perfect for washing fruits, vegetables, and rice, as well as draining pasta, noodles, and boiled foods. Its lightweight construction and easy-clean surface make it an ideal tool for busy kitchens, outdoor cooking, or travel. Key features Collapsible design folds flat for space-efficient storage Made of durable, food-grade silicone material Fine drain holes for quick, mess-free draining Comfortable side handles for secure grip Sturdy structure when popped up for rinsing Suitable for washing&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V14" t="inlineStr"/>
       <c r="W14" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/08_d17aa0e0-d3fa-4355-805d-3d7234dc72de.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-1.jpg</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_c5c5a28d-e52e-4e1e-8b0c-68bca9a69607.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_52a6813f-0bcb-4dd1-9fcc-48c2d3628c0f.jpg</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_2024-05-20T06_09_15.529Z.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-3.jpg</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_2024-05-20T08_17_42.303Z.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-4.jpg</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/07_f66eb85e-9a97-4c5e-b456-20c82b83b277.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-7.jpg</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/05_e4c6da89-6df8-42a1-8f8f-0f4ccd46b458.jpg</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr"/>
-      <c r="AE14" t="inlineStr"/>
-      <c r="AF14" t="inlineStr"/>
-      <c r="AG14" t="inlineStr"/>
-      <c r="AH14" t="inlineStr"/>
-      <c r="AI14" t="inlineStr"/>
-      <c r="AJ14" t="inlineStr"/>
-      <c r="AK14" t="inlineStr"/>
-      <c r="AL14" t="inlineStr"/>
-      <c r="AM14" t="inlineStr"/>
-      <c r="AN14" t="inlineStr"/>
-      <c r="AO14" t="inlineStr"/>
-      <c r="AP14" t="inlineStr"/>
-      <c r="AQ14" t="inlineStr"/>
-      <c r="AR14" t="inlineStr"/>
-      <c r="AS14" t="inlineStr"/>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AU14" t="inlineStr"/>
-      <c r="AV14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr"/>
-      <c r="AX14" t="inlineStr"/>
-      <c r="AY14" t="inlineStr"/>
-      <c r="AZ14" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="51" customHeight="1">
-      <c r="A15" t="inlineStr"/>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
       <c r="F15" t="inlineStr">
         <is>
-          <t>19251_2in1_towel_hanger_n_soap_stand_1pc</t>
+          <t>11401_plastic_gas_stove_burner_cover_10p</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2-in-1 Bathroom Organizer – Self-Adhesive Soap Holder &amp; Towel Rack</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
+          <t>Plastic Gas Stove Burner Cover Liners for Kitchen Cleaning and Hygiene (10 Pc)</t>
+        </is>
+      </c>
+      <c r="H15" t="n">
+        <v>480</v>
+      </c>
+      <c r="I15" t="n">
+        <v>349</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -9420,108 +8871,66 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Discover convenient space-saving with our 2-in-1 foldable sink strainer and soap holder, perfect for keeping your kitchen or bathroom tidy. This dual-purpose unit combines functionality with a stylish, compact design. Key features Multi-functional Design: Combines a sink strainer with a soap holder to keep essentials organized and accessible. Foldable &amp;amp; Space-Saving: Efficiently utilizes space, ideal for small kitchens or bathrooms. Durable ABS Material: Crafted from high-quality, water-resistant plastic for long-lasting use without rust. Easy Installation: Simple, no-drill mounting on smooth surfaces for immediate use. Modern Aesthetic: Elegant green and gold accents complement any kitchen or bathroom décor. Versatile Use: Perfect for holding soap, sponges, and straining food waste in the&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+          <t>&lt;p&gt;Disposable Plastic Gas Stove Burner Cover Liners with Raised Edges for Catching Oil, Food Spills and Cooking Residue Around Kitchen Burners (10 Pc) Description :- These gas stove burner cover liners help keep the cooking area cleaner by collecting oil splashes, food spills and residue around the burner. Their round open-center design fits around compatible stove burners and supports quicker cleanup during regular kitchen use. Key Features :- Open-center design fits around compatible gas burners Raised edges help contain spills and cooking residue Protective liner reduces direct mess on the stove surface Lightweight construction allows convenient placement Round shape provides practical burner-area coverage Disposable format supports quick cleanup after use Stackable design allows compact k&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U15" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V15" t="inlineStr"/>
       <c r="W15" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/19251_2in1_towel_hanger_n_soap_stand_1pc.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-1.jpg</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/WhatsAppImage2025-05-21at12.09.36.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-2.jpg</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_f1b2377a-ccf3-4194-9ff3-f812e3766f74.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-3.jpg</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_52db06b2-06d3-42f2-a190-1fbc55591537.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-4.jpg</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_18f76d35-82b2-4396-9de9-76cf8283ef30.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-5.jpg</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_7f993c3f-2bba-4f4b-8550-56abb194cd7c.jpg</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr"/>
-      <c r="AE15" t="inlineStr"/>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="inlineStr"/>
-      <c r="AH15" t="inlineStr"/>
-      <c r="AI15" t="inlineStr"/>
-      <c r="AJ15" t="inlineStr"/>
-      <c r="AK15" t="inlineStr"/>
-      <c r="AL15" t="inlineStr"/>
-      <c r="AM15" t="inlineStr"/>
-      <c r="AN15" t="inlineStr"/>
-      <c r="AO15" t="inlineStr"/>
-      <c r="AP15" t="inlineStr"/>
-      <c r="AQ15" t="inlineStr"/>
-      <c r="AR15" t="inlineStr"/>
-      <c r="AS15" t="inlineStr"/>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AU15" t="inlineStr"/>
-      <c r="AV15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr"/>
-      <c r="AX15" t="inlineStr"/>
-      <c r="AY15" t="inlineStr"/>
-      <c r="AZ15" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="16" ht="51" customHeight="1">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>23897_2in1_lint_remover</t>
+          <t>5871_soup_spoon_long_handle</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2-in-1 Portable Pet Hair and Lint Remover Brush for Clothes and Furniture</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
+          <t>Silicone Soup Spoon – Multifunctional Strainer &amp; Ladle | Quickslice</t>
+        </is>
+      </c>
+      <c r="H16" t="n">
+        <v>595</v>
+      </c>
+      <c r="I16" t="n">
+        <v>229</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -9530,108 +8939,66 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Keep your home and wardrobe free from unwanted pet hair and lint with our efficient 2-in-1 portable pet hair and lint remover. This dual-sided fabric cleaning tool is designed to easily tackle fuzz, fur, and loose fibres from various surfaces, ensuring your clothes and furniture look pristine. Its manual operation makes it a convenient and eco-friendly solution for everyday fabric care. Key features 2-in-1 dual-surface design for versatile fabric cleaning Textured brush side effectively loosens and lifts pet hair and surface lint Scraping edge efficiently gathers fuzz and loose fibres Reusable construction eliminates the need for disposable adhesive sheets Wide cleaning roller covers fabric surfaces quickly and effectively Comfortable ribbed handle provides a secure and ergonomic grip Manu&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr"/>
-      <c r="R16" t="inlineStr"/>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr"/>
+          <t>&lt;p&gt;Elevate your Indian kitchen experience with our premium Silicone Soup Spoon , designed for both efficiency and durability. This versatile kitchen tool is perfect for effortlessly serving soups, gravies, and stews, while its integrated straining function makes it ideal for separating liquids from solids. Crafted from high-quality, food-grade silicone with a robust stainless steel core, this long handle spoon ensures a comfortable grip and safe use on all types of cookware, including delicate non-stick surfaces. Say goodbye to scratched pots and hello to seamless cooking with Quickslice. Key features Food-Grade Silicone: Made from premium, BPA-free, and heat-resistant silicone, ensuring safety and longevity in your kitchen. Integrated Strainer: Cleverly designed with a perforated head, allow&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U16" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23897-2in1-lint-remover-01.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/5871_soup_spoon_long_handle.jpg</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23897-2in1-lint-remover-sku.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/0ed09443-014e-4d3b-9487-75d14c668891_8053bb08-02de-45ca-8639-b2465cfb357a.jpg</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23897-2in1-lint-remover-02.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_88bfeeeb-59ec-4b83-972a-5c0f071e922c.jpg</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23897-2in1-lint-remover-03.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_2056ab04-47f2-45bd-959c-cb027f30e827.jpg</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23897-2in1-lint-remover-white.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_faae6e8c-cf16-4787-9417-9702bb7038d0.jpg</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23897-2in1-lint-remover-size.jpg</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr"/>
-      <c r="AE16" t="inlineStr"/>
-      <c r="AF16" t="inlineStr"/>
-      <c r="AG16" t="inlineStr"/>
-      <c r="AH16" t="inlineStr"/>
-      <c r="AI16" t="inlineStr"/>
-      <c r="AJ16" t="inlineStr"/>
-      <c r="AK16" t="inlineStr"/>
-      <c r="AL16" t="inlineStr"/>
-      <c r="AM16" t="inlineStr"/>
-      <c r="AN16" t="inlineStr"/>
-      <c r="AO16" t="inlineStr"/>
-      <c r="AP16" t="inlineStr"/>
-      <c r="AQ16" t="inlineStr"/>
-      <c r="AR16" t="inlineStr"/>
-      <c r="AS16" t="inlineStr"/>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AU16" t="inlineStr"/>
-      <c r="AV16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr"/>
-      <c r="AX16" t="inlineStr"/>
-      <c r="AY16" t="inlineStr"/>
-      <c r="AZ16" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_e328dddc-891e-47d3-b5a2-77d55b9dd450.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="51" customHeight="1">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>whl182_41470_2in1_angle_cock_plastic_tap</t>
+          <t>whl282_21022_cute_teddy_bear_kids_water_</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2-in-1 Plastic Bib Cock Water Tap – Dual Outlet, Leak-Proof ABS Faucet</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
+          <t>Kids Water Bottle – Cartoon Bear Shape with Straw &amp; Strap</t>
+        </is>
+      </c>
+      <c r="H17" t="n">
+        <v>465</v>
+      </c>
+      <c r="I17" t="n">
+        <v>269</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -9640,104 +9007,66 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>&lt;p&gt;The 2-in-1 plastic bib cock water tap offers dual outlet functionality, allowing independent water flow control from two separate knobs. Crafted from premium ABS plastic, this wall-mounted water tap is ideal for bathrooms, utility areas, and washing machine connections, combining durability and leak-proof performance. Key features Dual Outlet Design: Two faucets operated by separate knobs for efficient water distribution. ABS Plastic Build: Rust-resistant, strong, and long-lasting material ensures durability. Leak-Proof Mechanism: Secure threading and internal washers prevent drips and water wastage. Ergonomic Controls: Smooth, easy-to-turn knobs for precise water flow regulation. Wall-Mounted Installation: Fits standard ½ inch pipe threads effortlessly. Multipurpose Use: Suitable for wash&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr"/>
-      <c r="R17" t="inlineStr"/>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr"/>
+          <t>&lt;p&gt;Kids water bottle designed with a cute cartoon bear shape, featuring a built-in straw and shoulder strap to make hydration fun and easy for children. This kids water bottle encourages regular drinking with its leakproof flip-lock lid and transparent body to monitor water levels. Key features Fun cartoon bear design tailored for kids Convenient built-in straw for easy sipping Leakproof flip-lock lid prevents spills and leaks Adjustable shoulder strap for hands-free carrying Transparent body to easily check remaining water Lightweight and safe edges suitable for children Encourages kids to drink water regularly Perfect for school, travel, and outdoor activities Materials &amp;amp; care Made from high-quality plastic materials, this water bottle is easy to clean and maintain. Hand wash recommended to&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U17" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V17" t="inlineStr"/>
       <c r="W17" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/UpHQk9SQR4.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Bottle-01_8f4648a9-b2f8-43d1-9988-fe2d06cd44b5.jpg</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/cMt9NIGgHS.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/8548082b-cecd-4ecc-a779-d0e2094031b7.jpg</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/lDBTCEMbwq.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Bottle-04_a6b8d7f6-d411-461a-8ad2-075562f1f480.jpg</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Zwly1fEysc.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/21022_cute_teddy_bear_kids_water_bottle_1pc.jpg</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/rO6YFG2olf.jpg</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr"/>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr"/>
-      <c r="AE17" t="inlineStr"/>
-      <c r="AF17" t="inlineStr"/>
-      <c r="AG17" t="inlineStr"/>
-      <c r="AH17" t="inlineStr"/>
-      <c r="AI17" t="inlineStr"/>
-      <c r="AJ17" t="inlineStr"/>
-      <c r="AK17" t="inlineStr"/>
-      <c r="AL17" t="inlineStr"/>
-      <c r="AM17" t="inlineStr"/>
-      <c r="AN17" t="inlineStr"/>
-      <c r="AO17" t="inlineStr"/>
-      <c r="AP17" t="inlineStr"/>
-      <c r="AQ17" t="inlineStr"/>
-      <c r="AR17" t="inlineStr"/>
-      <c r="AS17" t="inlineStr"/>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AU17" t="inlineStr"/>
-      <c r="AV17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr"/>
-      <c r="AX17" t="inlineStr"/>
-      <c r="AY17" t="inlineStr"/>
-      <c r="AZ17" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Bottle-05_79b91998-a4bf-4012-8ff4-a41f7297f602.jpg</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Bottle-06_81ae6ef2-c4f1-42a0-a098-64e3de016b31.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="51" customHeight="1">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>13314_2in1_multi_clea_clip_brush_1pc</t>
+          <t>5834_3in1_chopping_board_peeler_knife_se</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2-in-1 Multipurpose Cleaning Brush – Ergonomic Handle for Easy Cleaning</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>480</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+          <t>Kitchen Knife Set – 3 in 1 Knife, Chopping Board &amp; Peeler</t>
+        </is>
+      </c>
+      <c r="H18" t="n">
+        <v>460</v>
+      </c>
+      <c r="I18" t="n">
+        <v>269</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -9746,108 +9075,66 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>&lt;p&gt;The 2-in-1 Multipurpose Cleaning Brush is designed to make your household cleaning effortless and efficient. Its ergonomic handle ensures comfortable grip during extended use, while the strong bristles tackle dirt, grime, and stains across various surfaces. Perfect for cleaning tile joints, kitchen sinks, floors, and narrow spaces, this versatile brush simplifies deep cleaning tasks for every home. Key features Dual-purpose design for cleaning different surfaces Durable bristles remove tough dirt and stains Ergonomic handle for comfortable grip and control Suitable for wet and dry cleaning tasks Lightweight and easy to maneuver Ideal for cleaning tile gaps, sinks, floors, and narrow corners Materials &amp;amp; care Crafted from high-quality plastic and durable bristles, this cleaning brush require&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr"/>
+          <t>&lt;p&gt;Experience the convenience of our Kitchen Knife Set, a versatile 3 in 1 solution featuring a sharp kitchen knife, sturdy chopping board, and an efficient vegetable peeler. Designed for easy and safe food prep, this set is perfect for slicing, chopping, and peeling fruits and vegetables effortlessly. Key features Includes a sharp kitchen knife for precise cutting Durable chopping board offering a stable, hygienic surface Vegetable peeler that makes peeling quick and easy Compact and lightweight design ideal for daily cooking Easy to clean and maintain for long-lasting use Perfect for home cooks and professional chefs alike FAQ Q1: What does the Kitchen Knife Set include? A: The set includes a sharp knife, a sturdy chopping board, and a vegetable peeler. Q2: Is this set suitable for daily us&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U18" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V18" t="inlineStr"/>
       <c r="W18" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01florcelner.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/36_chopping-board.jpg</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/09-flor-celner.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_e97e52a4-ffc2-403f-b1f1-0a43a08c732b.jpg</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04florcelner.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/35_chopping-board.jpg</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05florcelner.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/38_chopping-board.jpg</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03florcelner.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/39_chopping-board.jpg</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07florcelner.jpg</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr"/>
-      <c r="AE18" t="inlineStr"/>
-      <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr"/>
-      <c r="AH18" t="inlineStr"/>
-      <c r="AI18" t="inlineStr"/>
-      <c r="AJ18" t="inlineStr"/>
-      <c r="AK18" t="inlineStr"/>
-      <c r="AL18" t="inlineStr"/>
-      <c r="AM18" t="inlineStr"/>
-      <c r="AN18" t="inlineStr"/>
-      <c r="AO18" t="inlineStr"/>
-      <c r="AP18" t="inlineStr"/>
-      <c r="AQ18" t="inlineStr"/>
-      <c r="AR18" t="inlineStr"/>
-      <c r="AS18" t="inlineStr"/>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AU18" t="inlineStr"/>
-      <c r="AV18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr"/>
-      <c r="AX18" t="inlineStr"/>
-      <c r="AY18" t="inlineStr"/>
-      <c r="AZ18" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/43_chopping-board.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="51" customHeight="1">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>5865_multifunction_grinding_machine</t>
+          <t>10595_supermom_full_round_pincer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2-in-1 Manual Citrus Juicer &amp; Grinder – Portable &amp; Easy to Use</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
+          <t>Stainless Steel Full Round Kitchen Pincer – Heavy Duty Grip</t>
+        </is>
+      </c>
+      <c r="H19" t="n">
+        <v>485</v>
+      </c>
+      <c r="I19" t="n">
+        <v>329</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -9856,108 +9143,66 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>&lt;p&gt;The yellow plastic manual food grinder is your essential kitchen companion for effortlessly preparing ingredients. Designed for convenience and portability, this versatile manual food grinder allows you to easily grind ginger, garlic, and other vegetables. Made from food-grade, BPA-free ABS plastic, it ensures no unwanted odors or flavors, keeping your food safe and pure while providing a durable solution for your daily cooking needs. Key features Multi-functional device for grinding ginger, garlic, and vegetables Portable, manual operation ideal for home, outdoor, camping, and travel use Made from durable, BPA-free plastic that is easy to clean Compact design with rotatable lid and modified blades for effortless food preparation Lightweight and easy to store, perfect for small kitchens an&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr"/>
-      <c r="R19" t="inlineStr"/>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr"/>
+          <t>&lt;p&gt;The stainless steel full round kitchen pincer offers heavy-duty, rust-resistant performance for safely handling hot cookware in any kitchen setting. Crafted from premium stainless steel, this kitchen pincer delivers unmatched durability and heat resistance, making it ideal for lifting and moving hot utensils like pressure cooker lids, kadhai, and tandoor grillware without risking burns. Its full round gripping ends provide a secure, slip-resistant hold, increasing safety and control with every use. Key features Made from premium stainless steel ensuring rust and corrosion resistance Full round gripping ends for firm, secure handling of hot cookware Ergonomic, slip-resistant handle for comfortable grip during extended use Heavy-duty construction supports lifting heavy pots and pans with eas&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U19" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V19" t="inlineStr"/>
       <c r="W19" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/5865_multifunction_grinding_machine.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/10595.png</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/71805f9a-3815-4cf3-936f-ab1c53f021c2.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_2b373ef3-c1de-43b4-8a05-afe9d3c70f0e.jpg</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_7e66daf0-9a3f-41a2-bda1-d9c66067d7fd.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_2cc68044-cd07-47c6-afc6-da5ce039f4b3.jpg</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_5d64bbf7-4962-4403-9f67-c7feb3983edc.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_f817ef22-e426-45b7-b8ed-73be3d1d2eec.jpg</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_cfaf27b2-3507-4e92-971b-fd8d95f3ce01.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_488e2cd9-49dc-4aed-9de6-cb7433861b80.jpg</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_e87013a0-0716-48d8-b2d9-a02cfa908ee3.jpg</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr"/>
-      <c r="AE19" t="inlineStr"/>
-      <c r="AF19" t="inlineStr"/>
-      <c r="AG19" t="inlineStr"/>
-      <c r="AH19" t="inlineStr"/>
-      <c r="AI19" t="inlineStr"/>
-      <c r="AJ19" t="inlineStr"/>
-      <c r="AK19" t="inlineStr"/>
-      <c r="AL19" t="inlineStr"/>
-      <c r="AM19" t="inlineStr"/>
-      <c r="AN19" t="inlineStr"/>
-      <c r="AO19" t="inlineStr"/>
-      <c r="AP19" t="inlineStr"/>
-      <c r="AQ19" t="inlineStr"/>
-      <c r="AR19" t="inlineStr"/>
-      <c r="AS19" t="inlineStr"/>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AU19" t="inlineStr"/>
-      <c r="AV19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr"/>
-      <c r="AX19" t="inlineStr"/>
-      <c r="AY19" t="inlineStr"/>
-      <c r="AZ19" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_9ac277ac-4dd4-43c7-96cc-ecdd7bb572a6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="51" customHeight="1">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>11272_plastic_colander_basket_with_bowl</t>
+          <t>10597_supermom_spring_o_masher</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2-in-1 Vegetable Washing Bowl – Effortless Rinsing &amp; Draining</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>435</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
+          <t>Stainless Steel Potato Masher – Heavy Duty with Comfortable Grip</t>
+        </is>
+      </c>
+      <c r="H20" t="n">
+        <v>529</v>
+      </c>
+      <c r="I20" t="n">
+        <v>349</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -9966,108 +9211,66 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>This 2-in-1 vegetable washing bowl is your essential kitchen tool for quick and hygienic food preparation. Designed with a built-in strainer, it simplifies rinsing, draining, and cleaning fruits, vegetables, and salads. The ergonomic handle offers a comfortable grip, making it easy to control and pour. Made from durable, lightweight plastic, this multipurpose kitchen accessory is perfect for daily use and helps maintain food hygiene effortlessly. Key features Dual-purpose bowl and strainer for versatile kitchen tasks Built-in handle for easy gripping and controlled pouring Ideal for washing, rinsing, and draining produce Made from durable, lightweight plastic for everyday use Easy to clean and maintain with simple hand wash Materials &amp; care Constructed from high-quality plastic, designed f</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr"/>
+          <t>&lt;p&gt;The stainless steel potato masher is a heavy-duty kitchen essential designed for effortless mashing of vegetables, potatoes, and fruits. Featuring a robust spring design and ergonomic non-slip handle, this masher ensures smooth, even pressure for the perfect mash every time. Whether preparing mashed potatoes, pav bhaji, soups, or baby food, this kitchen masher delivers reliable performance for home cooks and professionals alike. Key features Durable stainless steel spring design offers long-lasting strength and efficient mashing. Ergonomic handle with a comfortable, non-slip grip for ease of use and better control. Perfect for mashing potatoes, vegetables, fruits, pav bhaji, soups, and baby food. Easy to clean and maintain for everyday kitchen tasks. Compact, lightweight design allows conv&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U20" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V20" t="inlineStr"/>
       <c r="W20" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08-Vegetable-Basket.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-01.jpg</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04VegetableBasket.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_88888870-0e35-41de-9966-35da992a8f27.jpg</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01-Vegetable-Basket.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-02.jpg</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05VegetableBasket.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-03.jpg</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03VegetableBasket.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-05.jpg</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07VegetableBasket.jpg</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr"/>
-      <c r="AE20" t="inlineStr"/>
-      <c r="AF20" t="inlineStr"/>
-      <c r="AG20" t="inlineStr"/>
-      <c r="AH20" t="inlineStr"/>
-      <c r="AI20" t="inlineStr"/>
-      <c r="AJ20" t="inlineStr"/>
-      <c r="AK20" t="inlineStr"/>
-      <c r="AL20" t="inlineStr"/>
-      <c r="AM20" t="inlineStr"/>
-      <c r="AN20" t="inlineStr"/>
-      <c r="AO20" t="inlineStr"/>
-      <c r="AP20" t="inlineStr"/>
-      <c r="AQ20" t="inlineStr"/>
-      <c r="AR20" t="inlineStr"/>
-      <c r="AS20" t="inlineStr"/>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AU20" t="inlineStr"/>
-      <c r="AV20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr"/>
-      <c r="AX20" t="inlineStr"/>
-      <c r="AY20" t="inlineStr"/>
-      <c r="AZ20" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-04.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="21" ht="51" customHeight="1">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0073_2in1_clever_cutter</t>
+          <t>24591_vegetables_n_fruit_peeler_1pc</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2 in 1 Clever Cutter with Stainless Steel Blade and Cutting Board</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+          <t>Stainless Steel Vegetable and Fruit Peeler with Swivel Blade for Kitchen</t>
+        </is>
+      </c>
+      <c r="H21" t="n">
+        <v>525</v>
+      </c>
+      <c r="I21" t="n">
+        <v>229</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -10076,108 +9279,66 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>Simplify your kitchen tasks with the innovative 2-in-1 clever cutter, featuring a durable stainless steel blade and an integrated cutting board. This versatile tool revolutionises how you chop vegetables, fruits, and herbs, allowing you to cut directly over a bowl or pan, eliminating the need for extra chopping boards and reducing cleanup. Its unique design makes daily meal preparation faster and more efficient, perfect for busy Indian kitchens. Key features 2-in-1 design combines a sharp stainless steel blade with a built-in cutting board. Chop ingredients directly into your bowl, kadhai, or plate, saving time and effort. Eliminates the need for a separate chopping board, simplifying cleanup. Shear action requires less wrist strain compared to traditional knife chopping. Ergonomic silicon</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr"/>
-      <c r="R21" t="inlineStr"/>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr"/>
+          <t>&lt;p&gt;Discover the ultimate kitchen companion with our stainless steel swivel blade vegetable peeler . This essential tool is engineered for effortless peeling of various fruits and vegetables, making your food preparation quicker and more enjoyable. Its smooth swivel blade glides along contours, ensuring thin, efficient removal of skins without wasting pulp. The comfortable handle provides a steady grip, enhancing control and safety during use, while the durable stainless steel construction promises long-lasting performance in any kitchen. Key features Sharp swivel blade follows uneven produce surfaces for controlled, efficient peeling. Durable stainless steel construction ensures reliable everyday use and rust resistance. Comfortable cylindrical handle offers a steady, non-slip grip during foo&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U21" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V21" t="inlineStr"/>
       <c r="W21" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/0073.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-1.jpg</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/01_d7ae265e-e7e5-42d1-9769-2aaffcd6bd80.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-2.jpg</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/02_055a6c77-0c6e-4e63-aced-b11634f40e76.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-3.jpg</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/04_4964210f-9bff-46ea-8461-7aba561a9a70.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-4.jpg</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/07_05ed710d-c1ff-4b3d-93c1-625553a2d0ed.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-5.jpg</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/06_b99d8cd5-29f3-427c-bbdb-9214cd888923.jpg</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr"/>
-      <c r="AE21" t="inlineStr"/>
-      <c r="AF21" t="inlineStr"/>
-      <c r="AG21" t="inlineStr"/>
-      <c r="AH21" t="inlineStr"/>
-      <c r="AI21" t="inlineStr"/>
-      <c r="AJ21" t="inlineStr"/>
-      <c r="AK21" t="inlineStr"/>
-      <c r="AL21" t="inlineStr"/>
-      <c r="AM21" t="inlineStr"/>
-      <c r="AN21" t="inlineStr"/>
-      <c r="AO21" t="inlineStr"/>
-      <c r="AP21" t="inlineStr"/>
-      <c r="AQ21" t="inlineStr"/>
-      <c r="AR21" t="inlineStr"/>
-      <c r="AS21" t="inlineStr"/>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AU21" t="inlineStr"/>
-      <c r="AV21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr"/>
-      <c r="AX21" t="inlineStr"/>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="22" ht="51" customHeight="1">
-      <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23341_soap_pump_dispenser_with_sponge_ho</t>
+          <t>11035_apex_ss_chimta_1pc</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2 In 1 Press Soap Pump Dispenser with Sponge Holder for Kitchen Sink</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>460</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
+          <t>Durable Stainless Steel Chimta for Safe Kitchen Use</t>
+        </is>
+      </c>
+      <c r="H22" t="n">
+        <v>525</v>
+      </c>
+      <c r="I22" t="n">
+        <v>269</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
@@ -10186,108 +9347,66 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>Keep your kitchen sink tidy and organised with the 2 in 1 Press Soap Pump Dispenser. This innovative white and black soap pump dispenser combines a soap dispenser and a sponge holder, offering a clutter-free solution for your dishwashing needs. Its clever press-down mechanism dispenses the perfect amount of liquid soap directly onto your sponge, preventing wastage and making cleanup effortless. Key features 2-in-1 design integrates a soap dispenser and a dedicated sponge holder Effortless press-down action for precise soap dispensing onto your sponge Built-in drainage tray ensures your sponge remains dry and hygienic Transparent reservoir allows for easy monitoring of soap levels One-handed operation simplifies dishwashing tasks Minimises soap wastage by dispensing only the required quanti</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr"/>
+          <t>&lt;p&gt;Discover the essential kitchen tool for safe and effortless food handling. This premium stainless steel chimta, crafted for durability and performance, ensures you can manage hot items with confidence and ease. Perfect for a variety of cooking tasks, it&amp;#x27;s designed to be a reliable addition to any home or commercial kitchen. Ensures secure handling of hot food, providing a strong, reliable grip for flipping, turning, and serving with confidence and ease. Crafted from high-quality stainless steel, offering exceptional durability, rust resistance, and long-lasting performance for daily kitchen tasks. Designed with heat-resistant construction, allowing safe and comfortable use when cooking on gas stoves, tandoors, or induction cooktops. Simplifies your cooking, ideal for effortlessly managing&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V22" t="inlineStr"/>
       <c r="W22" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Soap-Dispenser-1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Chimta-WOSKU-01.jpg</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_a7152713-1926-42b7-903f-8b46cec274c8.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/477S.Schimta.jpg</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Soap-Dispenser-3.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Chimta-02.jpg</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Soap-Dispenser-4.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11035_apex_ss_chimta_1pc.jpg</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Soap-Dispenser-7.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Chimta-04.jpg</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Soap-Dispenser-6.jpg</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr"/>
-      <c r="AE22" t="inlineStr"/>
-      <c r="AF22" t="inlineStr"/>
-      <c r="AG22" t="inlineStr"/>
-      <c r="AH22" t="inlineStr"/>
-      <c r="AI22" t="inlineStr"/>
-      <c r="AJ22" t="inlineStr"/>
-      <c r="AK22" t="inlineStr"/>
-      <c r="AL22" t="inlineStr"/>
-      <c r="AM22" t="inlineStr"/>
-      <c r="AN22" t="inlineStr"/>
-      <c r="AO22" t="inlineStr"/>
-      <c r="AP22" t="inlineStr"/>
-      <c r="AQ22" t="inlineStr"/>
-      <c r="AR22" t="inlineStr"/>
-      <c r="AS22" t="inlineStr"/>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AU22" t="inlineStr"/>
-      <c r="AV22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr"/>
-      <c r="AX22" t="inlineStr"/>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Chimta-size.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="51" customHeight="1">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>whl282_16154_car_safety_hammer_1pc</t>
+          <t>12133_pots_n_pans_protectors_pad_3pc</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2 in 1 Car Safety Hammer Emergency Window Breaker and Seatbelt Cutter</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>199</t>
-        </is>
+          <t>Felt Pots and Pans Protectors – Set of 3 Sizes | Bake &amp; Dwell</t>
+        </is>
+      </c>
+      <c r="H23" t="n">
+        <v>569</v>
+      </c>
+      <c r="I23" t="n">
+        <v>219</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -10296,108 +9415,66 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Car &amp; Motorbike</t>
+          <t>Kitchen &amp; Dining</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>Stay prepared for any road emergency with this Red car safety hammer . It combines a hardened window glass breaker and a built-in seatbelt cutter in one compact tool, helping you escape quickly if your car ever gets stuck after an accident or flood. This essential car safety hammer ensures peace of mind on every journey, providing a reliable emergency escape tool for all drivers. Key features 2 in 1 emergency tool combines a window breaker and a seatbelt cutter Hardened metal point shatters car glass quickly in an emergency Built-in safety blade slices through jammed seatbelts with ease Ergonomic non-slip grip handle is easy to hold and swing Compact size fits in the glove box, door pocket, or under the seat Lightweight design makes it easy to keep within reach while driving Sturdy build i</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr"/>
-      <c r="R23" t="inlineStr"/>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr"/>
+          <t>&lt;p&gt;Felt pots and pans protectors are essential kitchen accessories that prevent scratches and damage to your cookware and countertops. This set of 3 protectors, available in large (38cm), medium (35cm), and small (26cm), ensures versatile use across all your pots, pans, plates, and bowls. Made from eco-friendly polyester felt, these protectors absorb impact and prevent stacking damage while adding a layer of heat protection. Key features Prevents scratches and chips between cookware pieces during storage or transport. Set includes three sizes: large, medium, and small for versatile kitchen use. Made from durable, eco-friendly polyester felt with a non-slip texture. Protects countertops from heat damage and wear during cooking and storage. Washable and reusable for long-lasting protection and&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V23" t="inlineStr"/>
       <c r="W23" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Car-Safety-Hammer-1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_25269f02-055a-4659-a291-500d76d2a632.jpg</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/16154_car_safety_hammer_brown_box_1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ec19082a-e5f4-4e4c-b86b-c65ae1a03429.jpg</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Car-Safety-Hammer-4.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_0f6aa29e-7d42-498c-bdea-1a4bed11a7b1.jpg</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Car-Safety-Hammer-5.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_a24a3d9f-48ed-4e64-a242-183097085924.jpg</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Car-Safety-Hammer-7.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_1b5c7773-d8de-4ed5-8534-4bfd25e3895b.jpg</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Car-Safety-Hammer-6.jpg</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr"/>
-      <c r="AE23" t="inlineStr"/>
-      <c r="AF23" t="inlineStr"/>
-      <c r="AG23" t="inlineStr"/>
-      <c r="AH23" t="inlineStr"/>
-      <c r="AI23" t="inlineStr"/>
-      <c r="AJ23" t="inlineStr"/>
-      <c r="AK23" t="inlineStr"/>
-      <c r="AL23" t="inlineStr"/>
-      <c r="AM23" t="inlineStr"/>
-      <c r="AN23" t="inlineStr"/>
-      <c r="AO23" t="inlineStr"/>
-      <c r="AP23" t="inlineStr"/>
-      <c r="AQ23" t="inlineStr"/>
-      <c r="AR23" t="inlineStr"/>
-      <c r="AS23" t="inlineStr"/>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AU23" t="inlineStr"/>
-      <c r="AV23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr"/>
-      <c r="AX23" t="inlineStr"/>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_918aca57-ed07-4823-90fc-f7beeab4b5ae.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="51" customHeight="1">
-      <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>12904_3d_mini_saturn_lamp_1pc</t>
+          <t>18209_tranparent_adhesive_hook_6pc</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>3D Saturn Lamp – Multicolor LED Night Light with Base | Styleva</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>565</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>349</t>
-        </is>
+          <t>Transparent Adhesive Hooks (6 Pcs) – Strong &amp; Reusable | GlimmerHome</t>
+        </is>
+      </c>
+      <c r="H24" t="n">
+        <v>595</v>
+      </c>
+      <c r="I24" t="n">
+        <v>229</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -10406,108 +9483,66 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Transform your living space into a cosmic wonderland with the captivating 3D Saturn lamp with wooden base . This exquisite multicolor night light brings the majestic beauty of the ringed planet right into your home, casting a soft, enchanting glow perfect for any room. Ideal for creating a serene ambiance or adding a unique decorative touch, this 3D Saturn lamp with wooden base is more than just a light source – it&amp;#x27;s a conversation starter and a piece of celestial art. Perfect for bedrooms, living rooms, or study areas, it’s designed to inspire awe and tranquility with its realistic 3D design and vibrant illumination. Elevate your home decor and enjoy a touch of the cosmos every day. Whether you&amp;#x27;re looking for a soothing bedside companion or a distinctive accent piece, this 3D Saturn lamp&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr"/>
-      <c r="R24" t="inlineStr"/>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr"/>
+          <t>&lt;p&gt;Transform your home organisation with our versatile 6-piece transparent adhesive hook set . These strong, damage-free wall hooks are perfect for decluttering kitchens, bathrooms, and living spaces without drilling or leaving residue. Enjoy a clean, organised environment with GlimmerHome&amp;#x27;s premium adhesive solution. Key features Damage-Free Adhesion: Each transparent adhesive hook features a separate backing strip that adheres firmly to flat surfaces like tiles, glass, metal, and painted walls, yet removes cleanly without leaving marks or damage. High Load Capacity: Designed for durability, these robust wall hooks can hold up to 3 kg, making them ideal for hanging towels, kitchen utensils, coats, bags, and more. Versatile &amp;amp; Multi-Purpose: Use these strong wall hooks in your kitchen for ladl&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U24" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V24" t="inlineStr"/>
       <c r="W24" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/12904_3d_mini_saturn_lamp_1pc.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/18209_6797fc84-afc2-466b-95f8-85630df2c85e.png</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/d92fb5c6-de4c-45df-8986-9a89824f4bcf.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04f0556f-6f62-4753-b7e7-1c93ed9374c3.jpg</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_abe84596-7ace-4a48-9c05-e2214cad70ef.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_548f39c8-7fd2-438e-bb25-36c27165b698.jpg</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_9eb58ce8-f0fc-4597-b13c-d20d5263fe12.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_5f77b3bb-bd98-4a6f-ac78-c644b98e92a7.jpg</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_f6617730-b241-49af-b714-fdcd5b0604b9.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/017_9155afd4-927a-4888-8b1c-35ed4bca6832.jpg</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_ef1ee784-e00d-4802-b2ba-3c5d64d59161.jpg</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr"/>
-      <c r="AD24" t="inlineStr"/>
-      <c r="AE24" t="inlineStr"/>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="inlineStr"/>
-      <c r="AH24" t="inlineStr"/>
-      <c r="AI24" t="inlineStr"/>
-      <c r="AJ24" t="inlineStr"/>
-      <c r="AK24" t="inlineStr"/>
-      <c r="AL24" t="inlineStr"/>
-      <c r="AM24" t="inlineStr"/>
-      <c r="AN24" t="inlineStr"/>
-      <c r="AO24" t="inlineStr"/>
-      <c r="AP24" t="inlineStr"/>
-      <c r="AQ24" t="inlineStr"/>
-      <c r="AR24" t="inlineStr"/>
-      <c r="AS24" t="inlineStr"/>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AU24" t="inlineStr"/>
-      <c r="AV24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr"/>
-      <c r="AX24" t="inlineStr"/>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_f7bd0aa4-9449-4a5b-831b-1f6ee70f0368.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="25" ht="51" customHeight="1">
-      <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>18056_3d_moving_sand_art_round_frame_1pc</t>
+          <t>whl175_94381_wg_1103_mix</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>3D Moving Sand Art Round Frame with Stand for Home and Office Table Decor</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>329</t>
-        </is>
+          <t>LED Study Lamp with 3 Brightness Modes, Touch Control &amp; Flexible Neck (Color may vary)</t>
+        </is>
+      </c>
+      <c r="H25" t="n">
+        <v>509</v>
+      </c>
+      <c r="I25" t="n">
+        <v>319</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -10516,108 +9551,61 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Discover the captivating beauty of Round Frame Moving Sand Art Decor , a unique piece designed to bring a sense of calm and visual interest to any space. This elegant art display allows you to create ever-changing landscape patterns by simply flipping or rotating the frame. Watch as the fine sand gracefully shifts and settles into new, mesmerising formations, offering a dynamic and relaxing decorative element for your home, office, or study table. Key features Flowing sand creates a different landscape pattern after each turn, offering endless visual delight. Round display frame provides an attractive and modern tabletop presentation. Stable stand supports freestanding placement on various flat surfaces. Slow, gentle sand movement delivers a calming and meditative visual experience. Includ&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr"/>
+          <t>&lt;p&gt;Brighten your workspace or study area with our versatile flexible neck LED desk lamp. This modern lamp features three adjustable brightness modes (Low, Medium, High) to suit any task, easily controlled with a sensitive touch button on its base. The flexible silicone gooseneck allows for effortless positioning, directing light exactly where you need it, making it perfect for reading, studying, working, or as a bedside light. Its compact design and non-slip base ensure stability on any surface, from study tables to office desks and kids&amp;#x27; rooms. Conveniently USB powered, this flexible neck LED desk lamp is an essential for efficient and comfortable lighting. Key features 3 Brightness Levels: Easily switch between Low, Medium, and High light modes for optimal visibility. Touch Control: Simple&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U25" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr"/>
       <c r="W25" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/18056-01.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/6ObziZgHB0.jpg</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/18056-02.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4WYl48GuEt.jpg</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/18056-03.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/hh7UyUhSXR.jpg</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/18056-04.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/G3T8shx0jb.jpg</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/18056-05.jpg</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/18056-06.jpg</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr"/>
-      <c r="AD25" t="inlineStr"/>
-      <c r="AE25" t="inlineStr"/>
-      <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr"/>
-      <c r="AH25" t="inlineStr"/>
-      <c r="AI25" t="inlineStr"/>
-      <c r="AJ25" t="inlineStr"/>
-      <c r="AK25" t="inlineStr"/>
-      <c r="AL25" t="inlineStr"/>
-      <c r="AM25" t="inlineStr"/>
-      <c r="AN25" t="inlineStr"/>
-      <c r="AO25" t="inlineStr"/>
-      <c r="AP25" t="inlineStr"/>
-      <c r="AQ25" t="inlineStr"/>
-      <c r="AR25" t="inlineStr"/>
-      <c r="AS25" t="inlineStr"/>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AU25" t="inlineStr"/>
-      <c r="AV25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr"/>
-      <c r="AX25" t="inlineStr"/>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Kf9qrNrAh3.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="26" ht="51" customHeight="1">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr">
         <is>
-          <t>23601_led_penguin_decorative_light</t>
+          <t>whl282_13405_cartoon_led_desk_lamp_1pc</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>3D LED Penguin Decorative Infinity Mirror Light for Room and Wall Decor</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
+          <t>Kids LED Desk Lamp – Cute Cartoon Eye-Protection | Deodap</t>
+        </is>
+      </c>
+      <c r="H26" t="n">
+        <v>510</v>
+      </c>
+      <c r="I26" t="n">
+        <v>349</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
@@ -10626,108 +9614,66 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>&lt;p&gt;3D LED Penguin Holographic Infinity Mirror Decorative Ambient Light for Room and Wall Decor (1 Pc) Description :- Add a playful glow to indoor spaces with this penguin-shaped LED decorative light. The reflective holographic interior creates an eye-catching infinity-style light effect, while the freestanding shape and lightweight battery box make it suitable for shelves, tables and decorative wall arrangements. Penguin-Shaped Design: Charming animal silhouette adds a fun decorative accent to bedrooms and living spaces. Infinity Mirror Effect: Reflective interior creates a layered, visually engaging illuminated appearance. Bright LED Illumination: Integrated LEDs produce a sparkling ambient glow for decorative use. Holographic Light Pattern: Reflective surface disperses colourful streaks and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr"/>
-      <c r="R26" t="inlineStr"/>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr"/>
+          <t>&lt;p&gt;Brighten up your child&amp;#x27;s study space or bedside with our adorable Kids LED Desk Lamp from Deodap. Designed with a charming cartoon character base, this flexible and portable lamp provides soft, eye-friendly illumination, making it perfect for reading, homework, or a comforting night light. Its advanced luminous technology ensures there&amp;#x27;s no harsh glare, safeguarding your little one&amp;#x27;s eyes during long study sessions or quiet bedtime stories. Give them the gift of comfortable and fun lighting with this versatile LED lamp. This delightful Kids LED Desk Lamp combines playful aesthetics with practical functionality. Whether placed on a study table, bedside cabinet, or carried around for creative play, its lightweight and flexible design adapts to various needs. The USB rechargeable feature adds&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U26" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V26" t="inlineStr"/>
       <c r="W26" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23601-01.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/13405_cartoon_led_desk_lamp_1pc.jpg</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23601-02.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/d8dad9aa-d991-4606-a71f-561e6256a024.jpg</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23601-03.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_59ead39c-d786-4226-8b68-7979a4ba3661.jpg</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23601-04.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_1576a615-9884-4df5-bc62-8acad894791d.jpg</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23601-05.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_bde756db-bd43-4bea-9032-87fe6dcf789f.jpg</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23601-06.jpg</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr"/>
-      <c r="AD26" t="inlineStr"/>
-      <c r="AE26" t="inlineStr"/>
-      <c r="AF26" t="inlineStr"/>
-      <c r="AG26" t="inlineStr"/>
-      <c r="AH26" t="inlineStr"/>
-      <c r="AI26" t="inlineStr"/>
-      <c r="AJ26" t="inlineStr"/>
-      <c r="AK26" t="inlineStr"/>
-      <c r="AL26" t="inlineStr"/>
-      <c r="AM26" t="inlineStr"/>
-      <c r="AN26" t="inlineStr"/>
-      <c r="AO26" t="inlineStr"/>
-      <c r="AP26" t="inlineStr"/>
-      <c r="AQ26" t="inlineStr"/>
-      <c r="AR26" t="inlineStr"/>
-      <c r="AS26" t="inlineStr"/>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AU26" t="inlineStr"/>
-      <c r="AV26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr"/>
-      <c r="AX26" t="inlineStr"/>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_333169df-d3f6-4529-9cb7-63be3d9e1164.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="51" customHeight="1">
-      <c r="A27" t="inlineStr"/>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>14814_decorative_led_bulb_lamp_1pc</t>
+          <t>23627_cute_panda_night_lamp_1pc</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>3D Firework LED Bulb – Sparkling Ambience for Home Decor</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>619</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
+          <t>Cute Panda Showpiece Night Light for Kids Room Table &amp; Home Decor</t>
+        </is>
+      </c>
+      <c r="H27" t="n">
+        <v>439</v>
+      </c>
+      <c r="I27" t="n">
+        <v>249</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -10736,108 +9682,66 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This 3D firework LED bulb creates a stunning sparkling ambience, making it perfect for home decor and night ambience lighting. The unique 3D firework effect produces a crystal sparkle glow that enhances bedrooms, living rooms, parties, and festival settings alike. Key features 3D firework effect LED bulb for eye-catching decorative lighting Crystal sparkle atmosphere lamp ideal for mood lighting Energy-efficient LED bulb suitable for indoor use Perfect for bedrooms, living rooms, cafes, restaurants, and parties Enhances festival decoration with colorful and warm glow Stylish design complements modern and traditional interiors Ideal gift for home decor and lighting enthusiasts Supports romantic mood lighting and night ambience setups Materials &amp;amp; care The bulb uses energy-saving LED componen&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr"/>
+          <t>&lt;p&gt;Add a cute and playful touch to your space with this adorable panda showpiece . Featuring a cheerful panda expression, raised paws, and attractive detailing, this compact showpiece is ideal for decorating kids&amp;#x27; rooms, study tables, desks, shelves, and bedside tables. Its charming design also makes it a lovely gifting option for children, friends, and panda lovers. Key Features Cute Panda Design: Adorable facial expression with attractive black, white, pink, and green detailing. Compact Decorative Showpiece: Easy to place on tables, desks, shelves, and cabinets. Kids Room Decor: Adds a fun and cheerful touch to children&amp;#x27;s rooms and study areas. Multipurpose Decoration: Suitable for home, bedroom, study table, office desk, and display shelf. Cute Gift Option: Ideal for birthdays, return gift&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U27" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V27" t="inlineStr"/>
       <c r="W27" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/2cad4d41-2e02-457a-a75c-8f22a897dc51.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/GFCe3rlgHp.jpg</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01b0628b-5a9a-4d95-9124-31e8b90914e0.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ucrJjgY1AW.jpg</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_cdad21bd-9487-4c2c-ab81-a65412fc8264.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/nIy5BvRK2Q.jpg</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_8fd0203b-7159-4758-a3e9-20b1ec5dda9c.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/VHw3tFUnjw.jpg</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_ca30ec74-093c-4347-94d1-74bca3d60a69.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/dsVOdM1a8j.jpg</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_96c73d1c-7fc8-4951-af94-33b854312906.jpg</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr"/>
-      <c r="AD27" t="inlineStr"/>
-      <c r="AE27" t="inlineStr"/>
-      <c r="AF27" t="inlineStr"/>
-      <c r="AG27" t="inlineStr"/>
-      <c r="AH27" t="inlineStr"/>
-      <c r="AI27" t="inlineStr"/>
-      <c r="AJ27" t="inlineStr"/>
-      <c r="AK27" t="inlineStr"/>
-      <c r="AL27" t="inlineStr"/>
-      <c r="AM27" t="inlineStr"/>
-      <c r="AN27" t="inlineStr"/>
-      <c r="AO27" t="inlineStr"/>
-      <c r="AP27" t="inlineStr"/>
-      <c r="AQ27" t="inlineStr"/>
-      <c r="AR27" t="inlineStr"/>
-      <c r="AS27" t="inlineStr"/>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AU27" t="inlineStr"/>
-      <c r="AV27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr"/>
-      <c r="AX27" t="inlineStr"/>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4A7fcmAQ14.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="51" customHeight="1">
-      <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21005_shell_shaped_makeup_brush_with_mir</t>
+          <t>4654_6pc_flexible_wall_hook</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>5 in 1 Makeup Brush Set – Compact Kit with Built-in Mirror</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>259</t>
-        </is>
+          <t>Wall Hook Rail – Heavy Duty 6-Pin Transparent Golden | GlimmerHome</t>
+        </is>
+      </c>
+      <c r="H28" t="n">
+        <v>489</v>
+      </c>
+      <c r="I28" t="n">
+        <v>219</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -10846,108 +9750,66 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Discover the convenience of the 5 in 1 makeup brush set, designed to keep your brushes organized and ready for flawless application anytime. This compact kit features a built-in mirror and a portable storage case, making it your perfect travel companion and daily beauty essential. Whether you’re at home or on the go, this makeup brush set ensures professional-looking makeup with ease. Key features Includes 5 versatile makeup brushes suitable for foundation, blush, powder, and face makeup Compact shell-shaped storage box with built-in mirror for on-the-go touch-ups Soft bristles that offer smooth and even makeup application Protects brushes while keeping them neatly organized and clean Lightweight and portable, ideal for daily use, travel, and gifting Easy to open and carry, fits perfectly&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr"/>
-      <c r="R28" t="inlineStr"/>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr"/>
+          <t>&lt;p&gt;Upgrade your home organisation with the Transparent 6-hook adhesive wall rail , designed to bring both style and exceptional utility to any space. Crafted for Indian homes, this heavy-duty 6-pin organiser helps declutter your living areas, offering a smart solution for hanging essentials. Its unique transparent and golden finish adds a touch of modern sophistication, making it more than just a functional item – it&amp;#x27;s a decor enhancer. Say goodbye to cluttered countertops and misplaced items. This versatile Transparent 6-hook adhesive wall rail is perfect for entryways, bathrooms, bedrooms, and kitchens, providing convenient access to coats, keys, towels, and accessories. Experience the blend of durability and design that GlimmerHome brings to your daily life, simplifying your home organisat&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U28" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V28" t="inlineStr"/>
       <c r="W28" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_979ba448-fb91-4c1f-9bc7-3b09deccb4d0.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Transparent-6-Wall-Hook-Using-1500x1500.png</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_8dd0d56f-4b92-41ba-b17b-9ff1c63e2161.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4654_7e0d08fc-1d7b-4546-a853-669e04f99943.jpg</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_0905a400-0b4e-4bac-b136-98dd1f141e58.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_6c983aa7-83e3-4e60-9f3d-8e9a2a8457fa.jpg</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_41269cd2-6094-4d20-82c1-7835af7a794f.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_c0cb4c30-a185-49c9-bbed-6d75bc1569da.jpg</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_dd6b4ba1-d88a-4aa7-8ecc-799e6007e941.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_c889bba5-02b7-4236-b77b-f8b024f2277e.jpg</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_ef720d06-0ed1-4aad-8cb5-c70c9c173964.jpg</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr"/>
-      <c r="AD28" t="inlineStr"/>
-      <c r="AE28" t="inlineStr"/>
-      <c r="AF28" t="inlineStr"/>
-      <c r="AG28" t="inlineStr"/>
-      <c r="AH28" t="inlineStr"/>
-      <c r="AI28" t="inlineStr"/>
-      <c r="AJ28" t="inlineStr"/>
-      <c r="AK28" t="inlineStr"/>
-      <c r="AL28" t="inlineStr"/>
-      <c r="AM28" t="inlineStr"/>
-      <c r="AN28" t="inlineStr"/>
-      <c r="AO28" t="inlineStr"/>
-      <c r="AP28" t="inlineStr"/>
-      <c r="AQ28" t="inlineStr"/>
-      <c r="AR28" t="inlineStr"/>
-      <c r="AS28" t="inlineStr"/>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AU28" t="inlineStr"/>
-      <c r="AV28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr"/>
-      <c r="AX28" t="inlineStr"/>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_0424d040-e5e1-4363-8a95-e79fc589719f.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="51" customHeight="1">
-      <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>18733_glass_hourglass_sand_timer_1pc</t>
+          <t>17597_decor_round_mehndi_name_plate_1pc</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>4-Minute Sand Timer Hourglass – Elegant Glass for Desk Decor</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>465</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+          <t>Mehndi Ceremony Wall Hanging – Lightweight Round Decorative Sign</t>
+        </is>
+      </c>
+      <c r="H29" t="n">
+        <v>485</v>
+      </c>
+      <c r="I29" t="n">
+        <v>259</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -10956,108 +9818,66 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Office Products</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Enhance your workspace or home with this elegant 4-minute sand timer hourglass . Crafted from sophisticated glass with fine yellow sand, it provides precise timing while adding a touch of vintage charm to any space. Key features 4-Minute Timing: Accurately measures four minutes, making this sand timer hourglass ideal for managing study sessions, cooking, or work tasks. Elegant Design: Transparent glass with smooth sand flow, making this hourglass timer a stylish addition to desks and shelves. Versatile Use: Suitable for kitchen, office, or decorative purposes, enhancing your environment with a calming vibe. Compact &amp;amp; Portable: Lightweight design allows easy placement in various settings. Calming Effect: Gentle sand flow creates a soothing atmosphere for focus and relaxation with this sand&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr"/>
+          <t>&lt;p&gt;Enhance your wedding with this Mehndi ceremony wall hanging, designed to bring a traditional and festive charm to your mehndi, haldi, sangeet, or pre-wedding décor. This lightweight round decorative sign features the Hindi “मेहंदी” cut-out lettering, making it an eye-catching backdrop element perfect for photo booths, stage styling, or entrance decorations. Key features Bold round wall sign with Hindi “मेहंदी” lettering for instant cultural theme décor Lightweight and reusable design for easy installation and storage Pre-drilled holes for quick hanging using hooks, nails, strings, or double-sided tape Smooth, wipe-clean surface that resists creasing unlike paper decorations Complements floral curtains, fairy lights, drapes, and balloons for elegant styling Travel-friendly for versatile use&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U29" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V29" t="inlineStr"/>
       <c r="W29" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Glass-Sand-Timer-1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-01.jpg</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_779aff7e-f3f4-437a-8db6-02e462782a6c.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/102517597-99Pc-Mahendi-Av-Sv.jpg</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Glass-Sand-Timer-2.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-06.jpg</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Glass-Sand-Timer-7.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-02.jpg</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Glass-Sand-Timer-3.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-05.jpg</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Glass-Sand-Timer-6.jpg</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr"/>
-      <c r="AD29" t="inlineStr"/>
-      <c r="AE29" t="inlineStr"/>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="inlineStr"/>
-      <c r="AH29" t="inlineStr"/>
-      <c r="AI29" t="inlineStr"/>
-      <c r="AJ29" t="inlineStr"/>
-      <c r="AK29" t="inlineStr"/>
-      <c r="AL29" t="inlineStr"/>
-      <c r="AM29" t="inlineStr"/>
-      <c r="AN29" t="inlineStr"/>
-      <c r="AO29" t="inlineStr"/>
-      <c r="AP29" t="inlineStr"/>
-      <c r="AQ29" t="inlineStr"/>
-      <c r="AR29" t="inlineStr"/>
-      <c r="AS29" t="inlineStr"/>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AU29" t="inlineStr"/>
-      <c r="AV29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr"/>
-      <c r="AX29" t="inlineStr"/>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-03.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="30" ht="51" customHeight="1">
-      <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>21114_4in1_manicure_n_pedicure_grooming_</t>
+          <t>whl175_77886_1723_3</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>4 in 1 Manicure and Pedicure Grooming Kit, Compact Nail Care Set</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+          <t>Lord Ganesha Hanging Suncatcher Wall Decor for Home, Balcony &amp; Car</t>
+        </is>
+      </c>
+      <c r="H30" t="n">
+        <v>539</v>
+      </c>
+      <c r="I30" t="n">
+        <v>399</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
@@ -11066,108 +9886,61 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Enhance your personal grooming routine with the 4 in 1 manicure and pedicure kit, designed to provide comprehensive nail care in one compact set. This versatile grooming kit is perfect for maintaining neat, well-shaped nails at home or on the go, making it an essential addition to your beauty and hygiene arsenal. Whether you are looking for a reliable nail cutter, file, tweezers or a hand mirror, this set covers all your nail care needs with ease and precision, ensuring smooth and well-groomed nails every time. Key features 4 in 1 complete grooming set with essential tools Includes nail file, scissors, tweezers, and mirror for comprehensive nail care Helps maintain clean, shaped, and well-groomed nails Compact, lightweight, and travel-friendly design Easy to use for daily grooming routines&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr"/>
-      <c r="R30" t="inlineStr"/>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr"/>
+          <t>&lt;p&gt;Enhance your home with the divine presence of this Lord Ganesha glass hanging decor. Featuring a vibrant Ganesha illustration, this decorative piece symbolizes wisdom, prosperity, and positive energy for any space. Key features Divine Lord Ganesha Design: Symbolizes wisdom, prosperity, protection, and positive energy for your home. Premium Hanging Cord: Durable natural jute rope with decorative beads adds a stylish finish. Multi-Purpose Decoration: Suitable for living room, pooja room, balcony, window, yoga room, meditation space, office, and car. Bright And Attractive Artwork: Vibrant colors add elegance and spiritual charm to any decor. Easy to Hang: Lightweight and ready to hang on hooks, walls, windows, or doors. Ideal Gift: Perfect for Diwali, Ganesh Chaturthi, housewarming, weddings,&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U30" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V30" t="inlineStr"/>
       <c r="W30" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/21114_4in1_manicure_n_pedicure_grooming_kit.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/BEWKLC04mY.png</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_579e0cc8-63b8-49ad-a631-9384aa578978.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wJ201azNKz.png</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/manicureset-06_b7603a74-8d62-46ed-8b17-32efe5bdb445.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wCD72wwif2.png</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/manicureset-02_4bdd11b7-721a-43eb-8c6a-618f0c8c667d.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4DFiLQ8IUO.png</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/manicureset-04_f3055e90-6009-4e63-9b5a-f767ed7f45bc.jpg</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/manicureset-07.jpg</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr"/>
-      <c r="AD30" t="inlineStr"/>
-      <c r="AE30" t="inlineStr"/>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="inlineStr"/>
-      <c r="AH30" t="inlineStr"/>
-      <c r="AI30" t="inlineStr"/>
-      <c r="AJ30" t="inlineStr"/>
-      <c r="AK30" t="inlineStr"/>
-      <c r="AL30" t="inlineStr"/>
-      <c r="AM30" t="inlineStr"/>
-      <c r="AN30" t="inlineStr"/>
-      <c r="AO30" t="inlineStr"/>
-      <c r="AP30" t="inlineStr"/>
-      <c r="AQ30" t="inlineStr"/>
-      <c r="AR30" t="inlineStr"/>
-      <c r="AS30" t="inlineStr"/>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AU30" t="inlineStr"/>
-      <c r="AV30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr"/>
-      <c r="AX30" t="inlineStr"/>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/FU2YHsgGEM.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="51" customHeight="1">
-      <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>12381_3d_creative_visualization_mahadev_</t>
+          <t>whl294_79825_17423_2_mix</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>3D Mahadev LED Lamp with Wooden Base for Home Decor Shelf (1 Pc)</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
+          <t>DIY Tulip Mirror Lamp Kit - Colorful LED Night Light Decor</t>
+        </is>
+      </c>
+      <c r="H31" t="n">
+        <v>485</v>
+      </c>
+      <c r="I31" t="n">
+        <v>349</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -11176,108 +9949,66 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Illuminate your space with the captivating Shiva acrylic LED lamp , a unique blend of spirituality and modern design. This elegant lamp features a beautifully etched Mahadev figure on an acrylic plate, seamlessly slotted into a sturdy wooden base. When unlit, the clear panel catches daylight, showcasing the intricate design as a subtle sculpture. When switched on, the LED light runs through the engraving, bringing the Mahadev figure to life with a gentle, ambient glow that transforms any room into a serene sanctuary. Key features Wooden base elevates the lamp from a gadget to a sophisticated decor piece Acrylic plate slots into the base, ensuring easy setup and a sleek profile Etched Mahadev figure catches daylight, offering visual appeal even when off LED light illuminates the engraving,&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr"/>
-      <c r="R31" t="inlineStr"/>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr"/>
+          <t>&lt;p&gt;Unleash your creativity and brighten any space with the captivating DIY Tulip Mirror Lamp Kit. This unique craft project transforms into a beautiful decorative light, featuring vibrant tulip flowers encased within reflective mirror panels. Enjoy the enchanting glow when lit, or the sleek mirror aesthetic when off, adding a touch of elegance to your home décor. Engage in a delightful DIY craft experience by assembling your own enchanting floral lamp, perfect for creative minds and décor enthusiasts. Experience a stunning visual transformation as colorful LED tulips illuminate when switched on, reflecting beautifully in the mirror panels. Adorn your space with a charming mix of pink, blue, yellow, and purple tulip-style flowers, creating an attractive and vibrant decorative display. Immerse&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U31" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V31" t="inlineStr"/>
       <c r="W31" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_9ecb0a6e-db8a-45c1-ab15-fafe2c213610.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/u8drG5EhUt.jpg</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_ac74986e-f919-4bd4-9d1b-171db085836d.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/CATOkciJbJ.jpg</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_2e5a1687-87e1-4e46-86cd-65c8fd1600eb.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Epb3Ml6Jfb.jpg</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_9154034c-a3ba-47d2-919f-e15afa8df3be.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/63AYFzw0Qy.jpg</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_b9502810-db3b-40e0-a50b-69b7520b1c93.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/5uHg5DzVvg.jpg</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_aa4bc92e-223a-47ea-9234-cc41df4af082.jpg</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr"/>
-      <c r="AD31" t="inlineStr"/>
-      <c r="AE31" t="inlineStr"/>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="inlineStr"/>
-      <c r="AH31" t="inlineStr"/>
-      <c r="AI31" t="inlineStr"/>
-      <c r="AJ31" t="inlineStr"/>
-      <c r="AK31" t="inlineStr"/>
-      <c r="AL31" t="inlineStr"/>
-      <c r="AM31" t="inlineStr"/>
-      <c r="AN31" t="inlineStr"/>
-      <c r="AO31" t="inlineStr"/>
-      <c r="AP31" t="inlineStr"/>
-      <c r="AQ31" t="inlineStr"/>
-      <c r="AR31" t="inlineStr"/>
-      <c r="AS31" t="inlineStr"/>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AU31" t="inlineStr"/>
-      <c r="AV31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr"/>
-      <c r="AX31" t="inlineStr"/>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/DGnfKB1TaP.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="51" customHeight="1">
-      <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>12385_3d_creative_visualization_ganesh_l</t>
+          <t>21058_cube_tulip_flower_night_lamp_set</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>3D Ganesha LED Lamp with Wooden Base for Home and Pooja Decor (1 Pc)</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+          <t>Tulip Flower LED Cube Night Lamp – Warm Ambient Decorative Light</t>
+        </is>
+      </c>
+      <c r="H32" t="n">
+        <v>499</v>
+      </c>
+      <c r="I32" t="n">
+        <v>349</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -11286,108 +10017,66 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Brighten your home and pooja corner with this elegant 3D Ganesha LED Lamp. This lamp serves as a beautiful decorative piece during the day, featuring a clear etched panel. When switched on, the Ganesha figure illuminates from the sturdy wooden base with a warm, comforting glow, creating a serene ambiance without the need for an open flame. Its compact size ensures it fits perfectly on mandir shelves, living room consoles, or office desks without overcrowding. Key features Provides a warm, flame-free glow for lasting evening illumination Compact design fits easily on mandir shelves with existing idols and thali Appears as a clear etched panel by day, lights up as Ganesha at night Solid wooden base adds stability and a decorative touch Acrylic plate efficiently carries LED light along the in&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr"/>
-      <c r="R32" t="inlineStr"/>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr"/>
+          <t>&lt;p&gt;Elevate your home atmosphere with the Tulip Flower LED Cube Night Lamp, a perfect blend of elegant design and soothing illumination. This decorative tulip flower LED cube lamp casts a warm ambient glow that enhances any room&amp;#x27;s mood and style. Key features Transparent cube design featuring a glowing tulip flower pattern Soft, warm LED light ideal for calming and ambient illumination Perfect for bedside, tabletop decor, and mood lighting Compact and lightweight for versatile placement on shelves and corners Enhances your home decor with a stylish floral accent Suitable for festive decoration and gifting on special occasions FAQ Q1: What is a Tulip Flower LED Cube Night Lamp? A: It&amp;#x27;s a decorative LED cube lamp with illuminated tulip flower patterns providing warm ambient lighting for home dec&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U32" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V32" t="inlineStr"/>
       <c r="W32" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_001a09a2-b9a6-41b2-ac4a-65b0c3dc285e.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/21058_cube_tulip_flower_night_lamp_set_showcase_9d041eca-ef47-441b-b6c4-254c25047868.png</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/12385.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_LED-Mirror.jpg</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_9b01b019-df03-49c4-b301-53f3e1212333.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_LED-Mirror.jpg</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_21efd4a1-5f64-4a2e-8bd0-33e926604fe7.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_LED-Mirror.jpg</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_c68a38d7-ecc5-4102-bdb0-7b84e1d02dc2.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_LED-Mirror.jpg</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_b57c0beb-c390-4f98-b1d7-e073f2ab8ba0.jpg</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
-      <c r="AI32" t="inlineStr"/>
-      <c r="AJ32" t="inlineStr"/>
-      <c r="AK32" t="inlineStr"/>
-      <c r="AL32" t="inlineStr"/>
-      <c r="AM32" t="inlineStr"/>
-      <c r="AN32" t="inlineStr"/>
-      <c r="AO32" t="inlineStr"/>
-      <c r="AP32" t="inlineStr"/>
-      <c r="AQ32" t="inlineStr"/>
-      <c r="AR32" t="inlineStr"/>
-      <c r="AS32" t="inlineStr"/>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AU32" t="inlineStr"/>
-      <c r="AV32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr"/>
-      <c r="AX32" t="inlineStr"/>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_LED-Mirror.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="33" ht="51" customHeight="1">
-      <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>12382_3d_creative_visualization_ganesh_l</t>
+          <t>whl175_77890_634_1</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>3D Ganesha Acrylic LED Lamp with Warm Golden Glow for Decor (1 Pc)</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+          <t>Cute Panda LED Night Lamp for Kids Room Bedroom &amp; Table Decor</t>
+        </is>
+      </c>
+      <c r="H33" t="n">
+        <v>489</v>
+      </c>
+      <c r="I33" t="n">
+        <v>249</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -11396,108 +10085,66 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Brighten your home with the enchanting Ganesha acrylic LED lamp , designed to cast a warm golden glow. Unlike harsh white lights, this lamp creates a serene and inviting atmosphere, perfect for any living space. The intricate Ganesha figure is delicately etched into the acrylic plate, with light emanating from the sturdy wooden base to highlight every detail. When switched off, it transforms into a clear, elegant panel on a wooden stand, ensuring your shelf remains stylishly decorated throughout the day. Key features Emits a warm golden glow, ideal for creating a cozy ambiance Features an intricately etched Ganesha figure on acrylic plate Illuminated from a durable wooden base for a sophisticated look Functions as a clear decorative panel when not lit Compact 10 cm size fits crowded shelve&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr"/>
-      <c r="R33" t="inlineStr"/>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr"/>
+          <t>&lt;p&gt;Brighten up any child&amp;#x27;s space with this adorable Panda LED Night Lamp. Featuring a charming panda character wearing a playful green leaf hat, this lamp emits a soft, warm glow, creating a comforting and cosy atmosphere in kids&amp;#x27; rooms and bedrooms. Its compact design makes it a versatile decorative piece for bedside tables, study desks, shelves, or nightstands, adding a touch of whimsy and warmth to any decor. Key features Adorable Panda Design: Features a cute panda with a unique green leaf-style top. Soft LED Illumination: Provides a gentle, warm light perfect for a relaxing nighttime ambience. Ideal for Kids&amp;#x27; Rooms: Attractive and safe lighting option suitable for children&amp;#x27;s bedrooms. Compact Tabletop Size: Easily fits on bedside tables, desks, and shelves. Decorative Accent: Adds a chee&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U33" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V33" t="inlineStr"/>
       <c r="W33" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_00508724-b349-4df3-8161-b8ece2f85a43.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/FKUenUuiTR.jpg</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_7a212faf-12ea-4fdf-b0f9-03056987c6e8.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/qrWMMj8Ix0.jpg</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_3ba043d0-c67d-45da-8af5-092bf4b4f42f.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4aHVA4gast.jpg</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_71f11a8b-17f2-4339-8d0e-d2944bb80eb8.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ey2n5tAG2O.jpg</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_466132c7-840b-44bf-aa4d-18952c6ddc65.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/yeIr4pK2bc.jpg</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_f1587c89-69c1-422d-83a4-ae45beb6b476.jpg</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr"/>
-      <c r="AD33" t="inlineStr"/>
-      <c r="AE33" t="inlineStr"/>
-      <c r="AF33" t="inlineStr"/>
-      <c r="AG33" t="inlineStr"/>
-      <c r="AH33" t="inlineStr"/>
-      <c r="AI33" t="inlineStr"/>
-      <c r="AJ33" t="inlineStr"/>
-      <c r="AK33" t="inlineStr"/>
-      <c r="AL33" t="inlineStr"/>
-      <c r="AM33" t="inlineStr"/>
-      <c r="AN33" t="inlineStr"/>
-      <c r="AO33" t="inlineStr"/>
-      <c r="AP33" t="inlineStr"/>
-      <c r="AQ33" t="inlineStr"/>
-      <c r="AR33" t="inlineStr"/>
-      <c r="AS33" t="inlineStr"/>
-      <c r="AT33" t="inlineStr"/>
-      <c r="AU33" t="inlineStr"/>
-      <c r="AV33" t="inlineStr"/>
-      <c r="AW33" t="inlineStr"/>
-      <c r="AX33" t="inlineStr"/>
-      <c r="AY33" t="inlineStr"/>
-      <c r="AZ33" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/qLsafc32Mr.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="51" customHeight="1">
-      <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr">
         <is>
-          <t>12384_3d_creative_visualization_lamp_no4</t>
+          <t>21255_cute_mini_panda_night_light_lamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>3D Crystal LED Table Lamp – Running Horses on Wooden Base</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>515</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+          <t>Cute Mini Panda Night Light – Soft LED Bedside Lamp for Kids</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>440</v>
+      </c>
+      <c r="I34" t="n">
+        <v>289</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -11506,108 +10153,66 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Home Decor</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Enhance your home décor with this exquisite 3D crystal LED table lamp featuring a running horses design, brilliantly illuminated with soft LED light on a sturdy wooden base. This ambient table lamp blends artistic crystal engraving with warm night lighting, creating a captivating focal point for bedrooms, living rooms, or offices. Key features Intricately engraved 3D running horses design inside clear crystal plate Soft LED illumination for gentle ambient lighting and mood enhancement Clear crystal enhances visual depth and artistic appeal Durable wooden base ensures stable tabletop placement Perfect decorative piece for modern and classic interior settings Functions as a night lamp, decorative accent, or thoughtful gift Materials &amp;amp; care This lamp combines a clear crystal plate with a soli&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr"/>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
+          <t>&lt;p&gt;The cute mini panda night light is designed to provide a gentle, calming glow that helps children feel safe and cozy at night. Perfect for bedrooms, nurseries, and study desks, this adorable panda lamp combines charming decor with functional lighting, creating a relaxing atmosphere for restful sleep. Its compact size makes it an ideal bedside companion, offering a soft, soothing light that does not disturb sleep patterns. Key features Cute panda design enhances room decor and adds a playful touch Soft LED light creates a calming, cozy ambiance Ideal as a night lamp for peaceful sleep and bedtime routines Compact and lightweight, perfect for small spaces and portable use Energy-efficient lighting saves power while illuminating effectively Child-safe and durable design ensures peace of mind&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U34" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V34" t="inlineStr"/>
       <c r="W34" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1744521e-7503-4a82-b751-7a5f912b4559.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-WOSKU-01.jpg</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/14419873-c55d-4b24-b9dd-54c078e5f0b4.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/21255.jpg</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/3dlamp-02.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-03.jpg</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/3dlamp-06.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-06.jpg</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/3dlamp-04.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-04.jpg</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/3dlamp-size.jpg</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr"/>
-      <c r="AD34" t="inlineStr"/>
-      <c r="AE34" t="inlineStr"/>
-      <c r="AF34" t="inlineStr"/>
-      <c r="AG34" t="inlineStr"/>
-      <c r="AH34" t="inlineStr"/>
-      <c r="AI34" t="inlineStr"/>
-      <c r="AJ34" t="inlineStr"/>
-      <c r="AK34" t="inlineStr"/>
-      <c r="AL34" t="inlineStr"/>
-      <c r="AM34" t="inlineStr"/>
-      <c r="AN34" t="inlineStr"/>
-      <c r="AO34" t="inlineStr"/>
-      <c r="AP34" t="inlineStr"/>
-      <c r="AQ34" t="inlineStr"/>
-      <c r="AR34" t="inlineStr"/>
-      <c r="AS34" t="inlineStr"/>
-      <c r="AT34" t="inlineStr"/>
-      <c r="AU34" t="inlineStr"/>
-      <c r="AV34" t="inlineStr"/>
-      <c r="AW34" t="inlineStr"/>
-      <c r="AX34" t="inlineStr"/>
-      <c r="AY34" t="inlineStr"/>
-      <c r="AZ34" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-07.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="51" customHeight="1">
-      <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>15438_6_led_solar_fence_light_2pc</t>
+          <t>4785_selfie_ring_light</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6 LED Solar Wall Fence Light – Honeycomb Shade Design, 2 Pc Set</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
+          <t>Selfie Ring Light – Portable LED for Flawless Photos &amp; Videos | Gambit</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>470</v>
+      </c>
+      <c r="I35" t="n">
+        <v>299</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
@@ -11616,108 +10221,66 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Illuminate your garden or patio effortlessly with this 2-piece set of 6 LED Solar Wall Fence Lights featuring a unique honeycomb shade design. These solar-powered fence lights provide bright, energy-efficient lighting, automatically turning on at dusk to enhance outdoor safety and ambience without the need for wiring or batteries. Key features Solar powered with built-in rechargeable battery for eco-friendly use 6 bright white LEDs per unit delivering effective outdoor illumination Honeycomb shade diffuser creating charming light patterns Durable waterproof and weather-resistant construction suitable for all seasons (IP65 rated) Automatic dusk-to-dawn sensor for effortless operation Compact half-round design ideal for mounting on fences or walls Includes mounting accessories for quick and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr"/>
-      <c r="R35" t="inlineStr"/>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr"/>
+          <t>&lt;p&gt;Transform your photos and videos with the ultimate Selfie Ring Light from Gambit, designed to provide professional-grade illumination wherever you go. Say goodbye to dull, poorly lit shots and hello to vibrant, perfectly exposed content. This portable ring light is an essential tool for creators, beauty enthusiasts, and anyone looking to enhance their digital presence with brilliant lighting. Whether you&amp;#x27;re taking a quick selfie, recording a detailed makeup tutorial, or engaging in video calls, this LED ring light ensures you always look your best. Its lightweight and compact design makes it incredibly easy to carry, fitting seamlessly into your bag or purse. Experience the difference a dedicated light source makes, providing even, soft illumination that eliminates harsh shadows and brings&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U35" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V35" t="inlineStr"/>
       <c r="W35" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/71ca71fc-d470-44c1-a3e3-1a9b141c05cf_8924a530-3aa4-447a-a8e4-db5cee92d5ed.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/01_9517595e-8d48-451f-91b7-e252bf2d5beb.jpg</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/6564318e-0a17-4c60-b40d-f0e9d864cda8_d0f82199-7f4e-4164-bda2-b4650453300d.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/F3KmSjCQqupnir8zXY8mlr2ezuDOTMSE6vAlE6DE.jpg</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_6afca26f-e20f-4588-bdc6-5f8eccbdf894.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/10_0d64f988-9475-46ff-b89d-9a7f34df7618.jpg</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_421d9fa5-d3fa-42d4-9cfb-388095a2d62d.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/2092621090.png</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_ffa2f3d9-4044-4ab8-b1b3-8eb53349ecb7.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/2092621089.png</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_0e862775-eb6a-4453-abc6-488db0b31249.jpg</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr"/>
-      <c r="AD35" t="inlineStr"/>
-      <c r="AE35" t="inlineStr"/>
-      <c r="AF35" t="inlineStr"/>
-      <c r="AG35" t="inlineStr"/>
-      <c r="AH35" t="inlineStr"/>
-      <c r="AI35" t="inlineStr"/>
-      <c r="AJ35" t="inlineStr"/>
-      <c r="AK35" t="inlineStr"/>
-      <c r="AL35" t="inlineStr"/>
-      <c r="AM35" t="inlineStr"/>
-      <c r="AN35" t="inlineStr"/>
-      <c r="AO35" t="inlineStr"/>
-      <c r="AP35" t="inlineStr"/>
-      <c r="AQ35" t="inlineStr"/>
-      <c r="AR35" t="inlineStr"/>
-      <c r="AS35" t="inlineStr"/>
-      <c r="AT35" t="inlineStr"/>
-      <c r="AU35" t="inlineStr"/>
-      <c r="AV35" t="inlineStr"/>
-      <c r="AW35" t="inlineStr"/>
-      <c r="AX35" t="inlineStr"/>
-      <c r="AY35" t="inlineStr"/>
-      <c r="AZ35" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/08_c074b9b2-7a8c-42fb-bac4-2024d4b136cb.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="51" customHeight="1">
-      <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1975_magic_puzzle_cube_4x4x4_at45</t>
+          <t>whl282_4810_portable_desk_fan_big</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4x4x4 Magic Cube – High Speed Stickerless Brain Teaser | Aditi</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>369</t>
-        </is>
+          <t>Portable Desk Fan – Quiet 3-Speed USB Power for Home &amp; Office | VoltDesk</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>455</v>
+      </c>
+      <c r="I36" t="n">
+        <v>299</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -11726,108 +10289,66 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Unlock your potential and challenge your mind with the Aditi 4x4x4 Magic Cube . This high-speed, stickerless puzzle is engineered for both budding enthusiasts and seasoned solvers in India, offering a captivating way to enhance cognitive skills and provide endless hours of fun for kids (8+) and adults alike. Experience the thrill of problem-solving and boost your mental agility with every smooth twist. Our premium 4x4x4 Magic Cube is designed for optimal performance and durability. Its vibrant, stickerless design ensures long-lasting enjoyment without the worry of fading or peeling, making it a reliable companion for daily practice or intense speedcubing sessions. Whether you&amp;#x27;re looking to improve focus, relieve stress, or simply enjoy a profound mental challenge, this magic cube is the pe&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr"/>
-      <c r="R36" t="inlineStr"/>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr"/>
+          <t>&lt;p&gt;Stay cool and comfortable anywhere with the **Mint green portable USB desk fan** from VoltDesk. Designed for ultimate convenience and efficiency, this compact yet powerful fan is your perfect companion for home, office, study, or travel. Experience a refreshing breeze without distracting noise, thanks to its advanced brushless motor and energy-saving USB power compatibility. Whether you&amp;#x27;re working, relaxing, or on the go, this Mint green portable USB desk fan ensures a steady, quiet airflow to keep you comfortable through the Indian summers. This versatile mini table fan is engineered for modern lifestyles, offering not just portability but also robust performance. Its thoughtful design includes a protective fence cover for enhanced safety, making it suitable for use around children and pe&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U36" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V36" t="inlineStr"/>
       <c r="W36" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_30437282-80e9-42ce-a2a2-e1bb473011f2.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_portable_desk_fan_big.jpg</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/29d12765-bde1-437a-9ab0-c0b73cad5b13.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_1.jpg</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_e62d1c29-3010-443c-ac6b-829bd45445e4.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810.jpg</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_ae7775d4-7b33-4167-bf4b-88c0e6a2b08e.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_2.jpg</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_30a53fdb-1f61-4122-8de4-0b68651b808b.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_3.jpg</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_71d7dbaa-8fa2-450f-8f71-20542c4863dd.jpg</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr"/>
-      <c r="AD36" t="inlineStr"/>
-      <c r="AE36" t="inlineStr"/>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="inlineStr"/>
-      <c r="AH36" t="inlineStr"/>
-      <c r="AI36" t="inlineStr"/>
-      <c r="AJ36" t="inlineStr"/>
-      <c r="AK36" t="inlineStr"/>
-      <c r="AL36" t="inlineStr"/>
-      <c r="AM36" t="inlineStr"/>
-      <c r="AN36" t="inlineStr"/>
-      <c r="AO36" t="inlineStr"/>
-      <c r="AP36" t="inlineStr"/>
-      <c r="AQ36" t="inlineStr"/>
-      <c r="AR36" t="inlineStr"/>
-      <c r="AS36" t="inlineStr"/>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AU36" t="inlineStr"/>
-      <c r="AV36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr"/>
-      <c r="AX36" t="inlineStr"/>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_5.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="51" customHeight="1">
-      <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>19458_knx_table_tennis_balls_6pc_cls_713</t>
+          <t>22669_mini_usb_fan_1pc</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3-Star Table Tennis Balls – Durable High Bounce Pack of 6</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>469</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+          <t>Portable USB Mini Fan – Compact &amp; Adjustable for Personal Cooling</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>475</v>
+      </c>
+      <c r="I37" t="n">
+        <v>219</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -11836,108 +10357,66 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Upgrade your play with our 3-Star Table Tennis Balls, designed for professional and amateur players seeking consistent bounce and durability. This pack of 6 regulation 40+ mm balls crafted from seamless ABS plastic guarantees stable flight and enhanced spin control for every rally. Key features Premium 3-star quality suitable for tournaments and practice sessions. Standard 40+ mm size ideal for official competitions and casual games. Seamless ABS plastic for long-lasting durability and consistent bounce. Optimized for stable flight trajectory and superior spin control. Bright orange color enhances visibility during fast, intense matches. Perfect for both indoor and outdoor table tennis tables. Materials &amp;amp; care Made from durable ABS plastic, these table tennis balls require no special maint&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr"/>
+          <t>&lt;p&gt;The Portable USB Mini Flexible Fan is your ideal solution for personal cooling on the go. With its bendable neck, you can direct airflow precisely where needed, making it perfect for workspaces, travel, and outdoor activities. Its compact design ensures portability without sacrificing performance, while being USB-powered means it’s compatible with laptops, power banks, and USB adapters for convenience anywhere you need a quick cool-down. Key features Flexible bendable neck for customized airflow direction USB powered for compatibility with laptops, power banks, and wall adapters Small, lightweight, and portable design ideal for travel and outdoor use Quiet operation suitable for office, study, or personal spaces Energy-efficient with durable construction for long-lasting use Materials &amp;amp; ca&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U37" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V37" t="inlineStr"/>
       <c r="W37" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/CLS-713-01.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-WOSKU-01.jpg</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/0807bdf8-093d-42ab-988f-01945577686a.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_4175b6cb-c6c1-4235-bf70-6662635ced44.jpg</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/TableTennisBalls-06.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-6.jpg</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/TableTennisBalls-04.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-04.jpg</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/TableTennisBalls-07.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-05.jpg</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/TableTennisBalls-02.jpg</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr"/>
-      <c r="AD37" t="inlineStr"/>
-      <c r="AE37" t="inlineStr"/>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="inlineStr"/>
-      <c r="AH37" t="inlineStr"/>
-      <c r="AI37" t="inlineStr"/>
-      <c r="AJ37" t="inlineStr"/>
-      <c r="AK37" t="inlineStr"/>
-      <c r="AL37" t="inlineStr"/>
-      <c r="AM37" t="inlineStr"/>
-      <c r="AN37" t="inlineStr"/>
-      <c r="AO37" t="inlineStr"/>
-      <c r="AP37" t="inlineStr"/>
-      <c r="AQ37" t="inlineStr"/>
-      <c r="AR37" t="inlineStr"/>
-      <c r="AS37" t="inlineStr"/>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AU37" t="inlineStr"/>
-      <c r="AV37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr"/>
-      <c r="AX37" t="inlineStr"/>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-size.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="51" customHeight="1">
-      <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
       <c r="F38" t="inlineStr">
         <is>
-          <t>15310_8in1_multi_cycling_bike_repair_too</t>
+          <t>6183_mini_usb_fan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>8-in-1 Portable Cycling Repair Tool Kit – Compact &amp; Durable</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
+          <t>Mini USB Fan Portable Mobile Phone Plug In Cooling Fan Soft Blades</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>599</v>
+      </c>
+      <c r="I38" t="n">
+        <v>229</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
@@ -11946,108 +10425,66 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Upgrade your bike maintenance with this essential 8-in-1 portable cycling repair tool kit, designed for convenience and versatility on the go. Whether you&amp;#x27;re a casual cyclist or a seasoned rider, this multi-tool kit makes quick repairs easy, featuring all the necessary tools packed into a compact, foldable design that fits comfortably in your pocket or bag. Built to withstand outdoor adventures and emergency repairs, this durable multi-tool includes screwdrivers and hex keys vital for bicycle repairs, general maintenance, or DIY tasks. Its lightweight yet sturdy construction ensures longevity, while the convenient clip or hook allows for effortless carrying during outdoor cycling, travel, or home repair projects. This multi-tool is an ideal companion for cyclists needing a reliable fix-any&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr"/>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr"/>
-      <c r="R38" t="inlineStr"/>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr"/>
+          <t>&lt;p&gt;Stay cool anywhere with this green portable USB-C phone fan. Designed for convenience, this mini fan plugs directly into your smartphone, offering instant personal cooling. Its soft, flexible blades ensure safety, making it perfect for travel, outdoor activities, or simply beating the summer heat. Key features Plugs directly into your mobile phone for instant personal cooling on the go Soft flexible blades are safe to touch and will not hurt fingers during use Compact and lightweight design fits easily in pockets, bags, and travel kits No batteries required as it draws power directly from your smartphone via USB-C Powerful airflow provides refreshing cooling during hot summer days Simple plug and play operation with no setup or charging needed Ideal for travel, commuting, outdoor events, a&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U38" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/folding-torx-key-set-1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-01.jpg</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_c3e345dc-70f4-4d51-83a4-c6858d690626.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_7568eccf-ac04-4a0b-a5ac-ed6145d5cecd.jpg</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/folding-torx-key-set-5.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-05.jpg</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/folding-torx-key-set-7.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-06.jpg</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/folding-torx-key-set-3.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-04.jpg</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/folding-torx-key-set-6.jpg</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr"/>
-      <c r="AD38" t="inlineStr"/>
-      <c r="AE38" t="inlineStr"/>
-      <c r="AF38" t="inlineStr"/>
-      <c r="AG38" t="inlineStr"/>
-      <c r="AH38" t="inlineStr"/>
-      <c r="AI38" t="inlineStr"/>
-      <c r="AJ38" t="inlineStr"/>
-      <c r="AK38" t="inlineStr"/>
-      <c r="AL38" t="inlineStr"/>
-      <c r="AM38" t="inlineStr"/>
-      <c r="AN38" t="inlineStr"/>
-      <c r="AO38" t="inlineStr"/>
-      <c r="AP38" t="inlineStr"/>
-      <c r="AQ38" t="inlineStr"/>
-      <c r="AR38" t="inlineStr"/>
-      <c r="AS38" t="inlineStr"/>
-      <c r="AT38" t="inlineStr"/>
-      <c r="AU38" t="inlineStr"/>
-      <c r="AV38" t="inlineStr"/>
-      <c r="AW38" t="inlineStr"/>
-      <c r="AX38" t="inlineStr"/>
-      <c r="AY38" t="inlineStr"/>
-      <c r="AZ38" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-size.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="39" ht="51" customHeight="1">
-      <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>6994_usb_7port_data_hub</t>
+          <t>22877_5_mode_mini_led_keychain_flashligh</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>7 Port USB Hub – 7-in-1 Individual Switches, LED Indicators | Compshop</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>545</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
+          <t>5 Mode Mini COB LED Keychain Flashlight with Carabiner Clip</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>539</v>
+      </c>
+      <c r="I39" t="n">
+        <v>329</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -12056,108 +10493,66 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>mobile accessories</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Are you constantly running out of USB ports on your laptop or PC? Upgrade your workspace connectivity with our versatile 7 Port USB Hub from Compshop. This essential accessory instantly expands your device&amp;#x27;s USB 2.0 capabilities, allowing you to connect multiple peripherals simultaneously without the hassle of constantly plugging and unplugging. Designed for efficiency and convenience, this USB splitter features individual on/off switches for each port, giving you complete control over your connected devices and helping to conserve power. Perfect for home, office, or travel, this data hub simplifies your digital life. Key Features Seven USB 2.0 Ports: Instantly add seven high-speed USB 2.0 ports to any compatible device, solving your connectivity challenges. Independent On/Off Switches: Ea&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr"/>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr"/>
+          <t>&lt;p&gt;Discover the versatility of the 5 Mode Mini COB LED Keychain Flashlight, your perfect companion for illumination on the go. This compact and powerful device, featuring a vibrant red and black design, ensures you always have light when you need it most. Ideal for everyday carry, it easily attaches to your keys or bag, providing reliable lighting for various situations. Key features Five lighting modes: high, low, strobe, SOS, and spotlight for adaptable use. Powerful COB LED panel offers bright, wide-area flood lighting. Secondary spotlight torch delivers a focused beam for longer distances. Built-in carabiner clip allows easy attachment to keys, bags, or belts. Ultra-compact, pocket-sized, and lightweight for effortless portability. Durable ABS plastic construction withstands daily use and&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U39" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V39" t="inlineStr"/>
       <c r="W39" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/USB-01.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-01.jpg</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_8085c215-2773-474f-b73c-aff40e4e45d8.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_8c5297b5-e3ce-4c22-8bcd-73584449baa9.jpg</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/USB-2.0-02.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-02.jpg</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/USB-04.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-04.jpg</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/USB-05.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-03.jpg</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/USB-06.jpg</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr"/>
-      <c r="AD39" t="inlineStr"/>
-      <c r="AE39" t="inlineStr"/>
-      <c r="AF39" t="inlineStr"/>
-      <c r="AG39" t="inlineStr"/>
-      <c r="AH39" t="inlineStr"/>
-      <c r="AI39" t="inlineStr"/>
-      <c r="AJ39" t="inlineStr"/>
-      <c r="AK39" t="inlineStr"/>
-      <c r="AL39" t="inlineStr"/>
-      <c r="AM39" t="inlineStr"/>
-      <c r="AN39" t="inlineStr"/>
-      <c r="AO39" t="inlineStr"/>
-      <c r="AP39" t="inlineStr"/>
-      <c r="AQ39" t="inlineStr"/>
-      <c r="AR39" t="inlineStr"/>
-      <c r="AS39" t="inlineStr"/>
-      <c r="AT39" t="inlineStr"/>
-      <c r="AU39" t="inlineStr"/>
-      <c r="AV39" t="inlineStr"/>
-      <c r="AW39" t="inlineStr"/>
-      <c r="AX39" t="inlineStr"/>
-      <c r="AY39" t="inlineStr"/>
-      <c r="AZ39" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-size.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="51" customHeight="1">
-      <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4969_toothbrush_case_6pc</t>
+          <t>13978_mini_light_up_torch</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>6pc Plastic Toothbrush Covers - Hygienic Travel Protection</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>439</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
+          <t>Mini LED Torch – Compact, Portable &amp; Bright Light</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>629</v>
+      </c>
+      <c r="I40" t="n">
+        <v>229</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
@@ -12166,108 +10561,66 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Keep your oral hygiene pristine wherever you go with these 6pc plastic toothbrush travel cases. Designed for the modern traveler and daily commuter, these hygienic protectors ensure your toothbrush remains clean, dry, and free from contaminants, offering peace of mind for your personal care. Key features Ensures Optimal Hygiene: Crafted from food-grade plastic, these covers maintain your toothbrush&amp;#x27;s cleanliness and protect it from external contaminants, promoting superior oral health. Designed for Dryness: Featuring a small ventilation hole at the bottom, these covers prevent moisture buildup, keeping your toothbrush dry and ready for its next use. Durable Travel Companion: Protects your toothbrush from dust, dirt, and compression deformation, making it an essential, lightweight accessory&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr"/>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr"/>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr"/>
-      <c r="R40" t="inlineStr"/>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr"/>
+          <t>&lt;p&gt;Discover the convenience of our Blue mini disco ball light wand, a compact and portable solution for reliable lighting and entertainment. This mini disco ball light wand is ideal for parties, events, or simply adding a fun ambiance to any room, providing bright, colourful illumination where you need it most. Lightweight and durable, it&amp;#x27;s designed for easy carrying and delivers efficient, long-lasting light with a captivating disco ball effect. Key features Compact size (10 cm length) for ultimate portability and easy handling Bright LED lights with a captivating mini disco ball effect Lightweight design, weighing just 35 grams, for effortless carrying Durable construction suitable for various indoor and outdoor settings Simple on/off switch for quick and easy operation Perfect for parties,&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U40" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V40" t="inlineStr"/>
       <c r="W40" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4969.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/13978.png</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/01_85ac7dc5-15d2-4c00-9b39-3c441186484f.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/3a5b73d1-bf19-4022-8c2a-db440ea0a35d.jpg</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/04_467c7a30-5f8b-4745-a5da-8701bf30e331.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_5f2c06c6-3367-44a6-be67-2e2f8fdcb255.jpg</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/05_3c1e279d-53ce-4e5e-908e-5d82843cd04b.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_27406132-5058-4c6f-b0d0-3393c17bc9b7.jpg</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/02_38626bd9-ca32-4b7b-8831-73b2420d9919.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_5742c6ca-7314-4e59-a2fa-54a570fd9d09.jpg</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/08_8d7ece0a-7ac0-43a4-98f4-97f77512431d.jpg</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr"/>
-      <c r="AD40" t="inlineStr"/>
-      <c r="AE40" t="inlineStr"/>
-      <c r="AF40" t="inlineStr"/>
-      <c r="AG40" t="inlineStr"/>
-      <c r="AH40" t="inlineStr"/>
-      <c r="AI40" t="inlineStr"/>
-      <c r="AJ40" t="inlineStr"/>
-      <c r="AK40" t="inlineStr"/>
-      <c r="AL40" t="inlineStr"/>
-      <c r="AM40" t="inlineStr"/>
-      <c r="AN40" t="inlineStr"/>
-      <c r="AO40" t="inlineStr"/>
-      <c r="AP40" t="inlineStr"/>
-      <c r="AQ40" t="inlineStr"/>
-      <c r="AR40" t="inlineStr"/>
-      <c r="AS40" t="inlineStr"/>
-      <c r="AT40" t="inlineStr"/>
-      <c r="AU40" t="inlineStr"/>
-      <c r="AV40" t="inlineStr"/>
-      <c r="AW40" t="inlineStr"/>
-      <c r="AX40" t="inlineStr"/>
-      <c r="AY40" t="inlineStr"/>
-      <c r="AZ40" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_b71c037b-f863-4f69-ab9b-53e09f4b7102.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="51" customHeight="1">
-      <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6076_4in1_medicine_crusher</t>
+          <t>6251_5in1_multifunction_brush</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>4-in-1 Portable Pill Cutter &amp; Crusher with Smart Storage</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>475</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+          <t>Computer Cleaning Kit – 5-in-1 Multi-Function PC &amp; Keyboard | Dustiva</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>479</v>
+      </c>
+      <c r="I41" t="n">
+        <v>249</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -12276,108 +10629,66 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Simplify your daily medication routine with the Organivo 4-in-1 Portable Pill Cutter &amp;amp; Crusher. Designed for ultimate convenience and efficiency, this compact device combines four essential functions to ensure you manage your pills effortlessly. Whether you need to accurately split tablets, crush them into fine powder, or keep them neatly organized, this versatile tool is your perfect health companion. Its durable plastic construction and thoughtful design make it ideal for home use and on-the-go. Precisely Cuts Tablets: Effortlessly divide various medication sizes into accurate halves, ensuring correct dosages and easier consumption for all users. Enjoy 4-in-1 Functionality: Seamlessly combine a precise pill cutter, effective crusher, and two partitioned storage compartments in one compac&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr"/>
-      <c r="R41" t="inlineStr"/>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr"/>
+          <t>&lt;p&gt;Keep your digital world spotless with the ultimate Computer Cleaning Kit from Dustiva. This 5-in-1 multi-function tool is meticulously designed to tackle every speck of dust and grime from your precious electronics, ensuring they look new and perform optimally. Perfect for gamers, professionals, and everyday users in India, this kit is your go-to solution for comprehensive device maintenance, enhancing longevity and performance for your PC, keyboard, and earbuds. Key features 5-in-1 Comprehensive Cleaning: Includes a metal pen tip for stubborn grime, a high-density brush, a soft flocking sponge for delicate surfaces, a robust keyboard brush, and an easy-to-use keycap puller. Precision Earbuds Cleaning: The delicate flocking sponge and metal pen tip are perfect for cleaning wireless earbud&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U41" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V41" t="inlineStr"/>
       <c r="W41" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/6076_4in1_medicine_crusher.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/3image_2793e13d-4fea-4a76-b3d9-af8a42520c96.jpg</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/6076.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/1image_c52a168c-ae61-4870-8128-c0d76696cef6_1.jpg</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_09a9f15b-3b55-43c6-b63d-de38d27eb142.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/2image_be686450-a4f9-4053-aad1-666afcaa5443.jpg</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/09_0425a143-dd4c-4800-8b22-bf48020577ac.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/7image_34fbcf4e-da9d-4bbb-a106-90222c272fa0.jpg</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11_ea0bb9d6-30a8-4fdc-b4f6-afe9049a8f01.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/4image_cc4a377e-c606-41f2-bfb3-251d61415521.jpg</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/10_064a8b7b-64d0-450b-aa04-436ca13d4849.jpg</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr"/>
-      <c r="AD41" t="inlineStr"/>
-      <c r="AE41" t="inlineStr"/>
-      <c r="AF41" t="inlineStr"/>
-      <c r="AG41" t="inlineStr"/>
-      <c r="AH41" t="inlineStr"/>
-      <c r="AI41" t="inlineStr"/>
-      <c r="AJ41" t="inlineStr"/>
-      <c r="AK41" t="inlineStr"/>
-      <c r="AL41" t="inlineStr"/>
-      <c r="AM41" t="inlineStr"/>
-      <c r="AN41" t="inlineStr"/>
-      <c r="AO41" t="inlineStr"/>
-      <c r="AP41" t="inlineStr"/>
-      <c r="AQ41" t="inlineStr"/>
-      <c r="AR41" t="inlineStr"/>
-      <c r="AS41" t="inlineStr"/>
-      <c r="AT41" t="inlineStr"/>
-      <c r="AU41" t="inlineStr"/>
-      <c r="AV41" t="inlineStr"/>
-      <c r="AW41" t="inlineStr"/>
-      <c r="AX41" t="inlineStr"/>
-      <c r="AY41" t="inlineStr"/>
-      <c r="AZ41" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/5image_7e463727-3a9c-4118-8718-49609b03d19a.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="51" customHeight="1">
-      <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr">
         <is>
-          <t>17952_soft_eraser_30pc_set</t>
+          <t>6124_4pc_multi_p_mob_stand</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4B Erasers – Smudge-Free 30-Pack for Students | TinyTrendy</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>559</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
+          <t>Wall Mounted Phone Holder – Multi-functional Organizer | Organivo</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>515</v>
+      </c>
+      <c r="I42" t="n">
+        <v>239</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -12386,108 +10697,66 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Discover the ultimate solution for clean, smudge-free corrections with our premium 4B Erasers 30-pack from TinyTrendy. Engineered for precision and efficiency, these high-quality yellow erasers are an indispensable tool for students, artists, and office professionals across India. Say goodbye to frustrating smudges and paper damage, and welcome a new era of pristine work and neat documents. Our 4B Erasers are specifically designed to tackle graphite pencil marks with effortless ease. Each eraser in this generous bulk pack promises a smooth, clean erase every single time, preserving the integrity of your notebooks, drawings, and important documents. Whether you&amp;#x27;re preparing for exams, perfecting a sketch, or simply tidying up daily notes, these erasers offer reliable performance that you ca&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr"/>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr"/>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr"/>
-      <c r="R42" t="inlineStr"/>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr"/>
+          <t>&lt;p&gt;Transform your living space and keep essentials neatly organised with our innovative Wall Mounted Phone Holder . This multi-functional organiser is designed to declutter your bedside, desk, or kitchen, providing a dedicated spot for your smartphone and remote controls. Say goodbye to misplaced remotes and tangled charging cables; this sleek solution from Organivo ensures everything is always within reach and perfectly tidy. Key features Dual Functionality: Serves as both a secure wall mounted phone holder and a convenient remote control organizer. Integrated Charging Port: Thoughtfully designed with a bottom opening, allowing you to charge your phone effortlessly while it rests in the holder. Easy, Damage-Free Installation: Features strong adhesive backing for quick and simple mounting on&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U42" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V42" t="inlineStr"/>
       <c r="W42" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_1a918657-9490-4364-8fea-823a3a184fc9.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/3b9a0d7f-a23d-4029-b99f-358519825831.jpg</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/887a20c7-07d9-46ac-a53a-1cb54bde788b.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/01_ad372f27-1965-4137-b508-425ee0c62640.jpg</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_1eaaa9c1-9821-4bf0-9aaf-7400402aaab1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_120dc563-a380-41e0-a7ac-df7cd114dd49.jpg</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_36dcea34-1f2a-4fe1-b2d8-523bc5559420.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/07_eebea5d0-1b3a-4f9d-a82e-b8e5ac760d57.jpg</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_724660c0-179c-4106-9657-62aff8ad665e.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/04_1667da0d-6ab3-4afb-8014-6ef3b3cf7eb7.jpg</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_179e5bf1-abc1-4d54-88c8-199f3cc9d0e5.jpg</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr"/>
-      <c r="AD42" t="inlineStr"/>
-      <c r="AE42" t="inlineStr"/>
-      <c r="AF42" t="inlineStr"/>
-      <c r="AG42" t="inlineStr"/>
-      <c r="AH42" t="inlineStr"/>
-      <c r="AI42" t="inlineStr"/>
-      <c r="AJ42" t="inlineStr"/>
-      <c r="AK42" t="inlineStr"/>
-      <c r="AL42" t="inlineStr"/>
-      <c r="AM42" t="inlineStr"/>
-      <c r="AN42" t="inlineStr"/>
-      <c r="AO42" t="inlineStr"/>
-      <c r="AP42" t="inlineStr"/>
-      <c r="AQ42" t="inlineStr"/>
-      <c r="AR42" t="inlineStr"/>
-      <c r="AS42" t="inlineStr"/>
-      <c r="AT42" t="inlineStr"/>
-      <c r="AU42" t="inlineStr"/>
-      <c r="AV42" t="inlineStr"/>
-      <c r="AW42" t="inlineStr"/>
-      <c r="AX42" t="inlineStr"/>
-      <c r="AY42" t="inlineStr"/>
-      <c r="AZ42" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/08_a3feea56-c6d4-4edb-8158-53709169177f.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="51" customHeight="1">
-      <c r="A43" t="inlineStr"/>
-      <c r="B43" t="inlineStr"/>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>whl334_92707_link_hub_black</t>
+          <t>23927_4_port_usb_to_usb</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4-Port USB 3.0 Hub, Plug &amp; Play High-Speed USB Splitter for Laptop and PC</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>539</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>379</t>
-        </is>
+          <t>USB to Four Port USB Hub Multi Interface Adapter for Laptop and Computer</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>475</v>
+      </c>
+      <c r="I43" t="n">
+        <v>289</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -12496,104 +10765,66 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Experience seamless connectivity with this 4-port USB 3.0 hub, designed for high-speed data transfer and effortless device expansion. This plug and play USB splitter is ideal for connecting multiple peripherals to your laptop or PC without hassle. Key features Expands your device&amp;#x27;s connectivity with four USB 3.0 ports Offers high-speed data transfer for efficient workflow Features a convenient plug and play design for instant use Includes a blue LED indicator to show active connection status Compact and lightweight, perfect for travel and everyday carry FAQ Q1: What devices can I connect to this 4-port USB 3.0 hub? A: You can connect a variety of USB devices such as keyboards, mice, pen drives, hard drives, printers, and other USB accessories. Q2: Is this USB hub compatible with both lapto&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr"/>
-      <c r="R43" t="inlineStr"/>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr"/>
+          <t>&lt;p&gt;Expand your connectivity with this versatile Silver 4-port USB hub adapter . Designed for both laptops and desktop computers, this compact device effortlessly transforms a single USB port into four, allowing you to connect multiple peripherals simultaneously. Ideal for decluttering your workspace or enhancing your travel accessory kit, this hub ensures seamless data transfer and device connectivity for everyday use. Key features Multi-interface USB hub design for expanded connectivity Standard USB input connector for universal compatibility Connects multiple USB accessories with ease Compact and lightweight body for portability Flexible attached connecting cable for convenient placement Simple plug-and-use design requires no drivers Suitable for both desk and on-the-go use Sleek silver and&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U43" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr"/>
       <c r="W43" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/RGuPQ5mJdX.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-1.jpg</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/lKpU7aeQbu.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-sku.jpg</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/DINwM09oWJ.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-2.jpg</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4GxoJDjOh4.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-3.jpg</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/tCFK5ZVzP6.png</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr"/>
-      <c r="AC43" t="inlineStr"/>
-      <c r="AD43" t="inlineStr"/>
-      <c r="AE43" t="inlineStr"/>
-      <c r="AF43" t="inlineStr"/>
-      <c r="AG43" t="inlineStr"/>
-      <c r="AH43" t="inlineStr"/>
-      <c r="AI43" t="inlineStr"/>
-      <c r="AJ43" t="inlineStr"/>
-      <c r="AK43" t="inlineStr"/>
-      <c r="AL43" t="inlineStr"/>
-      <c r="AM43" t="inlineStr"/>
-      <c r="AN43" t="inlineStr"/>
-      <c r="AO43" t="inlineStr"/>
-      <c r="AP43" t="inlineStr"/>
-      <c r="AQ43" t="inlineStr"/>
-      <c r="AR43" t="inlineStr"/>
-      <c r="AS43" t="inlineStr"/>
-      <c r="AT43" t="inlineStr"/>
-      <c r="AU43" t="inlineStr"/>
-      <c r="AV43" t="inlineStr"/>
-      <c r="AW43" t="inlineStr"/>
-      <c r="AX43" t="inlineStr"/>
-      <c r="AY43" t="inlineStr"/>
-      <c r="AZ43" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-7.jpg</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="51" customHeight="1">
-      <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>whl197_70191_spinny_twist_at242</t>
+          <t>23597_usb_rechargeable_led_flashlight</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>3-Wheel Spinning Bead Puzzle Toy – Spinny Twist Fidget Toy for Kids (Mix Colur)</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>429</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+          <t>USB Rechargeable LED Flashlight for Travel with Lamp Mode</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>559</v>
+      </c>
+      <c r="I44" t="n">
+        <v>349</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -12602,108 +10833,66 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Toys &amp; Games</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Make playtime more exciting with this Spinny Twist Bead Puzzle Toy . This colorful 3-wheel rotating puzzle lets kids spin and move the beads to match colors and create fun patterns. The smooth spinning design keeps children engaged while helping develop hand-eye coordination, focus, and problem-solving skills . Made with durable, child-safe plastic , the toy is lightweight and easy to hold, making it perfect for kids at home, school, or travel.&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr"/>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr"/>
+          <t>&lt;p&gt;USB Rechargeable LED Flashlight for Travel with Soft Lamp Mode for Trips, Camping and Night Use (1 Pc) Description :- A phone torch drains the battery you need for maps and calls, which is the wrong trade on a trip. This flashlight does the lighting so the phone does not have to. The beam covers a dark path or a hotel corridor, and the soft lamp mode gives enough light to find something in a bag without waking the person next to you. USB charging means the same cable that charges your phone charges this, so there is nothing extra to pack. Key Features Saves the phone battery you need for maps and calls Beam covers a dark path, corridor or campsite Soft lamp mode for finding things in a bag without waking anyone Charges off the same USB cable as your phone No batteries to carry or buy on th&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U44" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V44" t="inlineStr"/>
       <c r="W44" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/UOTiOKm3hf.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/c23b24ee-e8ec-4f49-a6a3-7fd08ff805ca.jpg</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/De24j6Dojm.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/d52ec2cc-e497-44d8-9c22-089d55f3fd44.jpg</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/VW5Y8WgLPz.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23597-usb-rechargeable-led-flashlight-3.jpg</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/67vYVpQWYw.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23597-usb-rechargeable-led-flashlight-4.jpg</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/nYqhVzDh48.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23597-usb-rechargeable-led-flashlight-5.jpg</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/seXvklDhup.png</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr"/>
-      <c r="AD44" t="inlineStr"/>
-      <c r="AE44" t="inlineStr"/>
-      <c r="AF44" t="inlineStr"/>
-      <c r="AG44" t="inlineStr"/>
-      <c r="AH44" t="inlineStr"/>
-      <c r="AI44" t="inlineStr"/>
-      <c r="AJ44" t="inlineStr"/>
-      <c r="AK44" t="inlineStr"/>
-      <c r="AL44" t="inlineStr"/>
-      <c r="AM44" t="inlineStr"/>
-      <c r="AN44" t="inlineStr"/>
-      <c r="AO44" t="inlineStr"/>
-      <c r="AP44" t="inlineStr"/>
-      <c r="AQ44" t="inlineStr"/>
-      <c r="AR44" t="inlineStr"/>
-      <c r="AS44" t="inlineStr"/>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AU44" t="inlineStr"/>
-      <c r="AV44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr"/>
-      <c r="AX44" t="inlineStr"/>
-      <c r="AY44" t="inlineStr"/>
-      <c r="AZ44" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23597-usb-rechargeable-led-flashlight-6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="45" ht="51" customHeight="1">
-      <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
       <c r="F45" t="inlineStr">
         <is>
-          <t>18995_anti_theft_3_digit_wire_lock_1pc</t>
+          <t>1637_usb_bike_light</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>3-Digit Combination Anti-Theft Padlock – Keyless Security &amp; Built-In Wire</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
+          <t>USB Rechargeable Bicycle Headlight with Handlebar Mount for Night Riding</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>499</v>
+      </c>
+      <c r="I45" t="n">
+        <v>299</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
@@ -12712,108 +10901,66 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Smart Gadgets</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Secure your valuables effortlessly with our 3-Digit Combination Anti-Theft Padlock, featuring a built-in wire for versatile protection without keys. This compact, durable lock ensures peace of mind for your belongings at home or on the go. Key features Robust Durability: Zinc alloy core and rustproof steel wire wrapped in a protective PVC coating resist scratches and tampering. Keyless Convenience: Easily set and use your personal 3-digit combination to unlock quickly without keys. Compact &amp;amp; Lightweight: Ideal for travel, it provides strong security without extra bulk. Multipurpose Use: Perfect for securing bikes, helmets, suitcases, gates, and more with versatile wire locking. Ready to Use: Includes one strong padlock with integrated wire for immediate protection. FAQ Q1: How do I set the&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr"/>
-      <c r="R45" t="inlineStr"/>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr"/>
+          <t>&lt;p&gt;Enhance your cycling safety with our USB rechargeable bicycle headlight , designed for superior visibility during night rides and low-light conditions. This reliable headlight ensures you can see the path ahead clearly and be seen by others, making your evening commutes and early morning adventures safer. Its compact design and easy handlebar mount make it a convenient and essential accessory for every cyclist. Key features Bright front beam provides excellent visibility in low-light conditions. USB rechargeable design eliminates the need for disposable batteries, offering an eco-friendly solution. Secure mounting bracket easily attaches to bicycle handlebars for stable positioning. Compact and lightweight body ensures it won&amp;#x27;t add unnecessary bulk to your bike. Simple control button allow&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U45" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V45" t="inlineStr"/>
       <c r="W45" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/18995_anti_theft_3_digit_wire_lock_1pc.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-01.jpg</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/325_57aa9611-3192-4790-a6c4-f1c35ed9d863.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-02.jpg</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_df97e7f6-26aa-4802-bafc-bb3dc99fe21c.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-03.jpg</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_52b6d37e-e647-4016-826b-241dc58c0dfc.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-04.jpg</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_9eccaca9-c684-410b-909c-3df0bd42ce29.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-05.jpg</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/09_8c0bf37f-826a-4e8a-88eb-d35417216fdb.jpg</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr"/>
-      <c r="AD45" t="inlineStr"/>
-      <c r="AE45" t="inlineStr"/>
-      <c r="AF45" t="inlineStr"/>
-      <c r="AG45" t="inlineStr"/>
-      <c r="AH45" t="inlineStr"/>
-      <c r="AI45" t="inlineStr"/>
-      <c r="AJ45" t="inlineStr"/>
-      <c r="AK45" t="inlineStr"/>
-      <c r="AL45" t="inlineStr"/>
-      <c r="AM45" t="inlineStr"/>
-      <c r="AN45" t="inlineStr"/>
-      <c r="AO45" t="inlineStr"/>
-      <c r="AP45" t="inlineStr"/>
-      <c r="AQ45" t="inlineStr"/>
-      <c r="AR45" t="inlineStr"/>
-      <c r="AS45" t="inlineStr"/>
-      <c r="AT45" t="inlineStr"/>
-      <c r="AU45" t="inlineStr"/>
-      <c r="AV45" t="inlineStr"/>
-      <c r="AW45" t="inlineStr"/>
-      <c r="AX45" t="inlineStr"/>
-      <c r="AY45" t="inlineStr"/>
-      <c r="AZ45" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-06.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="51" customHeight="1">
-      <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr">
         <is>
-          <t>23852_kids_tumbler_with_lid_n_straw_900m</t>
+          <t>whl193_66653_dryfruit_box_open_square_de</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ML Glass Tumbler with Handle – Stylish &amp; Durable Drinkware for Everyday Use</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>319</t>
-        </is>
+          <t>Royal Decorative Dry Fruit Box for Festive Serving &amp; Gifting</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>449</v>
+      </c>
+      <c r="I46" t="n">
+        <v>349</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -12822,108 +10969,61 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>&lt;p&gt;This glass tumbler with handle offers a stylish and functional way to enjoy your favorite beverages. Crafted from durable transparent glass, it features an ergonomic handle for comfortable grip and a spill-resistant lid with a reusable straw, making it ideal for home, office, or travel. The modern ribbed design adds an elegant touch to your drinkware collection, while the eco-friendly straw encourages sustainable sipping. Whether you’re having coffee, juice, smoothies, or iced tea, this multipurpose tumbler ensures a chic experience every time. Key features Elegant ribbed design for a modern look Transparent glass body showcases your drinks vibrant Spill-resistant lid with straw opening for convenience Ergonomic handle for comfortable gripping Includes reusable straw for eco-friendly usage&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr"/>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr"/>
+          <t>&lt;p&gt;Elevate your entertaining and gifting with the Royal Decorative Dry Fruit Box, a stunning piece designed to add elegance to any occasion. Perfect for showcasing an array of treats, from crunchy nuts to delightful sweets, this box combines traditional charm with practical functionality. Its exquisite design makes it a focal point on any table, embodying a sense of luxury and thoughtful presentation for both everyday use and special celebrations. Showcase Treats Elegantly: Designed for stylish serving and storage, this box beautifully displays nuts, dry fruits, sweets, and snacks, making every presentation special. Adds Royal Decorative Flair: Featuring a premium decorative design, it infuses a luxurious and traditional touch into your dining table and festive home decor instantly. Offers Ea&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U46" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr"/>
       <c r="W46" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/DA057j3tzy.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/iK4vbVtSFD.jpg</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jwvrzAy79Z.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/oVYvpUeGUz.jpg</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/gab4W5acIz.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/VxXcStBWAR.jpg</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/vg17b0XX8d.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/mQd4WElKJY.jpg</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/HEfTAMybQ6.jpg</t>
-        </is>
-      </c>
-      <c r="AB46" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/gC7sRk2x0h.jpg</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr"/>
-      <c r="AD46" t="inlineStr"/>
-      <c r="AE46" t="inlineStr"/>
-      <c r="AF46" t="inlineStr"/>
-      <c r="AG46" t="inlineStr"/>
-      <c r="AH46" t="inlineStr"/>
-      <c r="AI46" t="inlineStr"/>
-      <c r="AJ46" t="inlineStr"/>
-      <c r="AK46" t="inlineStr"/>
-      <c r="AL46" t="inlineStr"/>
-      <c r="AM46" t="inlineStr"/>
-      <c r="AN46" t="inlineStr"/>
-      <c r="AO46" t="inlineStr"/>
-      <c r="AP46" t="inlineStr"/>
-      <c r="AQ46" t="inlineStr"/>
-      <c r="AR46" t="inlineStr"/>
-      <c r="AS46" t="inlineStr"/>
-      <c r="AT46" t="inlineStr"/>
-      <c r="AU46" t="inlineStr"/>
-      <c r="AV46" t="inlineStr"/>
-      <c r="AW46" t="inlineStr"/>
-      <c r="AX46" t="inlineStr"/>
-      <c r="AY46" t="inlineStr"/>
-      <c r="AZ46" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/YAiVLYzI9T.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="51" customHeight="1">
-      <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
       <c r="F47" t="inlineStr">
         <is>
-          <t>7302_ladies_l_print_socks</t>
+          <t>14409_gold_metal_medal_n_tricolor_ribbon</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ankle Length Socks – Soft Cotton Breathable Combo | FitFuzion</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>485</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
+          <t>Gold Medal Gift with Tricolor Ribbon for Achievers, Kids and Winners (1 Pc)</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>505</v>
+      </c>
+      <c r="I47" t="n">
+        <v>219</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -12932,108 +11032,66 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Step into unparalleled comfort with FitFuzion&amp;#x27;s premium Ankle Length Socks , designed for the modern Indian man. Crafted from a luxurious blend of combed cotton, polyamide, and elastane, these socks offer superior breathability and a soft, skin-friendly feel. Perfect for everyday wear, our ankle length socks keep your feet fresh and comfortable, whether you&amp;#x27;re at work, hitting the gym, or relaxing at home. Experience the ideal combination of style, comfort, and durability that lasts all day long. Key Features Supreme Comfort: Made from high-quality combed cotton, ensuring a super soft and lightweight feel against your skin. Breathable Design: Allows your feet to breathe, keeping them cool and dry even during strenuous activities. Odour-Resistant: Infused with an odour-resistant formula tha&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr"/>
-      <c r="N47" t="inlineStr"/>
-      <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr"/>
-      <c r="R47" t="inlineStr"/>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr"/>
+          <t>&lt;p&gt;Celebrate success and milestones with this elegant Gold Medal Gift. Featuring a shiny gold finish and a vibrant tricolor ribbon, this award medal is a perfect keepsake for achievers of all ages. Ideal for recognising academic excellence, sports victories, or simply celebrating personal achievements, it makes a memorable token of pride and appreciation. Key features Gift of Pride: Celebrate achievements big and small. Gold Finish: Shiny, premium look. Tricolor Ribbon: Comfortable to wear around the neck. For All Ages: Suitable for kids and adults. Keepsake Gift: A lasting memory of a special moment. Many Occasions: Results, birthdays, sports and competitions. Lightweight: Easy to wear and carry. Easy Care: Wipe with a soft cloth to keep it shining. Materials &amp;amp; care Material: Metal with Fabr&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U47" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V47" t="inlineStr"/>
       <c r="W47" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Socks-01.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_439c02be-7e1a-45ae-9e16-fd6413cd5580.jpg</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_5dd250be-21e2-4119-a2ed-090e056fa387.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/14409.jpg</t>
         </is>
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Socks-03.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_d002869f-bad7-469c-8675-e6142dd728bc.jpg</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Socks-04.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_7de3e992-f6bf-4f9d-b0bb-4c4ac376125c.jpg</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Socks-05.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_800a7bc3-2477-4210-b220-6e490514726e.jpg</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Socks-07.jpg</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr"/>
-      <c r="AD47" t="inlineStr"/>
-      <c r="AE47" t="inlineStr"/>
-      <c r="AF47" t="inlineStr"/>
-      <c r="AG47" t="inlineStr"/>
-      <c r="AH47" t="inlineStr"/>
-      <c r="AI47" t="inlineStr"/>
-      <c r="AJ47" t="inlineStr"/>
-      <c r="AK47" t="inlineStr"/>
-      <c r="AL47" t="inlineStr"/>
-      <c r="AM47" t="inlineStr"/>
-      <c r="AN47" t="inlineStr"/>
-      <c r="AO47" t="inlineStr"/>
-      <c r="AP47" t="inlineStr"/>
-      <c r="AQ47" t="inlineStr"/>
-      <c r="AR47" t="inlineStr"/>
-      <c r="AS47" t="inlineStr"/>
-      <c r="AT47" t="inlineStr"/>
-      <c r="AU47" t="inlineStr"/>
-      <c r="AV47" t="inlineStr"/>
-      <c r="AW47" t="inlineStr"/>
-      <c r="AX47" t="inlineStr"/>
-      <c r="AY47" t="inlineStr"/>
-      <c r="AZ47" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_c18f5d4c-5cec-4262-b366-1e49c92c7c1d.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="51" customHeight="1">
-      <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr"/>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr">
         <is>
-          <t>8644_wagtail_brown_abrasive_wheel_3pc_no</t>
+          <t>whl282_19630_krishna_flute_metal_keychai</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Abrasive Buffing Wheel Set – 3mm Shank for Rotary Tools | Wagtail</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>589</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>219</t>
-        </is>
+          <t>Krishna Flute Keychain – Durable Stainless Steel Spiritual Accessory</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>499</v>
+      </c>
+      <c r="I48" t="n">
+        <v>219</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -13042,108 +11100,66 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Achieve professional-grade finishes and effortless restoration with the Wagtail Abrasive Buffing Wheel Set. Designed for precision and durability, this essential rotary tool accessory is perfect for tackling tough rust, corrosion, and various polishing tasks on a multitude of surfaces. Each abrasive buffing wheel in this 3-piece set offers superior performance, making your DIY projects and professional jobs smoother and more efficient. Whether you&amp;#x27;re working on delicate engraving or heavy-duty derusting, these versatile tools provide the perfect solution for a flawless finish. Crafted for Indian DIY enthusiasts and professional artisans alike, the Wagtail Abrasive Buffing Wheel Set is a must-have for any workshop. Its 3mm shank ensures compatibility with most standard rotary tools and hand&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr"/>
-      <c r="R48" t="inlineStr"/>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr"/>
+          <t>&lt;p&gt;Experience divine blessings with our Krishna flute keychain, crafted from premium stainless steel for durability and spiritual elegance. This keychain features the iconic image of Lord Krishna holding his mystical flute, symbolizing love, harmony, and devotion. Perfect for organizing car, bike, home, or office keys while keeping the positive energy of Krishna close. Key features Intricate Krishna flute design with precise laser-cut detailing High-quality stainless steel resistant to rust and wear Compact and lightweight for effortless everyday carry Strong metal ring securely holds multiple keys Polished finish adding a sleek and stylish look Ideal as a thoughtful gift for Janmashtami, Diwali, or other festivities Combines spiritual significance with practical utility Materials &amp;amp; care Made&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U48" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V48" t="inlineStr"/>
       <c r="W48" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/8644_wagtail_brown_abrasive_wheel_3pc_no39.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-02_166f48cb-9946-410b-83a4-4a6dd6a4f3be.jpg</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/b60af031-74c5-4d08-8f5e-be3eb70b45db.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/c5751ef3-5e9c-4060-85ef-a406ca3f909a_63b6b3a7-3e12-49b2-8d0c-828e9063dce3.jpg</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_5d0c8ea8-e7ff-4c9a-91d1-1065f5d208b8.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-01_dc3e06fe-f38d-4392-8ca0-bdb67e367317.jpg</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_676bdff3-5d50-45a7-aa08-e3504a5ba555.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-03_7878e90e-af45-49c2-b90b-a25ed15e63ca.jpg</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_b2d5ea1d-52b2-4aff-bf0e-1af9e2a785d7.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-05_eabc8cf7-87cd-4d8b-aa87-8176020672c1.jpg</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_f730f28a-29ec-4f2f-bc89-7b654406d443.jpg</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr"/>
-      <c r="AD48" t="inlineStr"/>
-      <c r="AE48" t="inlineStr"/>
-      <c r="AF48" t="inlineStr"/>
-      <c r="AG48" t="inlineStr"/>
-      <c r="AH48" t="inlineStr"/>
-      <c r="AI48" t="inlineStr"/>
-      <c r="AJ48" t="inlineStr"/>
-      <c r="AK48" t="inlineStr"/>
-      <c r="AL48" t="inlineStr"/>
-      <c r="AM48" t="inlineStr"/>
-      <c r="AN48" t="inlineStr"/>
-      <c r="AO48" t="inlineStr"/>
-      <c r="AP48" t="inlineStr"/>
-      <c r="AQ48" t="inlineStr"/>
-      <c r="AR48" t="inlineStr"/>
-      <c r="AS48" t="inlineStr"/>
-      <c r="AT48" t="inlineStr"/>
-      <c r="AU48" t="inlineStr"/>
-      <c r="AV48" t="inlineStr"/>
-      <c r="AW48" t="inlineStr"/>
-      <c r="AX48" t="inlineStr"/>
-      <c r="AY48" t="inlineStr"/>
-      <c r="AZ48" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-06_016cbeeb-315b-4913-8cbb-c622007878d7.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="51" customHeight="1">
-      <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr">
         <is>
-          <t>9542_wagtail_8in1_screwdrivers_set</t>
+          <t>13177_adhesive_phone_card_holder_1pc</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>8-in-1 Screwdriver Set – Precision Mobile Repair Tool | Wagtail</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>380</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>289</t>
-        </is>
+          <t>Adhesive Card Phone Holder – Zipper Pocket Wallet | Mobiléon</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>469</v>
+      </c>
+      <c r="I49" t="n">
+        <v>349</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
@@ -13152,108 +11168,66 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>mobile accessories</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Upgrade your essential toolkit with the highly versatile 8-in-1 Screwdriver Set from Wagtail, engineered for unparalleled precision and lasting durability. This comprehensive kit is your go-to solution for a vast array of tasks, from intricate mobile phone repairs and delicate electronics maintenance to everyday household fixes. Experience seamless operation and effortless handling thanks to its advanced ergonomic design and a secure non-slip grip, ensuring every repair job is completed with greater comfort, control, and efficiency. Key features Premium Quality Construction: Each screwdriver in this 8-in-1 set is meticulously crafted from high-grade aviation aluminum alloy, featuring high-hardness gold-plated screw heads that offer superior strength, resistance to wear, and exceptional lon&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr"/>
-      <c r="R49" t="inlineStr"/>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr"/>
+          <t>&lt;p&gt;Streamline your everyday essentials with the innovative Adhesive Card Phone Holder from Mobiléon. This sleek and practical accessory easily attaches to the back of almost any smartphone or case, transforming it into a convenient mobile wallet. No more fumbling for your cards or cash – everything you need is securely right at your fingertips. Designed for the modern Indian user, this durable phone back wallet combines minimalist style with maximum functionality, making it perfect for anyone looking to lighten their load while staying organised on the go. Key features Secure Zipper Pocket: Safely store your essential cards, ID, and cash in a discreet, zippered compartment, offering enhanced security over open card slots. Strong Adhesive Backing: Equipped with a high-quality adhesive, this mo&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V49" t="inlineStr"/>
       <c r="W49" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_7b202084-a1db-43a3-9798-38695bd92026.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_d38833c7-983f-43a2-a1dd-741444d2a86c.jpg</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/70a91515-2974-4be7-93e0-c0f7d9198997.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/2_7f3b98af-0baf-49f8-aa0b-eb72269a8e5a.jpg</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/018_d9641501-9ec6-4d23-8c7d-bd1c70f1f7ab.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1_9c8c1859-bb0a-45b4-a1b7-804b63796155.jpg</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_6abb4092-35b6-4edd-84d5-cbdeeeb5386d.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wallet-3.jpg</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_53247a37-2639-4f70-8740-82170e716880.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wallet-7.jpg</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_cc633bcf-4618-4f04-8b3e-bcaa7ba3ba29.jpg</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr"/>
-      <c r="AD49" t="inlineStr"/>
-      <c r="AE49" t="inlineStr"/>
-      <c r="AF49" t="inlineStr"/>
-      <c r="AG49" t="inlineStr"/>
-      <c r="AH49" t="inlineStr"/>
-      <c r="AI49" t="inlineStr"/>
-      <c r="AJ49" t="inlineStr"/>
-      <c r="AK49" t="inlineStr"/>
-      <c r="AL49" t="inlineStr"/>
-      <c r="AM49" t="inlineStr"/>
-      <c r="AN49" t="inlineStr"/>
-      <c r="AO49" t="inlineStr"/>
-      <c r="AP49" t="inlineStr"/>
-      <c r="AQ49" t="inlineStr"/>
-      <c r="AR49" t="inlineStr"/>
-      <c r="AS49" t="inlineStr"/>
-      <c r="AT49" t="inlineStr"/>
-      <c r="AU49" t="inlineStr"/>
-      <c r="AV49" t="inlineStr"/>
-      <c r="AW49" t="inlineStr"/>
-      <c r="AX49" t="inlineStr"/>
-      <c r="AY49" t="inlineStr"/>
-      <c r="AZ49" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wallet-6.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="51" customHeight="1">
-      <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>14446_7in1_manicure_tool_set</t>
+          <t>whl146_11521_apex_ss_cat_mug_250ml_cm_cp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>7 in 1 Manicure Tool Kit – Professional Nail &amp; Foot Care Set</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>479</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>279</t>
-        </is>
+          <t>Apex Cat Mug – 250 ml Stainless Steel Insulated Kids' Mug</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>510</v>
+      </c>
+      <c r="I50" t="n">
+        <v>319</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
@@ -13262,108 +11236,66 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>&lt;p&gt;The 7 in 1 Manicure Tool Kit ensures professional-quality nail and foot care for smooth, healthy hands and feet. This complete set is designed to tackle tough nails, calluses, dead skin, and corns with ease, making it ideal for both personal and salon use. Key features Includes seven essential manicure and foot care tools for comprehensive grooming Effectively removes calluses, corns, dead skin, and nail residues Crafted from durable, high-quality materials for long-lasting performance Compact and portable design for easy use at home or on the go Improves nail appearance and foot comfort through regular maintenance Suitable for both professional manicurists and personal grooming routines FAQ Q1: What tools are included in the 7 in 1 manicure tool kit? A: The kit contains seven essential to&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr"/>
-      <c r="R50" t="inlineStr"/>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr"/>
+          <t>&lt;p&gt;The Apex Cat Mug is a delightful insulated kids&amp;#x27; mug designed with a cute double-cat print to brighten up your child&amp;#x27;s beverage time. This 250 ml stainless steel insulated mug combines fun design with practical features like a leak-proof lid and durable plastic outer body, perfect for keeping drinks warm for longer while ensuring easy handling for little hands. Key features Adorable Cat Design: Features a colorful double-cat print adding a playful charm. Insulated Stainless Steel Inner: Keeps beverages at the ideal temperature longer, ideal for hot tea, milk, or soup. Durable Plastic Outer Body: Lightweight and break-resistant for safe daily use by kids. Leak-Proof Lid: Prevents spills ensuring mess-free transport in school bags or desks. Comfort Grip Handle: Ergonomically designed for sma&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U50" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/14446_7in1_manicure_tool_set.png</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_db6a104e-3139-4cde-985e-dd560fbbaed5.jpg</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/3ee2e778-8347-466e-a285-ce995e94eb9c.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/842a32ec-6bd0-4386-8711-1ba93fac9f16.jpg</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_69c02a79-5d65-457c-b82f-a40df1cccb69.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_d07ebb01-1990-4b5e-9b72-25c0360be465.jpg</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_4b15c2ff-3344-4877-bdcf-8d3a96b231b1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_62065805-7968-42b1-acdd-4b974ed1e1db.jpg</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_acea0966-b76d-448f-87ec-46a8282fca25.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_9f1877c2-c4d5-4899-a616-291ee62b4bf8.jpg</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_d4d61a3b-075a-48e5-a86f-c7fd8770198f.jpg</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr"/>
-      <c r="AD50" t="inlineStr"/>
-      <c r="AE50" t="inlineStr"/>
-      <c r="AF50" t="inlineStr"/>
-      <c r="AG50" t="inlineStr"/>
-      <c r="AH50" t="inlineStr"/>
-      <c r="AI50" t="inlineStr"/>
-      <c r="AJ50" t="inlineStr"/>
-      <c r="AK50" t="inlineStr"/>
-      <c r="AL50" t="inlineStr"/>
-      <c r="AM50" t="inlineStr"/>
-      <c r="AN50" t="inlineStr"/>
-      <c r="AO50" t="inlineStr"/>
-      <c r="AP50" t="inlineStr"/>
-      <c r="AQ50" t="inlineStr"/>
-      <c r="AR50" t="inlineStr"/>
-      <c r="AS50" t="inlineStr"/>
-      <c r="AT50" t="inlineStr"/>
-      <c r="AU50" t="inlineStr"/>
-      <c r="AV50" t="inlineStr"/>
-      <c r="AW50" t="inlineStr"/>
-      <c r="AX50" t="inlineStr"/>
-      <c r="AY50" t="inlineStr"/>
-      <c r="AZ50" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_35f0202e-f4af-43be-ba5c-ae92c52950c2.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="51" customHeight="1">
-      <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>20035_student_stationery_combo_set</t>
+          <t>whl282_12774_jewellery_gift_box_1pc</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>6-in-1 Stationery Set – Compact All-in-One School &amp; Office Kit</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>615</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>249</t>
-        </is>
+          <t>Ring Gift Box – Premium Elegant Presentation with Velvet Cushion</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>439</v>
+      </c>
+      <c r="I51" t="n">
+        <v>249</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
@@ -13372,108 +11304,66 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Office Products</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>&lt;p&gt;The 6-in-1 stationery set is your perfect companion for school, office, or home use, providing a compact and convenient all-in-one solution for all essential writing and organizing tasks. Key features Complete Stationery Set : Includes 3 vibrant pens, 1 compact stapler, 1 box of No.10-1M staples, and 1 eraser for versatile daily use. Colorful Pens : Smooth ink flow with a comfortable grip, perfect for writing and note-taking. Compact Stapler : Lightweight and easy to operate, ideal for binding papers in school or office environments. Durable Staples : No.10-1M staples ensure secure fastening with the stapler included. Effective Eraser : Soft and gentle on paper, removes pencil marks without smudging. Portable Design : Compact and travel-friendly, fits easily in bags or desk drawers. Suitab&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr"/>
-      <c r="R51" t="inlineStr"/>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr"/>
+          <t>&lt;p&gt;Ring gift box crafted to perfectly present and protect your precious jewelry with elegance. Its sturdy decorative exterior and soft velvet cushion make it ideal for gifting and storage of rings. Key features Elegant jewelry presentation box with decorative diamond-themed finish Soft velvet-lined interior cushion prevents scratches and holds rings securely Snap-style magnetic closure ensures the box remains firmly sealed Hard protective outer casing provides safe storage and durability Compact and lightweight design suitable for gifting and travel Striking contrast color enhances the overall luxurious appearance Perfect for proposals, engagements, anniversaries, and jewelry shop presentations Materials &amp;amp; care The box features a hard outer shell with a decorative finish and a soft velvet-lin&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U51" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V51" t="inlineStr"/>
       <c r="W51" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/20035_student_stationery_combo_set.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-WOSKU-01.jpg</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/46120035-6000Pc-DD_20035-Av-Sv.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/19412774-128Pc-Ringbox-Av-Sv.jpg</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_pen-set.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-05.jpg</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_craft-set_5a12582e-d064-4dd8-bf92-957d1feee96e.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-06.jpg</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_craft-set_873a7250-145a-4f28-9dfb-1a47f43ce7f0.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-04.jpg</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_pen-set.jpg</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr"/>
-      <c r="AD51" t="inlineStr"/>
-      <c r="AE51" t="inlineStr"/>
-      <c r="AF51" t="inlineStr"/>
-      <c r="AG51" t="inlineStr"/>
-      <c r="AH51" t="inlineStr"/>
-      <c r="AI51" t="inlineStr"/>
-      <c r="AJ51" t="inlineStr"/>
-      <c r="AK51" t="inlineStr"/>
-      <c r="AL51" t="inlineStr"/>
-      <c r="AM51" t="inlineStr"/>
-      <c r="AN51" t="inlineStr"/>
-      <c r="AO51" t="inlineStr"/>
-      <c r="AP51" t="inlineStr"/>
-      <c r="AQ51" t="inlineStr"/>
-      <c r="AR51" t="inlineStr"/>
-      <c r="AS51" t="inlineStr"/>
-      <c r="AT51" t="inlineStr"/>
-      <c r="AU51" t="inlineStr"/>
-      <c r="AV51" t="inlineStr"/>
-      <c r="AW51" t="inlineStr"/>
-      <c r="AX51" t="inlineStr"/>
-      <c r="AY51" t="inlineStr"/>
-      <c r="AZ51" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-size.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="51" customHeight="1">
-      <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
-      <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr">
         <is>
-          <t>13574_3_sided_soft_toothbrush_2pc</t>
+          <t>18916_plastic_flower_vase_1pc</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>3-Sided Toothbrush – Soft Bristle Set for Complete Oral Care | BrushedUp</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>530</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
+          <t>Plastic Flower Vase – Elegant Design for Home &amp; Gift</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>505</v>
+      </c>
+      <c r="I52" t="n">
+        <v>259</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
@@ -13482,108 +11372,66 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Transform your daily oral care routine with the innovative three-sided soft bristle toothbrushes from BrushedUp. Designed for a superior clean, this unique toothbrush reaches all tooth surfaces simultaneously, making brushing faster and more effective for both adults and children. Experience comprehensive plaque removal and a refreshing sensation with every brush, ensuring complete oral care with minimal effort and maximum efficiency. Say goodbye to missed spots and hello to a brighter, healthier smile. Our unique triple-head design is engineered to provide a gentle yet thorough cleaning experience. The soft, premium bristles are specifically designed to protect your gums while effectively removing plaque and food particles from every angle, including those hard-to-reach areas. Its ergonom&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr"/>
-      <c r="R52" t="inlineStr"/>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr"/>
+          <t>&lt;p&gt;Discover the charm of the Plastic Flower Vase, crafted for elegant home decor and perfect as a thoughtful gift for family and friends. This plastic flower vase offers a sleek silhouette that enhances any room, bringing a fresh, decorative touch to your living room, office, or dining table. Key features Elegant and modern design with a smooth, textured finish for a refined look. Multipurpose vase suitable for fresh bouquets, artificial flowers, and silk greenery. Lightweight plastic construction ensures durability and easy handling. Ideal for home decor, office desk embellishment, bathroom, kitchen, or wedding centrepieces. An excellent gifting choice for birthdays, housewarmings, and special occasions. Compact size with dimensions: length 18 cm, width 7 cm, height 7 cm for versatile placem&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U52" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr"/>
       <c r="W52" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/fdb70b55-5fd2-4847-9031-8d09ed1fa6d3.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_91c87a05-2ddc-443d-aee5-5aaa0ccf7bb7.jpg</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/141.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/c7b8256b-ca06-449d-b7e2-4627ed71258c.jpg</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_af911449-c989-4978-9fd7-c27e8d31ab61.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_09ed9caa-6d17-4595-8fd7-d5da22d94de9.jpg</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_b5091b49-94ec-4855-a1b4-ffea5ac1e64f.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_7cda10fe-b23b-41b8-9646-9b6189b2cc87.jpg</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_d56096f0-e545-4f28-b327-9bb3e288b647.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_671810cd-b793-47bd-9932-d837eb7a22ca.jpg</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_c7147f39-81e5-43f7-9f56-d2af6baedb72.jpg</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr"/>
-      <c r="AD52" t="inlineStr"/>
-      <c r="AE52" t="inlineStr"/>
-      <c r="AF52" t="inlineStr"/>
-      <c r="AG52" t="inlineStr"/>
-      <c r="AH52" t="inlineStr"/>
-      <c r="AI52" t="inlineStr"/>
-      <c r="AJ52" t="inlineStr"/>
-      <c r="AK52" t="inlineStr"/>
-      <c r="AL52" t="inlineStr"/>
-      <c r="AM52" t="inlineStr"/>
-      <c r="AN52" t="inlineStr"/>
-      <c r="AO52" t="inlineStr"/>
-      <c r="AP52" t="inlineStr"/>
-      <c r="AQ52" t="inlineStr"/>
-      <c r="AR52" t="inlineStr"/>
-      <c r="AS52" t="inlineStr"/>
-      <c r="AT52" t="inlineStr"/>
-      <c r="AU52" t="inlineStr"/>
-      <c r="AV52" t="inlineStr"/>
-      <c r="AW52" t="inlineStr"/>
-      <c r="AX52" t="inlineStr"/>
-      <c r="AY52" t="inlineStr"/>
-      <c r="AZ52" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_fe1fa176-7079-4eaf-ba0d-ae00d5d62249.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="51" customHeight="1">
-      <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
       <c r="F53" t="inlineStr">
         <is>
-          <t>21110_11in1_manicure_n_pedicure_grooming</t>
+          <t>whl282_22517_next_velvet_oud_attar_12ml</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>11 in 1 Manicure Pedicure Nail Care Kit – Professional Grooming Set | DeoDap</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>450</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>299</t>
-        </is>
+          <t>Next Velvet Oud Attar – Long Lasting, Premium Fragrance Oil</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>510</v>
+      </c>
+      <c r="I53" t="n">
+        <v>369</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
@@ -13592,108 +11440,66 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty Accessories</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Our 11 in 1 Manicure Pedicure Nail Care Kit offers a comprehensive solution for professional nail grooming right at home. This complete nail care set combines essential tools for trimming, shaping, and maintaining healthy nails, ensuring both hands and feet look neat and well-groomed. Whether you&amp;#x27;re tackling cuticle maintenance or smoothing rough edges, this kit is designed for precision and durability. Key features Complete 11-in-1 nail grooming tool set including nail clipper, cuticle nipper, nail file, scissors, tweezers, foot separator, and cleaning brush Professional quality tools crafted for precise nail trimming and shaping Ergonomic design for comfortable, secure handling in every use Helps maintain nail hygiene by removing rough edges and cleaning cuticles effectively Compact and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr"/>
-      <c r="R53" t="inlineStr"/>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr"/>
+          <t>&lt;p&gt;Discover the rich and luxurious scent of Next Velvet Oud Concentrated Attar Perfume 12 ML, designed for those who seek a deep, woody, and musky aroma that lasts for hours. This premium oud attar is ideal for individuals who appreciate traditional oriental fragrances with a modern twist. Crafted without alcohol, this unisex perfume offers a sophisticated,浓ent experience suitable for daily wear, special occasions, and religious gatherings. Its compact size makes it convenient for travel and on-the-go application, whether you prefer a roll-on or dab method. Key features Premium concentrated oud fragrance Long lasting and rich aroma Non alcoholic attar formula Suitable for men and women Elegant luxury bottle design Easy roll on or dab application 12 ML compact size Materials &amp;amp; care Maintain th&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U53" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V53" t="inlineStr"/>
       <c r="W53" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_4dcf21f6-61dc-4650-8d8a-ba44c861b18d.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-WOSKU-01.jpg</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_db698651-8517-4d43-8c6d-89b851ef0b3c.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-WSKU-01.jpg</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_e0a9af6b-3dd1-45cc-8eca-ce06c9e5d81a.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-05.jpg</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_8ec38e4b-853c-4479-b993-08ca94d628c2.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-04.jpg</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_6749c20f-ad0f-4d4a-ba54-190bfb9078dc.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-03.jpg</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_507d5eda-ca61-4f51-9ff2-83c53cae6299.jpg</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr"/>
-      <c r="AD53" t="inlineStr"/>
-      <c r="AE53" t="inlineStr"/>
-      <c r="AF53" t="inlineStr"/>
-      <c r="AG53" t="inlineStr"/>
-      <c r="AH53" t="inlineStr"/>
-      <c r="AI53" t="inlineStr"/>
-      <c r="AJ53" t="inlineStr"/>
-      <c r="AK53" t="inlineStr"/>
-      <c r="AL53" t="inlineStr"/>
-      <c r="AM53" t="inlineStr"/>
-      <c r="AN53" t="inlineStr"/>
-      <c r="AO53" t="inlineStr"/>
-      <c r="AP53" t="inlineStr"/>
-      <c r="AQ53" t="inlineStr"/>
-      <c r="AR53" t="inlineStr"/>
-      <c r="AS53" t="inlineStr"/>
-      <c r="AT53" t="inlineStr"/>
-      <c r="AU53" t="inlineStr"/>
-      <c r="AV53" t="inlineStr"/>
-      <c r="AW53" t="inlineStr"/>
-      <c r="AX53" t="inlineStr"/>
-      <c r="AY53" t="inlineStr"/>
-      <c r="AZ53" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-size.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="51" customHeight="1">
-      <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr">
         <is>
-          <t>whl175_67690_mn_033_go</t>
+          <t>8782_mini_jewelry_organizer_box</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>24K Gold Foil Rose – Luxurious Eternal Romantic Gift</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>449</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
+          <t>Travel Jewellery Box – Portable PU Leather Organiser | LilyGleam</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>525</v>
+      </c>
+      <c r="I54" t="n">
+        <v>269</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -13702,104 +11508,66 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Home &amp; Kitchen</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>Discover the timeless charm of the 24K Gold Foil Rose, a luxurious artificial flower perfect for expressing love on Valentine's Day, anniversaries, or special moments. This stunning rose captivates hearts with its rich golden shine and elegant design, making it an everlasting symbol of affection to cherish forever. Key features Finished with authentic 24K gold foil for a radiant, lasting glow Realistic petals and intricately detailed leaves that mimic natural beauty Sturdy metal stem ensures durability and long-lasting elegance Presented in a premium purple gift box with stylish gold accents, ready for gifting Ideal romantic keepsake gift for girlfriends, wives, or loved ones Perfect accent for home décor or as a valuable collectible item Materials &amp; care The rose is crafted with a metal s</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr"/>
+          <t>&lt;p&gt;Searching for the perfect travel jewellery box that combines style, functionality, and portability? Look no further than the LilyGleam Mini PU Leather Travel Jewellery Box. Designed for the modern Indian woman on the go, this elegant and compact organiser ensures your precious rings, necklaces, and earrings stay safe, secure, and tangle-free, whether you&amp;#x27;re heading to a weekend getaway or a business trip. Say goodbye to lost earrings and tangled chains with this essential accessory for every journey. Key features Compact &amp;amp; Portable Design: Perfectly palm-sized, this travel jewellery box easily fits into handbags, luggage, or carry-ons for convenient travel. Multi-Functional Storage: Thoughtfully designed compartments for rings, necklaces, earrings, studs, and even small makeup items like l&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U54" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V54" t="inlineStr"/>
       <c r="W54" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/whl175_67690_mn_033_go.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---05.jpg</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/KGig6X6Nd1.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/8782.jpg</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/v6DhBmH9if.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---03.jpg</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/m5WvGB9AUt.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---04.jpg</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/O5fO0vZlKw.jpg</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr"/>
-      <c r="AC54" t="inlineStr"/>
-      <c r="AD54" t="inlineStr"/>
-      <c r="AE54" t="inlineStr"/>
-      <c r="AF54" t="inlineStr"/>
-      <c r="AG54" t="inlineStr"/>
-      <c r="AH54" t="inlineStr"/>
-      <c r="AI54" t="inlineStr"/>
-      <c r="AJ54" t="inlineStr"/>
-      <c r="AK54" t="inlineStr"/>
-      <c r="AL54" t="inlineStr"/>
-      <c r="AM54" t="inlineStr"/>
-      <c r="AN54" t="inlineStr"/>
-      <c r="AO54" t="inlineStr"/>
-      <c r="AP54" t="inlineStr"/>
-      <c r="AQ54" t="inlineStr"/>
-      <c r="AR54" t="inlineStr"/>
-      <c r="AS54" t="inlineStr"/>
-      <c r="AT54" t="inlineStr"/>
-      <c r="AU54" t="inlineStr"/>
-      <c r="AV54" t="inlineStr"/>
-      <c r="AW54" t="inlineStr"/>
-      <c r="AX54" t="inlineStr"/>
-      <c r="AY54" t="inlineStr"/>
-      <c r="AZ54" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---07.jpg</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---06.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="51" customHeight="1">
-      <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
       <c r="F55" t="inlineStr">
         <is>
-          <t>whl146_11521_apex_ss_cat_mug_250ml_cm_cp</t>
+          <t>21611_golden_rose_n_box</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Apex Cat Mug – 250 ml Stainless Steel Insulated Kids' Mug</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>430</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
+          <t>Gold Plated Artificial Rose – Eternal Love Decor Gift</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>479</v>
+      </c>
+      <c r="I55" t="n">
+        <v>299</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -13808,108 +11576,66 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>The Apex Cat Mug is a delightful insulated kids' mug designed with a cute double-cat print to brighten up your child's beverage time. This 250 ml stainless steel insulated mug combines fun design with practical features like a leak-proof lid and durable plastic outer body, perfect for keeping drinks warm for longer while ensuring easy handling for little hands. Key features Adorable Cat Design: Features a colorful double-cat print adding a playful charm. Insulated Stainless Steel Inner: Keeps beverages at the ideal temperature longer, ideal for hot tea, milk, or soup. Durable Plastic Outer Body: Lightweight and break-resistant for safe daily use by kids. Leak-Proof Lid: Prevents spills ensuring mess-free transport in school bags or desks. Comfort Grip Handle: Ergonomically designed for sma</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr"/>
-      <c r="R55" t="inlineStr"/>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr"/>
+          <t>&lt;p&gt;This gold plated artificial rose is a timeless symbol of eternal love and appreciation. Crafted with exquisite detail, this decorative golden rose perfectly expresses affection and serves as a lasting gift that never wethers, making it an ideal choice for special occasions or home decor. Key features Premium gold plating: The rose is coated with 24K gold foil, symbolising nobility and eternal love. Handcrafted artistry: Expert artisans precisely create each rose to capture the beauty of natural flowers. Elegant presentation: Comes in a beautiful purple premium box with a transparent front to showcase the rose without unboxing. Versatile decoration: Ideal for home, office decor, weddings, parties, or special occasions. Never fades or wilts: A lasting expression of love and best wishes that&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U55" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="V55" t="inlineStr"/>
       <c r="W55" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_db6a104e-3139-4cde-985e-dd560fbbaed5.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/WhatsApp_Image_2026-08-27_at_18.57.15_20b57117-2e09-4f20-8eb5-393c691ed431.jpg</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/842a32ec-6bd0-4386-8711-1ba93fac9f16.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_c7bb241f-04da-47c1-8994-392fb0134638.jpg</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_d07ebb01-1990-4b5e-9b72-25c0360be465.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/whl175_67690_mn_033_go_3af2ed48-1c67-4301-b108-d55c01fa5eb1.jpg</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_62065805-7968-42b1-acdd-4b974ed1e1db.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/61ClF3UfoWL._SL1000_d63357b1-11b2-49f3-90f0-c7267d160838.jpg</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_9f1877c2-c4d5-4899-a616-291ee62b4bf8.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/41nZL-LzlYL_0884f0a3-0f89-4e37-b20a-f67a189543c7.jpg</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_35f0202e-f4af-43be-ba5c-ae92c52950c2.jpg</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr"/>
-      <c r="AD55" t="inlineStr"/>
-      <c r="AE55" t="inlineStr"/>
-      <c r="AF55" t="inlineStr"/>
-      <c r="AG55" t="inlineStr"/>
-      <c r="AH55" t="inlineStr"/>
-      <c r="AI55" t="inlineStr"/>
-      <c r="AJ55" t="inlineStr"/>
-      <c r="AK55" t="inlineStr"/>
-      <c r="AL55" t="inlineStr"/>
-      <c r="AM55" t="inlineStr"/>
-      <c r="AN55" t="inlineStr"/>
-      <c r="AO55" t="inlineStr"/>
-      <c r="AP55" t="inlineStr"/>
-      <c r="AQ55" t="inlineStr"/>
-      <c r="AR55" t="inlineStr"/>
-      <c r="AS55" t="inlineStr"/>
-      <c r="AT55" t="inlineStr"/>
-      <c r="AU55" t="inlineStr"/>
-      <c r="AV55" t="inlineStr"/>
-      <c r="AW55" t="inlineStr"/>
-      <c r="AX55" t="inlineStr"/>
-      <c r="AY55" t="inlineStr"/>
-      <c r="AZ55" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/51VptqPMk5L._SL1500_4de1596f-93c1-4a3f-b0d1-bf4af8467a34.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="51" customHeight="1">
-      <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr">
         <is>
-          <t>17853_safety_goggles_1pc</t>
+          <t>22311_paper_long_rectangle_empty_gift_bo</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Adjustable Safety Goggles – Impact-Resistant Polycarbonate Lens for Workplace &amp; Outdoor</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>229</t>
-        </is>
+          <t>Long Rectangular Paper Empty Gift Box with Bow for Jewellery and Gifting</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>509</v>
+      </c>
+      <c r="I56" t="n">
+        <v>219</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -13918,82 +11644,49 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Home Improvement</t>
+          <t>Gifts &amp; Hampers</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>Experience superior eye protection with our Adjustable Safety Goggles, crafted for comfort and durability. These goggles feature a clear polycarbonate lens that provides impact resistance and a wide field of view, making them ideal for various industrial, laboratory, construction, and outdoor activities. The adjustable temples ensure a snug fit for different head sizes, offering a customized and secure wear that stays comfortable during extended use. Lightweight and ergonomic, these safety goggles are designed to fit over prescription glasses, enabling safe and clear vision for all users. Whether you're working in a lab or working out in the outdoors, these goggles ensure your eyes are protected from dust, debris, chemical splashes, and impact hazards. Key features Impact-resistant clear p</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr"/>
+          <t>&lt;p&gt;Present your thoughtful gifts elegantly with this light blue rectangular gift box. Its sophisticated design and decorative bow create perfect packaging for jewellery, accessories, and other special presents, making every occasion memorable. Key features Long rectangular shape is ideal for slim gifts and accessories like watches or pens. Made from durable paper, offering a lightweight and eco-friendly packaging solution. Features an elegant decorative bow, providing a ready-to-gift appearance. Convenient removable lid allows for easy placement and stylish presentation of items. Compact profile ensures easy storage before use and after gifting. Neat light blue finish complements birthdays, anniversaries, and festive occasions. Reusable box can help organise small personal accessories or keep&lt;/p&gt;</t>
+        </is>
+      </c>
       <c r="U56" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
-      <c r="V56" t="inlineStr"/>
       <c r="W56" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/safety_goggles_17853_01_main.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-1-02.jpg</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/safety_goggles_17853_sku.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-2-01.jpg</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/safety_goggles_17853_02.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-3-03.jpg</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/safety_goggles_17853_04.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-4-04.jpg</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/safety_goggles_17853_03.jpg</t>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-5-07.jpg</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/safety_goggles_17853_05.jpg</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr"/>
-      <c r="AD56" t="inlineStr"/>
-      <c r="AE56" t="inlineStr"/>
-      <c r="AF56" t="inlineStr"/>
-      <c r="AG56" t="inlineStr"/>
-      <c r="AH56" t="inlineStr"/>
-      <c r="AI56" t="inlineStr"/>
-      <c r="AJ56" t="inlineStr"/>
-      <c r="AK56" t="inlineStr"/>
-      <c r="AL56" t="inlineStr"/>
-      <c r="AM56" t="inlineStr"/>
-      <c r="AN56" t="inlineStr"/>
-      <c r="AO56" t="inlineStr"/>
-      <c r="AP56" t="inlineStr"/>
-      <c r="AQ56" t="inlineStr"/>
-      <c r="AR56" t="inlineStr"/>
-      <c r="AS56" t="inlineStr"/>
-      <c r="AT56" t="inlineStr"/>
-      <c r="AU56" t="inlineStr"/>
-      <c r="AV56" t="inlineStr"/>
-      <c r="AW56" t="inlineStr"/>
-      <c r="AX56" t="inlineStr"/>
-      <c r="AY56" t="inlineStr"/>
-      <c r="AZ56" t="inlineStr"/>
+          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-6-06.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="51" customHeight="1"/>
     <row r="58" ht="51" customHeight="1"/>

--- a/smartbiz_bulk_upload_template_v10.xlsx
+++ b/smartbiz_bulk_upload_template_v10.xlsx
@@ -7661,7 +7661,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ56"/>
+  <dimension ref="A1:AZ1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="19.5" customWidth="1" min="1" max="1"/>
@@ -7973,3721 +7973,61 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="51" customHeight="1">
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>whl239_73330_rng_stn_om_12</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Om Mandala Rangoli Design – Mess-Free Pooja Decoration</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>539</v>
-      </c>
-      <c r="I2" t="n">
-        <v>259</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Enhance your pooja room or home entrance with this Om Mandala Rangoli design stencil. Perfect for creating a sacred and serene atmosphere during festivals and rituals, this stencil helps you achieve a clean, precise, and mess-free rangoli every time. Key features Sacred Om Design – Ideal for mandir, pooja rooms, and festive celebrations. Mess-Free Application – Keeps colors neatly within the stencil for crisp lines. Heavy MDF Base – Ensures stability and prevents movement even under a fan. Reusable and Durable – Made to last with sturdy materials for repeated use. Easy Maintenance – Simply brush off colors after use and store for next time. Materials &amp;amp; care Crafted from durable MDF, this rangoli stencil is designed for steady use. To maintain its quality, gently brush off any residual powd&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/nG8pP6034D.jpg</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/qjVOzEOdV6.jpg</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/7MiafrLHU9.jpg</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/eC4r57kdI4.jpg</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Wjirk4ymqK.jpg</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/9c038ad8-5546-4b2d-9475-6d6ce7435c04.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="51" customHeight="1">
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>whl313_90633_pm105_murti</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Panchmukhi Hanuman Idol for Home, Office &amp; Car Dashboard Spiritual Decor</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>499</v>
-      </c>
-      <c r="I3" t="n">
-        <v>349</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Discover the divine presence of a Panchmukhi Hanuman idol , perfect for enhancing your spiritual space. This beautifully crafted idol embodies protection, courage, and devotion, bringing positive energy to your home, office, or car dashboard. Its intricate design and antique bronze finish make it a truly special addition to any decor. Key features Premium antique bronze finish with detailed craftsmanship Depicts the powerful Panchmukhi (Five-Faced) Hanuman form Symbol of protection, courage, devotion, and success Intricate traditional design with sacred weapons and ornaments Ideal for home temples, offices, and spiritual spaces Durable and elegant decorative idol Perfect gift for Hanuman Jayanti, Diwali, housewarming ceremonies, and religious occasions Materials &amp;amp; care Crafted with a durab&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/0fKCWS2Oce.jpg</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/P7wd9B2NAL.jpg</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/n8Y1s6GVMm.jpg</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4eGHmZINcF.jpg</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/lVdyq9JuSj.jpg</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/HH9yyt2nK9.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="51" customHeight="1">
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>whl239_73363_decor_laxmi_charan_paduka_s</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Laxmi Charan Paduka Stickers – Festive Spiritual Home Décor (Pack of 2)</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>559</v>
-      </c>
-      <c r="I4" t="n">
-        <v>229</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Enhance your home&amp;#x27;s spiritual aura with our Laxmi Charan Paduka Sticker Set, designed to bring blessings and prosperity during festivals and daily pooja rituals. These sacred Laxmi Charan Paduka stickers feature traditional footprints embellished with vibrant beads and sparkling stones for a divine touch, making them perfect for festive spiritual home decor. Key features Traditional Goddess Lakshmi footprints featuring the auspicious Swastik symbol Decorated with multicolored beads, sequins, and glittering stones for vibrant appeal Easy peel-and-stick backing suitable for doors, walls, floors, and pooja thalis Reusable and simple to clean with a dry wipe, ideal for multiple festive occasions Perfect for Diwali, Lakshmi Pujan, Navratri, Griha Pravesh, and spiritual home decoration Comes pac&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_9da764a6-0ee2-4da6-aac6-e8bc7849da42.jpg</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_d891c284-8708-4c38-b0e4-aeca264c3244.jpg</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_edf02a26-c1a5-4ee0-a634-cb9843a6d666.jpg</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_155b0a2f-27c8-4248-af67-d5b57806a5a7.jpg</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_1e5c06fe-75d5-4c51-afe2-d262f4fccc14.jpg</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_7f2a7e37-7e1e-4011-af4f-c64f39073aa9.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="51" customHeight="1">
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>9041_small_hand_tally_counter</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Hand Tally Counter for Jaap and Mantra Chanting Pooja Use</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>509</v>
-      </c>
-      <c r="I5" t="n">
-        <v>219</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;A digital finger tally counter with strap simplifies your spiritual practices by accurately tracking repetitions. This essential tool ensures your focus remains on your jaap or mantra chanting, removing the distraction of manual counting. Its compact design and comfortable strap make it ideal for extended use during daily prayers, meditation, or temple visits. Key features Keeps precise count for uninterrupted chanting and meditation One-thumb press operation allows for easy, discreet counting Reading holds even when paused, perfect for intermittent use Quick reset dial returns count to zero for new sessions Compact size with a strap for comfortable, secure wear on finger Manual click mechanism means no batteries are required Portable design fits easily in pooja thali, pocket, or bag Versa&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/9041_656ca080-9177-4b35-93ae-60b7732d45e4.png</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/eedc839b-60ab-46ad-99d2-45ecaa0c38f3.jpg</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/7_7da8be7e-c7e8-48ac-90bb-dd94e795c570.jpg</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/8_4ba63586-6093-450c-8983-0bb4ad8820ff.jpg</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/4_11d433d1-4d76-44b8-b5fa-30b7cf078440.jpg</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/5_62ec6240-78d3-49c8-902a-1c574b5f8eac.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="51" customHeight="1">
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>22198_hand_shape_kankavati_kumkum_holder</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Hand Shaped Kankavati – Elegant Puja Storage with Enamel Work</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>535</v>
-      </c>
-      <c r="I6" t="n">
-        <v>229</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Discover the beauty and utility of the Hamsa hand decorative puja thali, an exquisite accessory designed for your sacred rituals. Crafted in a traditional hand (hamsa) shape, this kumkum holder features twin compartments for storing kumkum (roli) and chawal (rice), along with two additional lidded boxes for extra storage. Enhanced with intricate blue and teal enamel floral work on a rich golden finish, it adds a divine touch to your home temple, pooja thali, or festival celebrations. This elegant piece not only serves as a practical puja item but also accentuates the spiritual ambiance of your worship space. Key features Hamsa hand shaped decorative kumkum holder Dual compartments for kumkum and chawal Two extra lidded boxes for additional storage Rich golden finish with detailed enamel wo&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-01-no-sku_238ab33d-25cc-4182-82c4-47ef051b6e42.jpg</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-02-sku_b70a011f-7333-4e61-b427-3a05d88bfd4b.jpg</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-03-product_db2e4ff7-43b1-4168-ace1-6b2631e96070.jpg</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-04-product_c0d57e72-f3c9-4144-b5cb-d010ce441491.jpg</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-05-white-bg_27048fdf-a731-4c2b-a9a4-734b7cda6d2c.jpg</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22198-06-size_d81be685-bb60-4de5-b054-f198156a3229.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="51" customHeight="1">
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>whl175_94317_7104</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Decorative Palm Shape Ganesh Idols for Pooja Mandir, Table &amp; Home Decor (Set of 4)</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>479</v>
-      </c>
-      <c r="I7" t="n">
-        <v>349</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Add a distinctive devotional touch to your space with these Palm Shape Ganesh Idols. Each piece features Lord Ganesh seated within a hand-shaped frame, enhanced with metallic detailing that gives the idols a refined and traditional appearance. The compact design makes them suitable for home mandirs, pooja shelves, office desks, side tables and festive arrangements. The different metallic accents add variety while maintaining a coordinated overall look. Key Features Unique palm-shaped Ganesh idol design Decorative metallic detailing Elegant white finish Suitable for mandir and pooja setup Compact design for table and shelf placement Ideal for festive and devotional decoration Can be displayed together or separately Quantity: Set of 4&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/FxXtgzeQJm.png</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ioyZy5nIog.png</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/s9wUTME51k.png</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/r91BKyN07e.png</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/zDQ0S1HOvP.png</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Kc9dgHYt5a.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="51" customHeight="1">
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2234_silver_bajot</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Aluminium Foil Bajot – Handcrafted Pooja Chowki for Home | Styleva</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>500</v>
-      </c>
-      <c r="I8" t="n">
-        <v>219</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Elevate your spiritual space and home aesthetics with our exquisite Aluminium Foil Bajot . This beautifully handcrafted pooja chowki is designed to add a touch of traditional elegance to your rituals and interior decor. Perfect for royal weddings, daily pujas, or as a charming accent piece, this versatile patla combines durability with a luxurious finish, making it an essential addition to any Indian home. Key features Luxurious Minakari Design: Adorned with intricate white metal minakari work over aluminium foil, creating a royal and eye-catching appearance. Sturdy Wooden Construction: Built on a solid wooden base for lasting durability and stability. Multipurpose Utility: Ideal for placing deity idols during pooja, sitting comfortably for rituals, or as a decorative stand for plants and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/2_bdb9a21a-cd11-4af6-a6c7-f54b76dc16b9.jpg</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/2234SKUCODE.jpg</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/944879d7-32b1-4582-9b5a-83f6ced20d26.jpg</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/22341.jpg</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/4_2803ea4c-8890-4014-a2e1-9326a35f17ec.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="51" customHeight="1">
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>19675_shubh_labh_wall_hangings_2pc_no7</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Shubh Labh Wall Hangings – Set of 2 Festive Decorative Pieces</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>575</v>
-      </c>
-      <c r="I9" t="n">
-        <v>229</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Invite prosperity and good fortune into your home with this exquisite Shubh Labh wall hangings set. This vibrant set of two decorative pieces features traditional &amp;quot;Shubh&amp;quot; (auspicious) and &amp;quot;Labh&amp;quot; (profit) inscriptions, beautifully enhanced with shimmering glitter and intricate stonework. Perfect for elevating festive vibes or adding spiritual charm to your living spaces, these lightweight wall hangings instantly bring positivity and traditional Indian elegance. Key features Auspicious inscriptions: Displays &amp;quot;Shubh&amp;quot; and &amp;quot;Labh&amp;quot; symbols, promoting good luck and success. Festive design: Glitter-embellished and stone-studded for an eye-catching decorative appeal. Versatile placement: Ideal for home entrances, pooja rooms, temples, shops, or offices. Lightweight and easy to hang: Quick to install&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_8e3fcd8e-cfe6-4b3b-ad8e-780f5014fd5d.jpg</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/85c9a601-5322-428e-8145-60f1125d9a86.jpg</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_a36c43ec-b2ae-43ae-b6f3-4d0b7379be99.jpg</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_65960b96-d73c-4105-a152-bbdaa8429caf.jpg</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_a4e5998b-cba0-46cd-99ea-494709aeea51.jpg</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_a27e5163-97d3-490d-a3e2-80709a0433ce.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="51" customHeight="1">
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>8444_led_iceberg_light_1pc</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Iceberg Night Light – Flameless LED Decor for Home | Indo Glow</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>460</v>
-      </c>
-      <c r="I10" t="n">
-        <v>259</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Transform your living space with the enchanting LED light-up clear iceberg decor from Indo Glow. This modern and unique flameless LED lamp creates a serene ambiance, perfect for any room. Ideal for bedroom decor, festive celebrations like Diwali, or as a thoughtful gift, its captivating iceberg design adds a touch of contemporary elegance without the hazards of traditional candles. Experience the perfect blend of style and safety with our innovative LED light-up clear iceberg decor. Powered by energy-efficient LEDs, it offers a gentle, calming glow that enhances your home&amp;#x27;s atmosphere. Whether you&amp;#x27;re looking to create a cozy reading nook, a tranquil bedroom sanctuary, or a festive display for special occasions, this versatile night light is an excellent choice. Its compact size makes it a&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/8444_led_iceberg_light_1pc.jpg</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/0ee593c4-95b9-4def-87cf-594eb2310c96.jpg</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/19417.png</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/19418.png</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/011_8d4ae56c-5560-44b2-8f46-e4f7fefbdcb2.jpg</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/2092621834.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="51" customHeight="1">
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>whl167_48605_handcrafted_tulsi_diya_4pc</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Handcrafted Tulsi Kiyaro Diya Set – Festive Clay Oil Lamps with Swastik &amp; Shree</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>459</v>
-      </c>
-      <c r="I11" t="n">
-        <v>299</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Celebrate your festivals with the Handcrafted Tulsi Kiyaro Diya Set, a perfect blend of tradition and vibrant decor. These clay oil lamps, adorned with sacred Swastik and Shree symbols, bring divine positivity and an auspicious atmosphere to your home. Ideal for Diwali, Navratri, Ganesh Chaturthi, weddings, and daily pooja rituals, these square-shaped diyas are a beautiful spiritual addition to your festive decor. Key features Hand-painted square diyas featuring sacred Hindu symbols like Swastik and Shree for spiritual significance. Made from high-quality clay that enhances traditional authenticity and durability. Multi-color palette including red, green, purple, and orange to brighten your festive ambiance. Compatible with oil, ghee, or tealight candles for versatile use. Eco-friendly and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/cisTqUbngf.jpg</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ae6zk3JnnF.jpg</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/10ax8Rhryi.jpg</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/pDAthNJ4UE.jpg</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/pZtERD6xxD.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="51" customHeight="1">
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>whl202_67906_diya_flower_5l_red</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Flower 5-Step Decorative Diya – Multi-Purpose Eco-Friendly Holder</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>480</v>
-      </c>
-      <c r="I12" t="n">
-        <v>249</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Festive &amp; Lights</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Enhance your home ambiance with the Flower 5-Step Decorative Diya, a versatile eco-friendly gypsum holder perfect for pooja rituals, festive lighting, or stylish decor. This multi-purpose diya blends traditional charm with modern functionality to illuminate your space with warmth and serenity. Key features Crafted from premium-quality, non-toxic, and durable gypsum, ensuring an eco-friendly product Intricately handcrafted lotus flower design symbolizing purity and peace Multi-use as a diya, tealight candle holder, dhoop cone stand, mini planter, or creative craft base Elegant and smooth finish complements pooja rooms, offices, living areas, and festive decorations Perfect for Diwali, Navratri, weddings, housewarmings, and gifting Customizable surface — easily painted or decorated to suit y&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/mOff8nPgzy.png</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/b456Ff1Wkc.png</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/uLHCbmbvTd.png</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ZgWdJBsnmE.png</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/vju4NtPzlL.png</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/x1aApIbqsH.png</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="51" customHeight="1">
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>10314_ss_kitchen_veg_n_friut_grater</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Stainless Steel Cheese Grater – Multi-Purpose Kitchen Tool | CookAura</t>
-        </is>
-      </c>
-      <c r="H13" t="n">
-        <v>550</v>
-      </c>
-      <c r="I13" t="n">
-        <v>229</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Elevate your culinary experience with the CookAura Stainless Steel Cheese Grater , an essential multi-purpose tool for every Indian kitchen. This versatile grater is designed to make food preparation quicker, easier, and more efficient, whether you&amp;#x27;re grating hard cheeses, shredding fresh vegetables, or zesting citrus fruits. Its durable construction and ergonomic design ensure a comfortable grip and superior performance for all your grating needs. Crafted from high-quality stainless steel, this kitchen essential promises long-lasting sharpness and resistance to rust, making it a reliable companion for years to come. From ginger and garlic to chocolate and potatoes, this efficient kitchen tool handles a wide array of ingredients with ease. Its compact design also ensures it won&amp;#x27;t take up m&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_b3320453-ee8d-4bf5-b0ea-623fe797673d.jpg</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_cd98e4a7-fd75-4603-8071-6ab9c25a5b02.jpg</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_dcc8733f-c840-45a9-8f09-c98c74856e3d.jpg</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_07060837-ddc5-4743-b877-f8f3a50a3c73.jpg</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_c8bec7f9-6ccb-41a1-b3df-59122766b82b.jpg</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_e6461edb-bfed-45f3-87cb-42e6adc0fb96.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="51" customHeight="1">
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2996_round_sili_strainer_1pc_no1</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Silicone Collapsible Strainer – Space-Saving Kitchen Tool for Easy Draining</t>
-        </is>
-      </c>
-      <c r="H14" t="n">
-        <v>519</v>
-      </c>
-      <c r="I14" t="n">
-        <v>319</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The silicone collapsible strainer is an essential kitchen accessory that simplifies draining and rinsing tasks. Its flexible, food-grade silicone body folds flat, allowing for compact storage while providing a sturdy, reliable strainer when needed. Designed for versatile use, this collapsible colander is perfect for washing fruits, vegetables, and rice, as well as draining pasta, noodles, and boiled foods. Its lightweight construction and easy-clean surface make it an ideal tool for busy kitchens, outdoor cooking, or travel. Key features Collapsible design folds flat for space-efficient storage Made of durable, food-grade silicone material Fine drain holes for quick, mess-free draining Comfortable side handles for secure grip Sturdy structure when popped up for rinsing Suitable for washing&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-1.jpg</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_52a6813f-0bcb-4dd1-9fcc-48c2d3628c0f.jpg</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-3.jpg</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-4.jpg</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-7.jpg</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Silicone-Colander_2_-6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="51" customHeight="1">
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>11401_plastic_gas_stove_burner_cover_10p</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Plastic Gas Stove Burner Cover Liners for Kitchen Cleaning and Hygiene (10 Pc)</t>
-        </is>
-      </c>
-      <c r="H15" t="n">
-        <v>480</v>
-      </c>
-      <c r="I15" t="n">
-        <v>349</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Disposable Plastic Gas Stove Burner Cover Liners with Raised Edges for Catching Oil, Food Spills and Cooking Residue Around Kitchen Burners (10 Pc) Description :- These gas stove burner cover liners help keep the cooking area cleaner by collecting oil splashes, food spills and residue around the burner. Their round open-center design fits around compatible stove burners and supports quicker cleanup during regular kitchen use. Key Features :- Open-center design fits around compatible gas burners Raised edges help contain spills and cooking residue Protective liner reduces direct mess on the stove surface Lightweight construction allows convenient placement Round shape provides practical burner-area coverage Disposable format supports quick cleanup after use Stackable design allows compact k&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-1.jpg</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-2.jpg</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-3.jpg</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-4.jpg</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-5.jpg</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11401-6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="51" customHeight="1">
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>5871_soup_spoon_long_handle</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Silicone Soup Spoon – Multifunctional Strainer &amp; Ladle | Quickslice</t>
-        </is>
-      </c>
-      <c r="H16" t="n">
-        <v>595</v>
-      </c>
-      <c r="I16" t="n">
-        <v>229</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Elevate your Indian kitchen experience with our premium Silicone Soup Spoon , designed for both efficiency and durability. This versatile kitchen tool is perfect for effortlessly serving soups, gravies, and stews, while its integrated straining function makes it ideal for separating liquids from solids. Crafted from high-quality, food-grade silicone with a robust stainless steel core, this long handle spoon ensures a comfortable grip and safe use on all types of cookware, including delicate non-stick surfaces. Say goodbye to scratched pots and hello to seamless cooking with Quickslice. Key features Food-Grade Silicone: Made from premium, BPA-free, and heat-resistant silicone, ensuring safety and longevity in your kitchen. Integrated Strainer: Cleverly designed with a perforated head, allow&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/5871_soup_spoon_long_handle.jpg</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/0ed09443-014e-4d3b-9487-75d14c668891_8053bb08-02de-45ca-8639-b2465cfb357a.jpg</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_88bfeeeb-59ec-4b83-972a-5c0f071e922c.jpg</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_2056ab04-47f2-45bd-959c-cb027f30e827.jpg</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_faae6e8c-cf16-4787-9417-9702bb7038d0.jpg</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_e328dddc-891e-47d3-b5a2-77d55b9dd450.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="51" customHeight="1">
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>whl282_21022_cute_teddy_bear_kids_water_</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Kids Water Bottle – Cartoon Bear Shape with Straw &amp; Strap</t>
-        </is>
-      </c>
-      <c r="H17" t="n">
-        <v>465</v>
-      </c>
-      <c r="I17" t="n">
-        <v>269</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Kids water bottle designed with a cute cartoon bear shape, featuring a built-in straw and shoulder strap to make hydration fun and easy for children. This kids water bottle encourages regular drinking with its leakproof flip-lock lid and transparent body to monitor water levels. Key features Fun cartoon bear design tailored for kids Convenient built-in straw for easy sipping Leakproof flip-lock lid prevents spills and leaks Adjustable shoulder strap for hands-free carrying Transparent body to easily check remaining water Lightweight and safe edges suitable for children Encourages kids to drink water regularly Perfect for school, travel, and outdoor activities Materials &amp;amp; care Made from high-quality plastic materials, this water bottle is easy to clean and maintain. Hand wash recommended to&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Bottle-01_8f4648a9-b2f8-43d1-9988-fe2d06cd44b5.jpg</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/8548082b-cecd-4ecc-a779-d0e2094031b7.jpg</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Bottle-04_a6b8d7f6-d411-461a-8ad2-075562f1f480.jpg</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/21022_cute_teddy_bear_kids_water_bottle_1pc.jpg</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Bottle-05_79b91998-a4bf-4012-8ff4-a41f7297f602.jpg</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Bottle-06_81ae6ef2-c4f1-42a0-a098-64e3de016b31.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="51" customHeight="1">
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>5834_3in1_chopping_board_peeler_knife_se</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Kitchen Knife Set – 3 in 1 Knife, Chopping Board &amp; Peeler</t>
-        </is>
-      </c>
-      <c r="H18" t="n">
-        <v>460</v>
-      </c>
-      <c r="I18" t="n">
-        <v>269</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Experience the convenience of our Kitchen Knife Set, a versatile 3 in 1 solution featuring a sharp kitchen knife, sturdy chopping board, and an efficient vegetable peeler. Designed for easy and safe food prep, this set is perfect for slicing, chopping, and peeling fruits and vegetables effortlessly. Key features Includes a sharp kitchen knife for precise cutting Durable chopping board offering a stable, hygienic surface Vegetable peeler that makes peeling quick and easy Compact and lightweight design ideal for daily cooking Easy to clean and maintain for long-lasting use Perfect for home cooks and professional chefs alike FAQ Q1: What does the Kitchen Knife Set include? A: The set includes a sharp knife, a sturdy chopping board, and a vegetable peeler. Q2: Is this set suitable for daily us&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/36_chopping-board.jpg</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_e97e52a4-ffc2-403f-b1f1-0a43a08c732b.jpg</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/35_chopping-board.jpg</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/38_chopping-board.jpg</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/39_chopping-board.jpg</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/43_chopping-board.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="51" customHeight="1">
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>10595_supermom_full_round_pincer</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Stainless Steel Full Round Kitchen Pincer – Heavy Duty Grip</t>
-        </is>
-      </c>
-      <c r="H19" t="n">
-        <v>485</v>
-      </c>
-      <c r="I19" t="n">
-        <v>329</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The stainless steel full round kitchen pincer offers heavy-duty, rust-resistant performance for safely handling hot cookware in any kitchen setting. Crafted from premium stainless steel, this kitchen pincer delivers unmatched durability and heat resistance, making it ideal for lifting and moving hot utensils like pressure cooker lids, kadhai, and tandoor grillware without risking burns. Its full round gripping ends provide a secure, slip-resistant hold, increasing safety and control with every use. Key features Made from premium stainless steel ensuring rust and corrosion resistance Full round gripping ends for firm, secure handling of hot cookware Ergonomic, slip-resistant handle for comfortable grip during extended use Heavy-duty construction supports lifting heavy pots and pans with eas&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/10595.png</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_2b373ef3-c1de-43b4-8a05-afe9d3c70f0e.jpg</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_2cc68044-cd07-47c6-afc6-da5ce039f4b3.jpg</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_f817ef22-e426-45b7-b8ed-73be3d1d2eec.jpg</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_488e2cd9-49dc-4aed-9de6-cb7433861b80.jpg</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_9ac277ac-4dd4-43c7-96cc-ecdd7bb572a6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="51" customHeight="1">
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>10597_supermom_spring_o_masher</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Stainless Steel Potato Masher – Heavy Duty with Comfortable Grip</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>529</v>
-      </c>
-      <c r="I20" t="n">
-        <v>349</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The stainless steel potato masher is a heavy-duty kitchen essential designed for effortless mashing of vegetables, potatoes, and fruits. Featuring a robust spring design and ergonomic non-slip handle, this masher ensures smooth, even pressure for the perfect mash every time. Whether preparing mashed potatoes, pav bhaji, soups, or baby food, this kitchen masher delivers reliable performance for home cooks and professionals alike. Key features Durable stainless steel spring design offers long-lasting strength and efficient mashing. Ergonomic handle with a comfortable, non-slip grip for ease of use and better control. Perfect for mashing potatoes, vegetables, fruits, pav bhaji, soups, and baby food. Easy to clean and maintain for everyday kitchen tasks. Compact, lightweight design allows conv&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-01.jpg</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_88888870-0e35-41de-9966-35da992a8f27.jpg</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-02.jpg</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-03.jpg</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-05.jpg</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Maser-04.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="51" customHeight="1">
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>24591_vegetables_n_fruit_peeler_1pc</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Stainless Steel Vegetable and Fruit Peeler with Swivel Blade for Kitchen</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>525</v>
-      </c>
-      <c r="I21" t="n">
-        <v>229</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Discover the ultimate kitchen companion with our stainless steel swivel blade vegetable peeler . This essential tool is engineered for effortless peeling of various fruits and vegetables, making your food preparation quicker and more enjoyable. Its smooth swivel blade glides along contours, ensuring thin, efficient removal of skins without wasting pulp. The comfortable handle provides a steady grip, enhancing control and safety during use, while the durable stainless steel construction promises long-lasting performance in any kitchen. Key features Sharp swivel blade follows uneven produce surfaces for controlled, efficient peeling. Durable stainless steel construction ensures reliable everyday use and rust resistance. Comfortable cylindrical handle offers a steady, non-slip grip during foo&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-1.jpg</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-2.jpg</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-3.jpg</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-4.jpg</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-5.jpg</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/24591-6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="51" customHeight="1">
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>11035_apex_ss_chimta_1pc</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Durable Stainless Steel Chimta for Safe Kitchen Use</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>525</v>
-      </c>
-      <c r="I22" t="n">
-        <v>269</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Discover the essential kitchen tool for safe and effortless food handling. This premium stainless steel chimta, crafted for durability and performance, ensures you can manage hot items with confidence and ease. Perfect for a variety of cooking tasks, it&amp;#x27;s designed to be a reliable addition to any home or commercial kitchen. Ensures secure handling of hot food, providing a strong, reliable grip for flipping, turning, and serving with confidence and ease. Crafted from high-quality stainless steel, offering exceptional durability, rust resistance, and long-lasting performance for daily kitchen tasks. Designed with heat-resistant construction, allowing safe and comfortable use when cooking on gas stoves, tandoors, or induction cooktops. Simplifies your cooking, ideal for effortlessly managing&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Chimta-WOSKU-01.jpg</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/477S.Schimta.jpg</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Chimta-02.jpg</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/11035_apex_ss_chimta_1pc.jpg</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Chimta-04.jpg</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Chimta-size.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="51" customHeight="1">
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>12133_pots_n_pans_protectors_pad_3pc</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Felt Pots and Pans Protectors – Set of 3 Sizes | Bake &amp; Dwell</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>569</v>
-      </c>
-      <c r="I23" t="n">
-        <v>219</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Kitchen &amp; Dining</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Felt pots and pans protectors are essential kitchen accessories that prevent scratches and damage to your cookware and countertops. This set of 3 protectors, available in large (38cm), medium (35cm), and small (26cm), ensures versatile use across all your pots, pans, plates, and bowls. Made from eco-friendly polyester felt, these protectors absorb impact and prevent stacking damage while adding a layer of heat protection. Key features Prevents scratches and chips between cookware pieces during storage or transport. Set includes three sizes: large, medium, and small for versatile kitchen use. Made from durable, eco-friendly polyester felt with a non-slip texture. Protects countertops from heat damage and wear during cooking and storage. Washable and reusable for long-lasting protection and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_25269f02-055a-4659-a291-500d76d2a632.jpg</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ec19082a-e5f4-4e4c-b86b-c65ae1a03429.jpg</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_0f6aa29e-7d42-498c-bdea-1a4bed11a7b1.jpg</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_a24a3d9f-48ed-4e64-a242-183097085924.jpg</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_1b5c7773-d8de-4ed5-8534-4bfd25e3895b.jpg</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_918aca57-ed07-4823-90fc-f7beeab4b5ae.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="51" customHeight="1">
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>18209_tranparent_adhesive_hook_6pc</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Transparent Adhesive Hooks (6 Pcs) – Strong &amp; Reusable | GlimmerHome</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>595</v>
-      </c>
-      <c r="I24" t="n">
-        <v>229</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Transform your home organisation with our versatile 6-piece transparent adhesive hook set . These strong, damage-free wall hooks are perfect for decluttering kitchens, bathrooms, and living spaces without drilling or leaving residue. Enjoy a clean, organised environment with GlimmerHome&amp;#x27;s premium adhesive solution. Key features Damage-Free Adhesion: Each transparent adhesive hook features a separate backing strip that adheres firmly to flat surfaces like tiles, glass, metal, and painted walls, yet removes cleanly without leaving marks or damage. High Load Capacity: Designed for durability, these robust wall hooks can hold up to 3 kg, making them ideal for hanging towels, kitchen utensils, coats, bags, and more. Versatile &amp;amp; Multi-Purpose: Use these strong wall hooks in your kitchen for ladl&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/18209_6797fc84-afc2-466b-95f8-85630df2c85e.png</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04f0556f-6f62-4753-b7e7-1c93ed9374c3.jpg</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_548f39c8-7fd2-438e-bb25-36c27165b698.jpg</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_5f77b3bb-bd98-4a6f-ac78-c644b98e92a7.jpg</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/017_9155afd4-927a-4888-8b1c-35ed4bca6832.jpg</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_f7bd0aa4-9449-4a5b-831b-1f6ee70f0368.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="51" customHeight="1">
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>whl175_94381_wg_1103_mix</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>LED Study Lamp with 3 Brightness Modes, Touch Control &amp; Flexible Neck (Color may vary)</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>509</v>
-      </c>
-      <c r="I25" t="n">
-        <v>319</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Brighten your workspace or study area with our versatile flexible neck LED desk lamp. This modern lamp features three adjustable brightness modes (Low, Medium, High) to suit any task, easily controlled with a sensitive touch button on its base. The flexible silicone gooseneck allows for effortless positioning, directing light exactly where you need it, making it perfect for reading, studying, working, or as a bedside light. Its compact design and non-slip base ensure stability on any surface, from study tables to office desks and kids&amp;#x27; rooms. Conveniently USB powered, this flexible neck LED desk lamp is an essential for efficient and comfortable lighting. Key features 3 Brightness Levels: Easily switch between Low, Medium, and High light modes for optimal visibility. Touch Control: Simple&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/6ObziZgHB0.jpg</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4WYl48GuEt.jpg</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/hh7UyUhSXR.jpg</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/G3T8shx0jb.jpg</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Kf9qrNrAh3.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="51" customHeight="1">
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>whl282_13405_cartoon_led_desk_lamp_1pc</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Kids LED Desk Lamp – Cute Cartoon Eye-Protection | Deodap</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>510</v>
-      </c>
-      <c r="I26" t="n">
-        <v>349</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Brighten up your child&amp;#x27;s study space or bedside with our adorable Kids LED Desk Lamp from Deodap. Designed with a charming cartoon character base, this flexible and portable lamp provides soft, eye-friendly illumination, making it perfect for reading, homework, or a comforting night light. Its advanced luminous technology ensures there&amp;#x27;s no harsh glare, safeguarding your little one&amp;#x27;s eyes during long study sessions or quiet bedtime stories. Give them the gift of comfortable and fun lighting with this versatile LED lamp. This delightful Kids LED Desk Lamp combines playful aesthetics with practical functionality. Whether placed on a study table, bedside cabinet, or carried around for creative play, its lightweight and flexible design adapts to various needs. The USB rechargeable feature adds&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/13405_cartoon_led_desk_lamp_1pc.jpg</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/d8dad9aa-d991-4606-a71f-561e6256a024.jpg</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_59ead39c-d786-4226-8b68-7979a4ba3661.jpg</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_1576a615-9884-4df5-bc62-8acad894791d.jpg</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_bde756db-bd43-4bea-9032-87fe6dcf789f.jpg</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_333169df-d3f6-4529-9cb7-63be3d9e1164.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="51" customHeight="1">
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>23627_cute_panda_night_lamp_1pc</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Cute Panda Showpiece Night Light for Kids Room Table &amp; Home Decor</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>439</v>
-      </c>
-      <c r="I27" t="n">
-        <v>249</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Add a cute and playful touch to your space with this adorable panda showpiece . Featuring a cheerful panda expression, raised paws, and attractive detailing, this compact showpiece is ideal for decorating kids&amp;#x27; rooms, study tables, desks, shelves, and bedside tables. Its charming design also makes it a lovely gifting option for children, friends, and panda lovers. Key Features Cute Panda Design: Adorable facial expression with attractive black, white, pink, and green detailing. Compact Decorative Showpiece: Easy to place on tables, desks, shelves, and cabinets. Kids Room Decor: Adds a fun and cheerful touch to children&amp;#x27;s rooms and study areas. Multipurpose Decoration: Suitable for home, bedroom, study table, office desk, and display shelf. Cute Gift Option: Ideal for birthdays, return gift&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/GFCe3rlgHp.jpg</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ucrJjgY1AW.jpg</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/nIy5BvRK2Q.jpg</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/VHw3tFUnjw.jpg</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/dsVOdM1a8j.jpg</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4A7fcmAQ14.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="51" customHeight="1">
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>4654_6pc_flexible_wall_hook</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Wall Hook Rail – Heavy Duty 6-Pin Transparent Golden | GlimmerHome</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>489</v>
-      </c>
-      <c r="I28" t="n">
-        <v>219</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Upgrade your home organisation with the Transparent 6-hook adhesive wall rail , designed to bring both style and exceptional utility to any space. Crafted for Indian homes, this heavy-duty 6-pin organiser helps declutter your living areas, offering a smart solution for hanging essentials. Its unique transparent and golden finish adds a touch of modern sophistication, making it more than just a functional item – it&amp;#x27;s a decor enhancer. Say goodbye to cluttered countertops and misplaced items. This versatile Transparent 6-hook adhesive wall rail is perfect for entryways, bathrooms, bedrooms, and kitchens, providing convenient access to coats, keys, towels, and accessories. Experience the blend of durability and design that GlimmerHome brings to your daily life, simplifying your home organisat&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Transparent-6-Wall-Hook-Using-1500x1500.png</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4654_7e0d08fc-1d7b-4546-a853-669e04f99943.jpg</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_6c983aa7-83e3-4e60-9f3d-8e9a2a8457fa.jpg</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_c0cb4c30-a185-49c9-bbed-6d75bc1569da.jpg</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_c889bba5-02b7-4236-b77b-f8b024f2277e.jpg</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_0424d040-e5e1-4363-8a95-e79fc589719f.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="51" customHeight="1">
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>17597_decor_round_mehndi_name_plate_1pc</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Mehndi Ceremony Wall Hanging – Lightweight Round Decorative Sign</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>485</v>
-      </c>
-      <c r="I29" t="n">
-        <v>259</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Enhance your wedding with this Mehndi ceremony wall hanging, designed to bring a traditional and festive charm to your mehndi, haldi, sangeet, or pre-wedding décor. This lightweight round decorative sign features the Hindi “मेहंदी” cut-out lettering, making it an eye-catching backdrop element perfect for photo booths, stage styling, or entrance decorations. Key features Bold round wall sign with Hindi “मेहंदी” lettering for instant cultural theme décor Lightweight and reusable design for easy installation and storage Pre-drilled holes for quick hanging using hooks, nails, strings, or double-sided tape Smooth, wipe-clean surface that resists creasing unlike paper decorations Complements floral curtains, fairy lights, drapes, and balloons for elegant styling Travel-friendly for versatile use&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-01.jpg</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/102517597-99Pc-Mahendi-Av-Sv.jpg</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-06.jpg</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-02.jpg</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-05.jpg</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Mehndi-wall-Decoration-03.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="51" customHeight="1">
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>whl175_77886_1723_3</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Lord Ganesha Hanging Suncatcher Wall Decor for Home, Balcony &amp; Car</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>539</v>
-      </c>
-      <c r="I30" t="n">
-        <v>399</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Enhance your home with the divine presence of this Lord Ganesha glass hanging decor. Featuring a vibrant Ganesha illustration, this decorative piece symbolizes wisdom, prosperity, and positive energy for any space. Key features Divine Lord Ganesha Design: Symbolizes wisdom, prosperity, protection, and positive energy for your home. Premium Hanging Cord: Durable natural jute rope with decorative beads adds a stylish finish. Multi-Purpose Decoration: Suitable for living room, pooja room, balcony, window, yoga room, meditation space, office, and car. Bright And Attractive Artwork: Vibrant colors add elegance and spiritual charm to any decor. Easy to Hang: Lightweight and ready to hang on hooks, walls, windows, or doors. Ideal Gift: Perfect for Diwali, Ganesh Chaturthi, housewarming, weddings,&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/BEWKLC04mY.png</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wJ201azNKz.png</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wCD72wwif2.png</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4DFiLQ8IUO.png</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/FU2YHsgGEM.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="51" customHeight="1">
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>whl294_79825_17423_2_mix</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>DIY Tulip Mirror Lamp Kit - Colorful LED Night Light Decor</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>485</v>
-      </c>
-      <c r="I31" t="n">
-        <v>349</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Unleash your creativity and brighten any space with the captivating DIY Tulip Mirror Lamp Kit. This unique craft project transforms into a beautiful decorative light, featuring vibrant tulip flowers encased within reflective mirror panels. Enjoy the enchanting glow when lit, or the sleek mirror aesthetic when off, adding a touch of elegance to your home décor. Engage in a delightful DIY craft experience by assembling your own enchanting floral lamp, perfect for creative minds and décor enthusiasts. Experience a stunning visual transformation as colorful LED tulips illuminate when switched on, reflecting beautifully in the mirror panels. Adorn your space with a charming mix of pink, blue, yellow, and purple tulip-style flowers, creating an attractive and vibrant decorative display. Immerse&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/u8drG5EhUt.jpg</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/CATOkciJbJ.jpg</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Epb3Ml6Jfb.jpg</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/63AYFzw0Qy.jpg</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/5uHg5DzVvg.jpg</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/DGnfKB1TaP.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="51" customHeight="1">
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>21058_cube_tulip_flower_night_lamp_set</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Tulip Flower LED Cube Night Lamp – Warm Ambient Decorative Light</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>499</v>
-      </c>
-      <c r="I32" t="n">
-        <v>349</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Elevate your home atmosphere with the Tulip Flower LED Cube Night Lamp, a perfect blend of elegant design and soothing illumination. This decorative tulip flower LED cube lamp casts a warm ambient glow that enhances any room&amp;#x27;s mood and style. Key features Transparent cube design featuring a glowing tulip flower pattern Soft, warm LED light ideal for calming and ambient illumination Perfect for bedside, tabletop decor, and mood lighting Compact and lightweight for versatile placement on shelves and corners Enhances your home decor with a stylish floral accent Suitable for festive decoration and gifting on special occasions FAQ Q1: What is a Tulip Flower LED Cube Night Lamp? A: It&amp;#x27;s a decorative LED cube lamp with illuminated tulip flower patterns providing warm ambient lighting for home dec&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/21058_cube_tulip_flower_night_lamp_set_showcase_9d041eca-ef47-441b-b6c4-254c25047868.png</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_LED-Mirror.jpg</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_LED-Mirror.jpg</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_LED-Mirror.jpg</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_LED-Mirror.jpg</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_LED-Mirror.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="51" customHeight="1">
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>whl175_77890_634_1</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Cute Panda LED Night Lamp for Kids Room Bedroom &amp; Table Decor</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>489</v>
-      </c>
-      <c r="I33" t="n">
-        <v>249</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Brighten up any child&amp;#x27;s space with this adorable Panda LED Night Lamp. Featuring a charming panda character wearing a playful green leaf hat, this lamp emits a soft, warm glow, creating a comforting and cosy atmosphere in kids&amp;#x27; rooms and bedrooms. Its compact design makes it a versatile decorative piece for bedside tables, study desks, shelves, or nightstands, adding a touch of whimsy and warmth to any decor. Key features Adorable Panda Design: Features a cute panda with a unique green leaf-style top. Soft LED Illumination: Provides a gentle, warm light perfect for a relaxing nighttime ambience. Ideal for Kids&amp;#x27; Rooms: Attractive and safe lighting option suitable for children&amp;#x27;s bedrooms. Compact Tabletop Size: Easily fits on bedside tables, desks, and shelves. Decorative Accent: Adds a chee&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W33" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/FKUenUuiTR.jpg</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/qrWMMj8Ix0.jpg</t>
-        </is>
-      </c>
-      <c r="Y33" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4aHVA4gast.jpg</t>
-        </is>
-      </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/ey2n5tAG2O.jpg</t>
-        </is>
-      </c>
-      <c r="AA33" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/yeIr4pK2bc.jpg</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/qLsafc32Mr.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="51" customHeight="1">
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>21255_cute_mini_panda_night_light_lamp</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Cute Mini Panda Night Light – Soft LED Bedside Lamp for Kids</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>440</v>
-      </c>
-      <c r="I34" t="n">
-        <v>289</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>Home Decor</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The cute mini panda night light is designed to provide a gentle, calming glow that helps children feel safe and cozy at night. Perfect for bedrooms, nurseries, and study desks, this adorable panda lamp combines charming decor with functional lighting, creating a relaxing atmosphere for restful sleep. Its compact size makes it an ideal bedside companion, offering a soft, soothing light that does not disturb sleep patterns. Key features Cute panda design enhances room decor and adds a playful touch Soft LED light creates a calming, cozy ambiance Ideal as a night lamp for peaceful sleep and bedtime routines Compact and lightweight, perfect for small spaces and portable use Energy-efficient lighting saves power while illuminating effectively Child-safe and durable design ensures peace of mind&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W34" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-WOSKU-01.jpg</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/21255.jpg</t>
-        </is>
-      </c>
-      <c r="Y34" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-03.jpg</t>
-        </is>
-      </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-06.jpg</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-04.jpg</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Lightpanda-07.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="51" customHeight="1">
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>4785_selfie_ring_light</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Selfie Ring Light – Portable LED for Flawless Photos &amp; Videos | Gambit</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>470</v>
-      </c>
-      <c r="I35" t="n">
-        <v>299</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Transform your photos and videos with the ultimate Selfie Ring Light from Gambit, designed to provide professional-grade illumination wherever you go. Say goodbye to dull, poorly lit shots and hello to vibrant, perfectly exposed content. This portable ring light is an essential tool for creators, beauty enthusiasts, and anyone looking to enhance their digital presence with brilliant lighting. Whether you&amp;#x27;re taking a quick selfie, recording a detailed makeup tutorial, or engaging in video calls, this LED ring light ensures you always look your best. Its lightweight and compact design makes it incredibly easy to carry, fitting seamlessly into your bag or purse. Experience the difference a dedicated light source makes, providing even, soft illumination that eliminates harsh shadows and brings&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W35" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/01_9517595e-8d48-451f-91b7-e252bf2d5beb.jpg</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/F3KmSjCQqupnir8zXY8mlr2ezuDOTMSE6vAlE6DE.jpg</t>
-        </is>
-      </c>
-      <c r="Y35" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/10_0d64f988-9475-46ff-b89d-9a7f34df7618.jpg</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/2092621090.png</t>
-        </is>
-      </c>
-      <c r="AA35" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/2092621089.png</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/08_c074b9b2-7a8c-42fb-bac4-2024d4b136cb.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="51" customHeight="1">
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>whl282_4810_portable_desk_fan_big</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Portable Desk Fan – Quiet 3-Speed USB Power for Home &amp; Office | VoltDesk</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>455</v>
-      </c>
-      <c r="I36" t="n">
-        <v>299</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Stay cool and comfortable anywhere with the **Mint green portable USB desk fan** from VoltDesk. Designed for ultimate convenience and efficiency, this compact yet powerful fan is your perfect companion for home, office, study, or travel. Experience a refreshing breeze without distracting noise, thanks to its advanced brushless motor and energy-saving USB power compatibility. Whether you&amp;#x27;re working, relaxing, or on the go, this Mint green portable USB desk fan ensures a steady, quiet airflow to keep you comfortable through the Indian summers. This versatile mini table fan is engineered for modern lifestyles, offering not just portability but also robust performance. Its thoughtful design includes a protective fence cover for enhanced safety, making it suitable for use around children and pe&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_portable_desk_fan_big.jpg</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_1.jpg</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810.jpg</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_2.jpg</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_3.jpg</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/4810_5.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="51" customHeight="1">
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>22669_mini_usb_fan_1pc</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Portable USB Mini Fan – Compact &amp; Adjustable for Personal Cooling</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>475</v>
-      </c>
-      <c r="I37" t="n">
-        <v>219</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The Portable USB Mini Flexible Fan is your ideal solution for personal cooling on the go. With its bendable neck, you can direct airflow precisely where needed, making it perfect for workspaces, travel, and outdoor activities. Its compact design ensures portability without sacrificing performance, while being USB-powered means it’s compatible with laptops, power banks, and USB adapters for convenience anywhere you need a quick cool-down. Key features Flexible bendable neck for customized airflow direction USB powered for compatibility with laptops, power banks, and wall adapters Small, lightweight, and portable design ideal for travel and outdoor use Quiet operation suitable for office, study, or personal spaces Energy-efficient with durable construction for long-lasting use Materials &amp;amp; ca&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-WOSKU-01.jpg</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_4175b6cb-c6c1-4235-bf70-6662635ced44.jpg</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-6.jpg</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-04.jpg</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-05.jpg</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/PoweredMiniFan-size.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="51" customHeight="1">
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>6183_mini_usb_fan</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Mini USB Fan Portable Mobile Phone Plug In Cooling Fan Soft Blades</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>599</v>
-      </c>
-      <c r="I38" t="n">
-        <v>229</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Stay cool anywhere with this green portable USB-C phone fan. Designed for convenience, this mini fan plugs directly into your smartphone, offering instant personal cooling. Its soft, flexible blades ensure safety, making it perfect for travel, outdoor activities, or simply beating the summer heat. Key features Plugs directly into your mobile phone for instant personal cooling on the go Soft flexible blades are safe to touch and will not hurt fingers during use Compact and lightweight design fits easily in pockets, bags, and travel kits No batteries required as it draws power directly from your smartphone via USB-C Powerful airflow provides refreshing cooling during hot summer days Simple plug and play operation with no setup or charging needed Ideal for travel, commuting, outdoor events, a&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W38" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-01.jpg</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_7568eccf-ac04-4a0b-a5ac-ed6145d5cecd.jpg</t>
-        </is>
-      </c>
-      <c r="Y38" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-05.jpg</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-06.jpg</t>
-        </is>
-      </c>
-      <c r="AA38" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-04.jpg</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniUSBFan-size.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="51" customHeight="1">
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>22877_5_mode_mini_led_keychain_flashligh</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>5 Mode Mini COB LED Keychain Flashlight with Carabiner Clip</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>539</v>
-      </c>
-      <c r="I39" t="n">
-        <v>329</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Discover the versatility of the 5 Mode Mini COB LED Keychain Flashlight, your perfect companion for illumination on the go. This compact and powerful device, featuring a vibrant red and black design, ensures you always have light when you need it most. Ideal for everyday carry, it easily attaches to your keys or bag, providing reliable lighting for various situations. Key features Five lighting modes: high, low, strobe, SOS, and spotlight for adaptable use. Powerful COB LED panel offers bright, wide-area flood lighting. Secondary spotlight torch delivers a focused beam for longer distances. Built-in carabiner clip allows easy attachment to keys, bags, or belts. Ultra-compact, pocket-sized, and lightweight for effortless portability. Durable ABS plastic construction withstands daily use and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-01.jpg</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/sku_8c5297b5-e3ce-4c22-8bcd-73584449baa9.jpg</t>
-        </is>
-      </c>
-      <c r="Y39" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-02.jpg</t>
-        </is>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-04.jpg</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-03.jpg</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/MiniPortableFlashlightKeychain-size.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="51" customHeight="1">
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>13978_mini_light_up_torch</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Mini LED Torch – Compact, Portable &amp; Bright Light</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>629</v>
-      </c>
-      <c r="I40" t="n">
-        <v>229</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Discover the convenience of our Blue mini disco ball light wand, a compact and portable solution for reliable lighting and entertainment. This mini disco ball light wand is ideal for parties, events, or simply adding a fun ambiance to any room, providing bright, colourful illumination where you need it most. Lightweight and durable, it&amp;#x27;s designed for easy carrying and delivers efficient, long-lasting light with a captivating disco ball effect. Key features Compact size (10 cm length) for ultimate portability and easy handling Bright LED lights with a captivating mini disco ball effect Lightweight design, weighing just 35 grams, for effortless carrying Durable construction suitable for various indoor and outdoor settings Simple on/off switch for quick and easy operation Perfect for parties,&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W40" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/13978.png</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/3a5b73d1-bf19-4022-8c2a-db440ea0a35d.jpg</t>
-        </is>
-      </c>
-      <c r="Y40" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_5f2c06c6-3367-44a6-be67-2e2f8fdcb255.jpg</t>
-        </is>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_27406132-5058-4c6f-b0d0-3393c17bc9b7.jpg</t>
-        </is>
-      </c>
-      <c r="AA40" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_5742c6ca-7314-4e59-a2fa-54a570fd9d09.jpg</t>
-        </is>
-      </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_b71c037b-f863-4f69-ab9b-53e09f4b7102.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="51" customHeight="1">
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>6251_5in1_multifunction_brush</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Computer Cleaning Kit – 5-in-1 Multi-Function PC &amp; Keyboard | Dustiva</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>479</v>
-      </c>
-      <c r="I41" t="n">
-        <v>249</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Keep your digital world spotless with the ultimate Computer Cleaning Kit from Dustiva. This 5-in-1 multi-function tool is meticulously designed to tackle every speck of dust and grime from your precious electronics, ensuring they look new and perform optimally. Perfect for gamers, professionals, and everyday users in India, this kit is your go-to solution for comprehensive device maintenance, enhancing longevity and performance for your PC, keyboard, and earbuds. Key features 5-in-1 Comprehensive Cleaning: Includes a metal pen tip for stubborn grime, a high-density brush, a soft flocking sponge for delicate surfaces, a robust keyboard brush, and an easy-to-use keycap puller. Precision Earbuds Cleaning: The delicate flocking sponge and metal pen tip are perfect for cleaning wireless earbud&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W41" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/3image_2793e13d-4fea-4a76-b3d9-af8a42520c96.jpg</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/1image_c52a168c-ae61-4870-8128-c0d76696cef6_1.jpg</t>
-        </is>
-      </c>
-      <c r="Y41" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/2image_be686450-a4f9-4053-aad1-666afcaa5443.jpg</t>
-        </is>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/7image_34fbcf4e-da9d-4bbb-a106-90222c272fa0.jpg</t>
-        </is>
-      </c>
-      <c r="AA41" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/4image_cc4a377e-c606-41f2-bfb3-251d61415521.jpg</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/5image_7e463727-3a9c-4118-8718-49609b03d19a.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="51" customHeight="1">
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>6124_4pc_multi_p_mob_stand</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Wall Mounted Phone Holder – Multi-functional Organizer | Organivo</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>515</v>
-      </c>
-      <c r="I42" t="n">
-        <v>239</v>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Transform your living space and keep essentials neatly organised with our innovative Wall Mounted Phone Holder . This multi-functional organiser is designed to declutter your bedside, desk, or kitchen, providing a dedicated spot for your smartphone and remote controls. Say goodbye to misplaced remotes and tangled charging cables; this sleek solution from Organivo ensures everything is always within reach and perfectly tidy. Key features Dual Functionality: Serves as both a secure wall mounted phone holder and a convenient remote control organizer. Integrated Charging Port: Thoughtfully designed with a bottom opening, allowing you to charge your phone effortlessly while it rests in the holder. Easy, Damage-Free Installation: Features strong adhesive backing for quick and simple mounting on&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W42" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/3b9a0d7f-a23d-4029-b99f-358519825831.jpg</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/01_ad372f27-1965-4137-b508-425ee0c62640.jpg</t>
-        </is>
-      </c>
-      <c r="Y42" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_120dc563-a380-41e0-a7ac-df7cd114dd49.jpg</t>
-        </is>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/07_eebea5d0-1b3a-4f9d-a82e-b8e5ac760d57.jpg</t>
-        </is>
-      </c>
-      <c r="AA42" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/04_1667da0d-6ab3-4afb-8014-6ef3b3cf7eb7.jpg</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/products/08_a3feea56-c6d4-4edb-8158-53709169177f.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="51" customHeight="1">
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>23927_4_port_usb_to_usb</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>USB to Four Port USB Hub Multi Interface Adapter for Laptop and Computer</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>475</v>
-      </c>
-      <c r="I43" t="n">
-        <v>289</v>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Expand your connectivity with this versatile Silver 4-port USB hub adapter . Designed for both laptops and desktop computers, this compact device effortlessly transforms a single USB port into four, allowing you to connect multiple peripherals simultaneously. Ideal for decluttering your workspace or enhancing your travel accessory kit, this hub ensures seamless data transfer and device connectivity for everyday use. Key features Multi-interface USB hub design for expanded connectivity Standard USB input connector for universal compatibility Connects multiple USB accessories with ease Compact and lightweight body for portability Flexible attached connecting cable for convenient placement Simple plug-and-use design requires no drivers Suitable for both desk and on-the-go use Sleek silver and&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W43" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-1.jpg</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-sku.jpg</t>
-        </is>
-      </c>
-      <c r="Y43" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-2.jpg</t>
-        </is>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-3.jpg</t>
-        </is>
-      </c>
-      <c r="AA43" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-7.jpg</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23927-USB-Splitter-multiport-Adapter-6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="51" customHeight="1">
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>23597_usb_rechargeable_led_flashlight</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>USB Rechargeable LED Flashlight for Travel with Lamp Mode</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>559</v>
-      </c>
-      <c r="I44" t="n">
-        <v>349</v>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;USB Rechargeable LED Flashlight for Travel with Soft Lamp Mode for Trips, Camping and Night Use (1 Pc) Description :- A phone torch drains the battery you need for maps and calls, which is the wrong trade on a trip. This flashlight does the lighting so the phone does not have to. The beam covers a dark path or a hotel corridor, and the soft lamp mode gives enough light to find something in a bag without waking the person next to you. USB charging means the same cable that charges your phone charges this, so there is nothing extra to pack. Key Features Saves the phone battery you need for maps and calls Beam covers a dark path, corridor or campsite Soft lamp mode for finding things in a bag without waking anyone Charges off the same USB cable as your phone No batteries to carry or buy on th&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/c23b24ee-e8ec-4f49-a6a3-7fd08ff805ca.jpg</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/d52ec2cc-e497-44d8-9c22-089d55f3fd44.jpg</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23597-usb-rechargeable-led-flashlight-3.jpg</t>
-        </is>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23597-usb-rechargeable-led-flashlight-4.jpg</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23597-usb-rechargeable-led-flashlight-5.jpg</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/23597-usb-rechargeable-led-flashlight-6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="51" customHeight="1">
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>1637_usb_bike_light</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>USB Rechargeable Bicycle Headlight with Handlebar Mount for Night Riding</t>
-        </is>
-      </c>
-      <c r="H45" t="n">
-        <v>499</v>
-      </c>
-      <c r="I45" t="n">
-        <v>299</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Smart Gadgets</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Enhance your cycling safety with our USB rechargeable bicycle headlight , designed for superior visibility during night rides and low-light conditions. This reliable headlight ensures you can see the path ahead clearly and be seen by others, making your evening commutes and early morning adventures safer. Its compact design and easy handlebar mount make it a convenient and essential accessory for every cyclist. Key features Bright front beam provides excellent visibility in low-light conditions. USB rechargeable design eliminates the need for disposable batteries, offering an eco-friendly solution. Secure mounting bracket easily attaches to bicycle handlebars for stable positioning. Compact and lightweight body ensures it won&amp;#x27;t add unnecessary bulk to your bike. Simple control button allow&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-01.jpg</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-02.jpg</t>
-        </is>
-      </c>
-      <c r="Y45" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-03.jpg</t>
-        </is>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-04.jpg</t>
-        </is>
-      </c>
-      <c r="AA45" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-05.jpg</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1637-06.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="51" customHeight="1">
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>whl193_66653_dryfruit_box_open_square_de</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Royal Decorative Dry Fruit Box for Festive Serving &amp; Gifting</t>
-        </is>
-      </c>
-      <c r="H46" t="n">
-        <v>449</v>
-      </c>
-      <c r="I46" t="n">
-        <v>349</v>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Elevate your entertaining and gifting with the Royal Decorative Dry Fruit Box, a stunning piece designed to add elegance to any occasion. Perfect for showcasing an array of treats, from crunchy nuts to delightful sweets, this box combines traditional charm with practical functionality. Its exquisite design makes it a focal point on any table, embodying a sense of luxury and thoughtful presentation for both everyday use and special celebrations. Showcase Treats Elegantly: Designed for stylish serving and storage, this box beautifully displays nuts, dry fruits, sweets, and snacks, making every presentation special. Adds Royal Decorative Flair: Featuring a premium decorative design, it infuses a luxurious and traditional touch into your dining table and festive home decor instantly. Offers Ea&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W46" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/iK4vbVtSFD.jpg</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/oVYvpUeGUz.jpg</t>
-        </is>
-      </c>
-      <c r="Y46" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/VxXcStBWAR.jpg</t>
-        </is>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/mQd4WElKJY.jpg</t>
-        </is>
-      </c>
-      <c r="AA46" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/YAiVLYzI9T.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="51" customHeight="1">
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>14409_gold_metal_medal_n_tricolor_ribbon</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Gold Medal Gift with Tricolor Ribbon for Achievers, Kids and Winners (1 Pc)</t>
-        </is>
-      </c>
-      <c r="H47" t="n">
-        <v>505</v>
-      </c>
-      <c r="I47" t="n">
-        <v>219</v>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Celebrate success and milestones with this elegant Gold Medal Gift. Featuring a shiny gold finish and a vibrant tricolor ribbon, this award medal is a perfect keepsake for achievers of all ages. Ideal for recognising academic excellence, sports victories, or simply celebrating personal achievements, it makes a memorable token of pride and appreciation. Key features Gift of Pride: Celebrate achievements big and small. Gold Finish: Shiny, premium look. Tricolor Ribbon: Comfortable to wear around the neck. For All Ages: Suitable for kids and adults. Keepsake Gift: A lasting memory of a special moment. Many Occasions: Results, birthdays, sports and competitions. Lightweight: Easy to wear and carry. Easy Care: Wipe with a soft cloth to keep it shining. Materials &amp;amp; care Material: Metal with Fabr&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W47" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_439c02be-7e1a-45ae-9e16-fd6413cd5580.jpg</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/14409.jpg</t>
-        </is>
-      </c>
-      <c r="Y47" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_d002869f-bad7-469c-8675-e6142dd728bc.jpg</t>
-        </is>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_7de3e992-f6bf-4f9d-b0bb-4c4ac376125c.jpg</t>
-        </is>
-      </c>
-      <c r="AA47" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/07_800a7bc3-2477-4210-b220-6e490514726e.jpg</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_c18f5d4c-5cec-4262-b366-1e49c92c7c1d.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="51" customHeight="1">
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>whl282_19630_krishna_flute_metal_keychai</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Krishna Flute Keychain – Durable Stainless Steel Spiritual Accessory</t>
-        </is>
-      </c>
-      <c r="H48" t="n">
-        <v>499</v>
-      </c>
-      <c r="I48" t="n">
-        <v>219</v>
-      </c>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Experience divine blessings with our Krishna flute keychain, crafted from premium stainless steel for durability and spiritual elegance. This keychain features the iconic image of Lord Krishna holding his mystical flute, symbolizing love, harmony, and devotion. Perfect for organizing car, bike, home, or office keys while keeping the positive energy of Krishna close. Key features Intricate Krishna flute design with precise laser-cut detailing High-quality stainless steel resistant to rust and wear Compact and lightweight for effortless everyday carry Strong metal ring securely holds multiple keys Polished finish adding a sleek and stylish look Ideal as a thoughtful gift for Janmashtami, Diwali, or other festivities Combines spiritual significance with practical utility Materials &amp;amp; care Made&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U48" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W48" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-02_166f48cb-9946-410b-83a4-4a6dd6a4f3be.jpg</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/c5751ef3-5e9c-4060-85ef-a406ca3f909a_63b6b3a7-3e12-49b2-8d0c-828e9063dce3.jpg</t>
-        </is>
-      </c>
-      <c r="Y48" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-01_dc3e06fe-f38d-4392-8ca0-bdb67e367317.jpg</t>
-        </is>
-      </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-03_7878e90e-af45-49c2-b90b-a25ed15e63ca.jpg</t>
-        </is>
-      </c>
-      <c r="AA48" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-05_eabc8cf7-87cd-4d8b-aa87-8176020672c1.jpg</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Krishna-keychain-06_016cbeeb-315b-4913-8cbb-c622007878d7.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="51" customHeight="1">
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>13177_adhesive_phone_card_holder_1pc</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Adhesive Card Phone Holder – Zipper Pocket Wallet | Mobiléon</t>
-        </is>
-      </c>
-      <c r="H49" t="n">
-        <v>469</v>
-      </c>
-      <c r="I49" t="n">
-        <v>349</v>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Streamline your everyday essentials with the innovative Adhesive Card Phone Holder from Mobiléon. This sleek and practical accessory easily attaches to the back of almost any smartphone or case, transforming it into a convenient mobile wallet. No more fumbling for your cards or cash – everything you need is securely right at your fingertips. Designed for the modern Indian user, this durable phone back wallet combines minimalist style with maximum functionality, making it perfect for anyone looking to lighten their load while staying organised on the go. Key features Secure Zipper Pocket: Safely store your essential cards, ID, and cash in a discreet, zippered compartment, offering enhanced security over open card slots. Strong Adhesive Backing: Equipped with a high-quality adhesive, this mo&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U49" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W49" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_d38833c7-983f-43a2-a1dd-741444d2a86c.jpg</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/2_7f3b98af-0baf-49f8-aa0b-eb72269a8e5a.jpg</t>
-        </is>
-      </c>
-      <c r="Y49" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/1_9c8c1859-bb0a-45b4-a1b7-804b63796155.jpg</t>
-        </is>
-      </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wallet-3.jpg</t>
-        </is>
-      </c>
-      <c r="AA49" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wallet-7.jpg</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/wallet-6.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="51" customHeight="1">
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>whl146_11521_apex_ss_cat_mug_250ml_cm_cp</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Apex Cat Mug – 250 ml Stainless Steel Insulated Kids' Mug</t>
-        </is>
-      </c>
-      <c r="H50" t="n">
-        <v>510</v>
-      </c>
-      <c r="I50" t="n">
-        <v>319</v>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;The Apex Cat Mug is a delightful insulated kids&amp;#x27; mug designed with a cute double-cat print to brighten up your child&amp;#x27;s beverage time. This 250 ml stainless steel insulated mug combines fun design with practical features like a leak-proof lid and durable plastic outer body, perfect for keeping drinks warm for longer while ensuring easy handling for little hands. Key features Adorable Cat Design: Features a colorful double-cat print adding a playful charm. Insulated Stainless Steel Inner: Keeps beverages at the ideal temperature longer, ideal for hot tea, milk, or soup. Durable Plastic Outer Body: Lightweight and break-resistant for safe daily use by kids. Leak-Proof Lid: Prevents spills ensuring mess-free transport in school bags or desks. Comfort Grip Handle: Ergonomically designed for sma&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W50" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_db6a104e-3139-4cde-985e-dd560fbbaed5.jpg</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/842a32ec-6bd0-4386-8711-1ba93fac9f16.jpg</t>
-        </is>
-      </c>
-      <c r="Y50" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_d07ebb01-1990-4b5e-9b72-25c0360be465.jpg</t>
-        </is>
-      </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_62065805-7968-42b1-acdd-4b974ed1e1db.jpg</t>
-        </is>
-      </c>
-      <c r="AA50" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_9f1877c2-c4d5-4899-a616-291ee62b4bf8.jpg</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/06_35f0202e-f4af-43be-ba5c-ae92c52950c2.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="51" customHeight="1">
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>whl282_12774_jewellery_gift_box_1pc</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Ring Gift Box – Premium Elegant Presentation with Velvet Cushion</t>
-        </is>
-      </c>
-      <c r="H51" t="n">
-        <v>439</v>
-      </c>
-      <c r="I51" t="n">
-        <v>249</v>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Ring gift box crafted to perfectly present and protect your precious jewelry with elegance. Its sturdy decorative exterior and soft velvet cushion make it ideal for gifting and storage of rings. Key features Elegant jewelry presentation box with decorative diamond-themed finish Soft velvet-lined interior cushion prevents scratches and holds rings securely Snap-style magnetic closure ensures the box remains firmly sealed Hard protective outer casing provides safe storage and durability Compact and lightweight design suitable for gifting and travel Striking contrast color enhances the overall luxurious appearance Perfect for proposals, engagements, anniversaries, and jewelry shop presentations Materials &amp;amp; care The box features a hard outer shell with a decorative finish and a soft velvet-lin&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W51" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-WOSKU-01.jpg</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/19412774-128Pc-Ringbox-Av-Sv.jpg</t>
-        </is>
-      </c>
-      <c r="Y51" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-05.jpg</t>
-        </is>
-      </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-06.jpg</t>
-        </is>
-      </c>
-      <c r="AA51" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-04.jpg</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/Ringbox-size.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="51" customHeight="1">
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>18916_plastic_flower_vase_1pc</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Plastic Flower Vase – Elegant Design for Home &amp; Gift</t>
-        </is>
-      </c>
-      <c r="H52" t="n">
-        <v>505</v>
-      </c>
-      <c r="I52" t="n">
-        <v>259</v>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Discover the charm of the Plastic Flower Vase, crafted for elegant home decor and perfect as a thoughtful gift for family and friends. This plastic flower vase offers a sleek silhouette that enhances any room, bringing a fresh, decorative touch to your living room, office, or dining table. Key features Elegant and modern design with a smooth, textured finish for a refined look. Multipurpose vase suitable for fresh bouquets, artificial flowers, and silk greenery. Lightweight plastic construction ensures durability and easy handling. Ideal for home decor, office desk embellishment, bathroom, kitchen, or wedding centrepieces. An excellent gifting choice for birthdays, housewarmings, and special occasions. Compact size with dimensions: length 18 cm, width 7 cm, height 7 cm for versatile placem&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/01_91c87a05-2ddc-443d-aee5-5aaa0ccf7bb7.jpg</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/c7b8256b-ca06-449d-b7e2-4627ed71258c.jpg</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/03_09ed9caa-6d17-4595-8fd7-d5da22d94de9.jpg</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/04_7cda10fe-b23b-41b8-9646-9b6189b2cc87.jpg</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/05_671810cd-b793-47bd-9932-d837eb7a22ca.jpg</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/02_fe1fa176-7079-4eaf-ba0d-ae00d5d62249.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="51" customHeight="1">
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>whl282_22517_next_velvet_oud_attar_12ml</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Next Velvet Oud Attar – Long Lasting, Premium Fragrance Oil</t>
-        </is>
-      </c>
-      <c r="H53" t="n">
-        <v>510</v>
-      </c>
-      <c r="I53" t="n">
-        <v>369</v>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Discover the rich and luxurious scent of Next Velvet Oud Concentrated Attar Perfume 12 ML, designed for those who seek a deep, woody, and musky aroma that lasts for hours. This premium oud attar is ideal for individuals who appreciate traditional oriental fragrances with a modern twist. Crafted without alcohol, this unisex perfume offers a sophisticated,浓ent experience suitable for daily wear, special occasions, and religious gatherings. Its compact size makes it convenient for travel and on-the-go application, whether you prefer a roll-on or dab method. Key features Premium concentrated oud fragrance Long lasting and rich aroma Non alcoholic attar formula Suitable for men and women Elegant luxury bottle design Easy roll on or dab application 12 ML compact size Materials &amp;amp; care Maintain th&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U53" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W53" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-WOSKU-01.jpg</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-WSKU-01.jpg</t>
-        </is>
-      </c>
-      <c r="Y53" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-05.jpg</t>
-        </is>
-      </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-04.jpg</t>
-        </is>
-      </c>
-      <c r="AA53" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-03.jpg</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/NextCareVelvetOudAttar-size.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="51" customHeight="1">
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>8782_mini_jewelry_organizer_box</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Travel Jewellery Box – Portable PU Leather Organiser | LilyGleam</t>
-        </is>
-      </c>
-      <c r="H54" t="n">
-        <v>525</v>
-      </c>
-      <c r="I54" t="n">
-        <v>269</v>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Searching for the perfect travel jewellery box that combines style, functionality, and portability? Look no further than the LilyGleam Mini PU Leather Travel Jewellery Box. Designed for the modern Indian woman on the go, this elegant and compact organiser ensures your precious rings, necklaces, and earrings stay safe, secure, and tangle-free, whether you&amp;#x27;re heading to a weekend getaway or a business trip. Say goodbye to lost earrings and tangled chains with this essential accessory for every journey. Key features Compact &amp;amp; Portable Design: Perfectly palm-sized, this travel jewellery box easily fits into handbags, luggage, or carry-ons for convenient travel. Multi-Functional Storage: Thoughtfully designed compartments for rings, necklaces, earrings, studs, and even small makeup items like l&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U54" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W54" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---05.jpg</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/8782.jpg</t>
-        </is>
-      </c>
-      <c r="Y54" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---03.jpg</t>
-        </is>
-      </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---04.jpg</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---07.jpg</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/jewelry-box-1---06.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="51" customHeight="1">
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>21611_golden_rose_n_box</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Gold Plated Artificial Rose – Eternal Love Decor Gift</t>
-        </is>
-      </c>
-      <c r="H55" t="n">
-        <v>479</v>
-      </c>
-      <c r="I55" t="n">
-        <v>299</v>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;This gold plated artificial rose is a timeless symbol of eternal love and appreciation. Crafted with exquisite detail, this decorative golden rose perfectly expresses affection and serves as a lasting gift that never wethers, making it an ideal choice for special occasions or home decor. Key features Premium gold plating: The rose is coated with 24K gold foil, symbolising nobility and eternal love. Handcrafted artistry: Expert artisans precisely create each rose to capture the beauty of natural flowers. Elegant presentation: Comes in a beautiful purple premium box with a transparent front to showcase the rose without unboxing. Versatile decoration: Ideal for home, office decor, weddings, parties, or special occasions. Never fades or wilts: A lasting expression of love and best wishes that&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/WhatsApp_Image_2026-08-27_at_18.57.15_20b57117-2e09-4f20-8eb5-393c691ed431.jpg</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/08_c7bb241f-04da-47c1-8994-392fb0134638.jpg</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/whl175_67690_mn_033_go_3af2ed48-1c67-4301-b108-d55c01fa5eb1.jpg</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/61ClF3UfoWL._SL1000_d63357b1-11b2-49f3-90f0-c7267d160838.jpg</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/41nZL-LzlYL_0884f0a3-0f89-4e37-b20a-f67a189543c7.jpg</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/51VptqPMk5L._SL1500_4de1596f-93c1-4a3f-b0d1-bf4af8467a34.jpg</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="51" customHeight="1">
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>22311_paper_long_rectangle_empty_gift_bo</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Long Rectangular Paper Empty Gift Box with Bow for Jewellery and Gifting</t>
-        </is>
-      </c>
-      <c r="H56" t="n">
-        <v>509</v>
-      </c>
-      <c r="I56" t="n">
-        <v>219</v>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>GENERAL</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>Gifts &amp; Hampers</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>&lt;p&gt;Present your thoughtful gifts elegantly with this light blue rectangular gift box. Its sophisticated design and decorative bow create perfect packaging for jewellery, accessories, and other special presents, making every occasion memorable. Key features Long rectangular shape is ideal for slim gifts and accessories like watches or pens. Made from durable paper, offering a lightweight and eco-friendly packaging solution. Features an elegant decorative bow, providing a ready-to-gift appearance. Convenient removable lid allows for easy placement and stylish presentation of items. Compact profile ensures easy storage before use and after gifting. Neat light blue finish complements birthdays, anniversaries, and festive occasions. Reusable box can help organise small personal accessories or keep&lt;/p&gt;</t>
-        </is>
-      </c>
-      <c r="U56" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="W56" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-1-02.jpg</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-2-01.jpg</t>
-        </is>
-      </c>
-      <c r="Y56" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-3-03.jpg</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-4-04.jpg</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-5-07.jpg</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>https://cdn.shopify.com/s/files/1/0782/3284/6646/files/22311-6-06.jpg</t>
-        </is>
-      </c>
-    </row>
+    <row r="2" ht="51" customHeight="1"/>
+    <row r="3" ht="51" customHeight="1"/>
+    <row r="4" ht="51" customHeight="1"/>
+    <row r="5" ht="51" customHeight="1"/>
+    <row r="6" ht="51" customHeight="1"/>
+    <row r="7" ht="51" customHeight="1"/>
+    <row r="8" ht="51" customHeight="1"/>
+    <row r="9" ht="51" customHeight="1"/>
+    <row r="10" ht="51" customHeight="1"/>
+    <row r="11" ht="51" customHeight="1"/>
+    <row r="12" ht="51" customHeight="1"/>
+    <row r="13" ht="51" customHeight="1"/>
+    <row r="14" ht="51" customHeight="1"/>
+    <row r="15" ht="51" customHeight="1"/>
+    <row r="16" ht="51" customHeight="1"/>
+    <row r="17" ht="51" customHeight="1"/>
+    <row r="18" ht="51" customHeight="1"/>
+    <row r="19" ht="51" customHeight="1"/>
+    <row r="20" ht="51" customHeight="1"/>
+    <row r="21" ht="51" customHeight="1"/>
+    <row r="22" ht="51" customHeight="1"/>
+    <row r="23" ht="51" customHeight="1"/>
+    <row r="24" ht="51" customHeight="1"/>
+    <row r="25" ht="51" customHeight="1"/>
+    <row r="26" ht="51" customHeight="1"/>
+    <row r="27" ht="51" customHeight="1"/>
+    <row r="28" ht="51" customHeight="1"/>
+    <row r="29" ht="51" customHeight="1"/>
+    <row r="30" ht="51" customHeight="1"/>
+    <row r="31" ht="51" customHeight="1"/>
+    <row r="32" ht="51" customHeight="1"/>
+    <row r="33" ht="51" customHeight="1"/>
+    <row r="34" ht="51" customHeight="1"/>
+    <row r="35" ht="51" customHeight="1"/>
+    <row r="36" ht="51" customHeight="1"/>
+    <row r="37" ht="51" customHeight="1"/>
+    <row r="38" ht="51" customHeight="1"/>
+    <row r="39" ht="51" customHeight="1"/>
+    <row r="40" ht="51" customHeight="1"/>
+    <row r="41" ht="51" customHeight="1"/>
+    <row r="42" ht="51" customHeight="1"/>
+    <row r="43" ht="51" customHeight="1"/>
+    <row r="44" ht="51" customHeight="1"/>
+    <row r="45" ht="51" customHeight="1"/>
+    <row r="46" ht="51" customHeight="1"/>
+    <row r="47" ht="51" customHeight="1"/>
+    <row r="48" ht="51" customHeight="1"/>
+    <row r="49" ht="51" customHeight="1"/>
+    <row r="50" ht="51" customHeight="1"/>
+    <row r="51" ht="51" customHeight="1"/>
+    <row r="52" ht="51" customHeight="1"/>
+    <row r="53" ht="51" customHeight="1"/>
+    <row r="54" ht="51" customHeight="1"/>
+    <row r="55" ht="51" customHeight="1"/>
+    <row r="56" ht="51" customHeight="1"/>
     <row r="57" ht="51" customHeight="1"/>
     <row r="58" ht="51" customHeight="1"/>
     <row r="59" ht="51" customHeight="1"/>
